--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="136">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -146,17 +146,14 @@
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110423</t>
   </si>
   <si>
-    <t xml:space="preserve">BOLOGNESE, JOSEPH &amp; VIVI A: PLAN AMENDMENT to redesignate the existing land use: PA-26-700026-BOLOGNESE, JOSEPH &amp; VIVI A:
-PLAN AMENDMENT to redesignate the existing land use category from Corridor Mixed-Use (CM) to Compact Neighborhood (CN) on 1.93 acres.  Generally located north of Serene Avenue and east of Grand Canyon Drive within Enterprise. JJ/rk (For possible action)</t>
+    <t xml:space="preserve">Shamaim Henderson family entertainment centre: UC-26-0309-SHAMAIM HENDERSON, LLC:
+USE PERMITS for the following: 1) an avocational or vocational training facility; and 2) a recreational or entertainment facility on a portion of 5.11 acres in an IL (Industrial Light) Zone and an IP (Industrial Park) Zone within the Airport Environs (AE-60 &amp; AE-65) Overlay. Generally located south of Pilot Road and west of Bermuda Road within Enterprise.  MN/hw/cv  (For possible action)</t>
   </si>
   <si>
     <t>2026-07-20 | Clark County</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110398</t>
-  </si>
-  <si>
-    <t>Clark County filings are running ahead of Las Vegas this month. Worth a call before the next hearing cycle.</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110386</t>
   </si>
   <si>
     <t>By market</t>
@@ -183,33 +180,26 @@
 DESIGN REVIEW for a multi-family residential development in conjunction with an existing golf course on a 1.7 acre portion of 8.05 acres in a C-2 (General Commercial District) Zone within the Southern Highlands Planned Community (PCO) Overlay.  Generally located north of Robert Trent Jones Lane and west of Southern Highlands Parkway within Enterprise.  JJ/bb/kh  (For possible action)</t>
   </si>
   <si>
+    <t>Clark County | 163 At Casino Drive casino: Approve and authorize the Chair to sign Supplemental No. 8 to the interlocal contract between Clark County and Regional Flood Control District to extend the contract term for design of the State Route 163 at Casino Drive project.  (For possible action)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clark County | Visible Noise family entertainment centre: UC-26-0303-VISIBLE NOISE, LLC:
 HOLDOVER USE PERMIT for a proposed recreational or entertainment facility within an existing office/warehouse complex on a portion of 5.31 acres in an IP (Industrial Park) Zone within the Airport Environs (AE-60) Overlay. Generally located west of Tenaya Way and north of Sunset Road within Spring Valley.  MN/rp/cv  (For possible action)</t>
   </si>
   <si>
-    <t>Clark County | 163 At Casino Drive casino: Approve and authorize the Chair to sign Supplemental No. 8 to the interlocal contract between Clark County and Regional Flood Control District to extend the contract term for design of the State Route 163 at Casino Drive project.  (For possible action)</t>
+    <t>Clark County | Hilton Resorts resort: 3. UC-26-0373-HILTON RESORTS CORPORATION: USE PERMIT for a monorail on approximately 21 acres in an RM50 (Residential Multi-Family 50) Zone, a CR (Commercial Resort) Zone, and an IL (Industrial Light)</t>
+  </si>
+  <si>
+    <t>2026-07-28 | Clark County</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-uc-26-0373</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | Buona Vita resort: 2. AR-26-400068 (ET-25-400074(UC-23-0659))-BUONA VITA, LLC: USE PERMIT FIRST APPLICATION FOR REVIEW for daycare and school. WAIVERS OF DEVELOPMENT STANDARDS for the following: 1) trash enclosure; and </t>
   </si>
   <si>
-    <t>2026-07-28 | Clark County</t>
-  </si>
-  <si>
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-ar-26-400068+et-25-400074+uc-23-0659</t>
-  </si>
-  <si>
-    <t>Clark County | Hilton Resorts resort: 3. UC-26-0373-HILTON RESORTS CORPORATION: USE PERMIT for a monorail on approximately 21 acres in an RM50 (Residential Multi-Family 50) Zone, a CR (Commercial Resort) Zone, and an IL (Industrial Light)</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-uc-26-0373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Beltway 101, LLC &amp; Blue 10 leisure development: PA-26-700025-BELTWAY 101, LLC &amp; BLUE 10, LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 4.51 acres. Generally located north of Blue Diamond Road and west of Montessouri Street (alignment) within Enterprise. JJ/gc (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110451</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | Tropicana Land resort: WS-26-0113-TROPICANA LAND, LLC:
@@ -219,6 +209,13 @@
   <si>
     <t xml:space="preserve">Clark County | South Decatur Holding CO leisure development: PA-26-700010-SOUTH DECATUR HOLDING CO., LLC:
 PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 2.64 acres.  Generally located east of Decatur Boulevard and south of Moberly Avenue (alignment) within Enterprise. MN/rk (For possible action)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark County | Church Searchlight Community leisure development: PA-26-700019-CHURCH SEARCHLIGHT COMMUNITY:
+PLAN AMENDMENT to redesignate the existing land use category from Public Use (PU) to Neighborhood commercial (NC) on 4.8 acres.   Generally located west of US Highway 95 and north of State Route 164 within Searchlight. MN/rk  (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110428</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | G D Carden Entertainment museum: ET-26-400054 (UC-25-0072)-GD CARDEN ENTERTAINMENT, LLC:
@@ -227,22 +224,22 @@
 DESIGN REVIEW for a recreational or entertainment facility and museum on 1.82 acres in an RS20 (Residential Single-Family 20) Zone within a Historic Designation (HDO) Overlay.  Generally located north of Vegas Drive and west of Valley Drive within the Lone Mountain Planning Area.  WM/rr/cv  (For possible action)</t>
   </si>
   <si>
-    <t xml:space="preserve">Clark County | Church Searchlight Community leisure development: PA-26-700019-CHURCH SEARCHLIGHT COMMUNITY:
-PLAN AMENDMENT to redesignate the existing land use category from Public Use (PU) to Neighborhood commercial (NC) on 4.8 acres.   Generally located west of US Highway 95 and north of State Route 164 within Searchlight. MN/rk  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110428</t>
+    <t xml:space="preserve">Clark County | Beltway 101, LLC &amp; Blue 10 leisure development: PA-26-700025-BELTWAY 101, LLC &amp; BLUE 10, LLC:
+PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 4.51 acres. Generally located north of Blue Diamond Road and west of Montessouri Street (alignment) within Enterprise. JJ/gc (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark County | Shamaim Henderson family entertainment centre: UC-26-0309-SHAMAIM HENDERSON, LLC:
+USE PERMITS for the following: 1) an avocational or vocational training facility; and 2) a recreational or entertainment facility on a portion of 5.11 acres in an IL (Industrial Light) Zone and an IP (Industrial Park) Zone within the Airport Environs (AE-60 &amp; AE-65) Overlay. Generally located south of Pilot Road and west of Bermuda Road within Enterprise.  MN/hw/cv  (For possible action)</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | BOLOGNESE, JOSEPH &amp; VIVI A: PLAN AMENDMENT to redesignate the existing land use: PA-26-700026-BOLOGNESE, JOSEPH &amp; VIVI A:
 PLAN AMENDMENT to redesignate the existing land use category from Corridor Mixed-Use (CM) to Compact Neighborhood (CN) on 1.93 acres.  Generally located north of Serene Avenue and east of Grand Canyon Drive within Enterprise. JJ/rk (For possible action)</t>
   </si>
   <si>
-    <t xml:space="preserve">Clark County | Shamaim Henderson family entertainment centre: UC-26-0309-SHAMAIM HENDERSON, LLC:
-USE PERMITS for the following: 1) an avocational or vocational training facility; and 2) a recreational or entertainment facility on a portion of 5.11 acres in an IL (Industrial Light) Zone and an IP (Industrial Park) Zone within the Airport Environs (AE-60 &amp; AE-65) Overlay. Generally located south of Pilot Road and west of Bermuda Road within Enterprise.  MN/hw/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110386</t>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110398</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | Diamond Quail leisure development: PA-26-700018-DIAMOND QUAIL, LLC:
@@ -264,14 +261,34 @@
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110314</t>
   </si>
   <si>
+    <t xml:space="preserve">Clark County | Sustainable Development Fund 1 leisure development: PA-26-700021-SUSTAINABLE DEVELOPMENT FUND 1, LLC:
+HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Business Employment (BE) on 0.95 acres.  Generally located east of Decatur Boulevard and north of Eldorado Lane within Enterprise. MN/rk  (For possible action)</t>
+  </si>
+  <si>
+    <t>2026-07-06 | Clark County</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110272</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clark County | CITY OF LAS VEGAS: HOLDOVER PLAN AMENDMENT to redesignate the existing land use: PA-26-700022-CITY OF LAS VEGAS:
 HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Public Use (PU) to Urban Neighborhood (UN) on a 15.20 acre portion of a 31.58 acre site. Generally located south of Vegas Valley Drive and west of Tree Line Drive (alignment) within Sunrise Manor. TS/gc (For possible action)</t>
   </si>
   <si>
-    <t>2026-07-06 | Clark County</t>
-  </si>
-  <si>
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark County | Buffalo Amigos, LLC Etal &amp; Silver Serene leisure development: PA-26-700004-BUFFALO AMIGOS, LLC ETAL &amp; SILVER SERENE, LLC:
+AMENDED HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Ranch Estate Neighborhood (RN) to Low-Intensity Suburban Neighborhood (LN) on 5.10 acres (previously notified as 5.0 acres). Generally located west of Buffalo Drive and north of Torino Avenue within Enterprise.  JJ/rk (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110255</t>
+  </si>
+  <si>
+    <t>Clark County | 215 And Windmill Lane leisure development: Approve and authorize the Community Housing Administrator to nominate a 20-acre site known as APN# 177-11-401-004, a Bureau of Land Management (BLM) site reserved by the County for affordable housing located at the northeast corner of I-215 and Windmill Lane, for use as affordable housing pursuant to Section 7(b) of the Southern Nevada Public Lands Management Act; approve and authorize the Director of Real Property Management to accept conveyance of the site from the BLM, and subsequently transfer the site via quitclaim deed and disposition and development agreement to Coordinated Living of Southern Nevada for the development of affordable housing; and authorize the Director of Real Property Management, or her designee, to sign any documents related thereto (For possible action.)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110284</t>
   </si>
   <si>
     <t xml:space="preserve">Clark County | Horizon West Homes leisure development: PA-26-700017-HORIZON WEST HOMES, LLC:
@@ -281,26 +298,6 @@
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110264</t>
   </si>
   <si>
-    <t xml:space="preserve">Clark County | Buffalo Amigos, LLC Etal &amp; Silver Serene leisure development: PA-26-700004-BUFFALO AMIGOS, LLC ETAL &amp; SILVER SERENE, LLC:
-AMENDED HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Ranch Estate Neighborhood (RN) to Low-Intensity Suburban Neighborhood (LN) on 5.10 acres (previously notified as 5.0 acres). Generally located west of Buffalo Drive and north of Torino Avenue within Enterprise.  JJ/rk (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110255</t>
-  </si>
-  <si>
-    <t>Clark County | 215 And Windmill Lane leisure development: Approve and authorize the Community Housing Administrator to nominate a 20-acre site known as APN# 177-11-401-004, a Bureau of Land Management (BLM) site reserved by the County for affordable housing located at the northeast corner of I-215 and Windmill Lane, for use as affordable housing pursuant to Section 7(b) of the Southern Nevada Public Lands Management Act; approve and authorize the Director of Real Property Management to accept conveyance of the site from the BLM, and subsequently transfer the site via quitclaim deed and disposition and development agreement to Coordinated Living of Southern Nevada for the development of affordable housing; and authorize the Director of Real Property Management, or her designee, to sign any documents related thereto (For possible action.)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Sustainable Development Fund 1 leisure development: PA-26-700021-SUSTAINABLE DEVELOPMENT FUND 1, LLC:
-HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Business Employment (BE) on 0.95 acres.  Generally located east of Decatur Boulevard and north of Eldorado Lane within Enterprise. MN/rk  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110272</t>
-  </si>
-  <si>
     <t>Clark County | REFRIGERATION SUPPLIES DISTRIBUTOR: DESIGN REVIEW for a proposed: 6. DR-26-0236-REFRIGERATION SUPPLIES DISTRIBUTOR: DESIGN REVIEW for a proposed office/warehouse building on 1.91 acres in an IL (Industrial Light) Zone within the Airport Environs (AE-60) Overlay. Gen</t>
   </si>
   <si>
@@ -358,19 +355,19 @@
     <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42376#item-ha8f0435b0451</t>
   </si>
   <si>
+    <t>Las Vegas | Brandywine Bookmaking casino: 18. For possible action to approve a new Non Restricted Gaming license for BRANDYWINE BOOKMAKING LLC dba WILLIAM HILL RACE &amp; SPORTS BOOK dba PLAZA HOTEL &amp; CASINO at 1 South Main Street - Ward 5 (Summe</t>
+  </si>
+  <si>
+    <t>2026-04-15 | Las Vegas</t>
+  </si>
+  <si>
+    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h2667b1bb6acb</t>
+  </si>
+  <si>
     <t>Las Vegas | 2000 South Las Vegas Boulevard casino: 14. For possible action to approve a new Non Restricted Gaming license for WILLIAM HILL l dba WILLIAM HILL RACE &amp; SPORTS BOOK db at THE STRAT, HOTEL, CASINO &amp; TOWER at 2000 South Las Vegas Boulevard -</t>
   </si>
   <si>
-    <t>2026-04-15 | Las Vegas</t>
-  </si>
-  <si>
     <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h836f352fe1c5</t>
-  </si>
-  <si>
-    <t>Las Vegas | Brandywine Bookmaking casino: 18. For possible action to approve a new Non Restricted Gaming license for BRANDYWINE BOOKMAKING LLC dba WILLIAM HILL RACE &amp; SPORTS BOOK dba PLAZA HOTEL &amp; CASINO at 1 South Main Street - Ward 5 (Summe</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h2667b1bb6acb</t>
   </si>
   <si>
     <t>Las Vegas | WILLIAM HILL ll casino: 15. For possible action to approve a new Non Restricted Gaming license for WILLIAM HILL ll dba WILLIAM HILL RACE &amp; SPORTS BOOK dba FOUR QUEENS HOTEL AND CASINO at 202 Fremont Street - Ward 3 (Diaz) Ag</t>
@@ -835,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1081,58 +1078,58 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
@@ -1144,12 +1141,12 @@
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
@@ -1158,15 +1155,15 @@
         <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
@@ -1183,7 +1180,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -1192,49 +1189,49 @@
         <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
         <v>54</v>
       </c>
-      <c r="D27" t="s">
-        <v>55</v>
-      </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
@@ -1246,29 +1243,29 @@
         <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
         <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
@@ -1280,12 +1277,12 @@
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
@@ -1297,29 +1294,29 @@
         <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
@@ -1331,250 +1328,250 @@
         <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
         <v>69</v>
       </c>
-      <c r="D36" t="s">
-        <v>70</v>
-      </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" t="s">
         <v>74</v>
       </c>
-      <c r="D38" t="s">
-        <v>75</v>
-      </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
       </c>
       <c r="C44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" t="s">
         <v>88</v>
       </c>
-      <c r="D44" t="s">
-        <v>89</v>
-      </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
         <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="E48" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
@@ -1583,219 +1580,219 @@
         <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" t="s">
         <v>104</v>
       </c>
-      <c r="D51" t="s">
-        <v>105</v>
-      </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
         <v>16</v>
       </c>
       <c r="C56" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" t="s">
         <v>116</v>
       </c>
-      <c r="D56" t="s">
-        <v>117</v>
-      </c>
       <c r="E56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D59" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -1812,7 +1809,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
@@ -1829,7 +1826,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
@@ -1841,23 +1838,6 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" t="s">
-        <v>136</v>
-      </c>
-      <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" t="s">
         <v>14</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -19,16 +19,16 @@
     <t>Prepared for Simtec Attractions by Philip Kwong</t>
   </si>
   <si>
-    <t>Geography: Clark County, Las Vegas</t>
+    <t>Geography: Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World</t>
   </si>
   <si>
     <t>Period: July 2026</t>
   </si>
   <si>
-    <t>Filters: dormant excluded | context records included | stage: filed</t>
-  </si>
-  <si>
-    <t>Basis: 44 projects, 76 records</t>
+    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Leisure Destination | venue: Mixed-Use Development</t>
+  </si>
+  <si>
+    <t>Basis: 29 projects, 86 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -52,397 +52,290 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Clark County, Las Vegas for July 2026. It is drawn from 44 projects and 76 captured records. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 29 projects and 86 captured records. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>What moved</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>OCVibe: filed to approved</t>
+  </si>
+  <si>
+    <t>2026-07-13 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
     <t>Headline finds</t>
   </si>
   <si>
-    <t>RECORD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nevada Palace resort: PA-26-700023-NEVADA PALACE, LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Entertainment Mixed-Use (EM) to Compact Neighborhood (CN) on 29.46 acres. Generally located northeast of Boulder Highway and southeast of Harmon Avenue within Sunrise Manor and Whitney. JG/gc (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-08-04 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110561</t>
+    <t>OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
   </si>
   <si>
     <t>PRESS</t>
   </si>
   <si>
-    <t>Top Gun Las Vegas: Top Gun Vegas Locks South Strip Site at 4815 Las Vegas ...</t>
-  </si>
-  <si>
-    <t>2026-07-26 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://deeparrival.com/news/top-gun-vegas-south-strip-site-july-2026/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Southern Highlands Golf Club leisure development: UC-26-0350-SOUTHERN HIGHLANDS GOLF CLUB:
-USE PERMITS for the following: 1) multi-family residential development; 2) modified development standards.
-DESIGN REVIEW for a multi-family residential development in conjunction with an existing golf course on a 1.7 acre portion of 8.05 acres in a C-2 (General Commercial District) Zone within the Southern Highlands Planned Community (PCO) Overlay.  Generally located north of Robert Trent Jones Lane and west of Southern Highlands Parkway within Enterprise.  JJ/bb/kh  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visible Noise family entertainment centre: UC-26-0303-VISIBLE NOISE, LLC:
-HOLDOVER USE PERMIT for a proposed recreational or entertainment facility within an existing office/warehouse complex on a portion of 5.31 acres in an IP (Industrial Park) Zone within the Airport Environs (AE-60) Overlay. Generally located west of Tenaya Way and north of Sunset Road within Spring Valley.  MN/rp/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-08-03 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tropicana Land resort: WS-26-0113-TROPICANA LAND, LLC:
-HOLDOVER WAIVER OF DEVELOPMENT STANDARDS for modified driveway geometrics.
-DESIGN REVIEW for a resort hotel on a 26.11 acre portion of 35.11 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay. Generally located south of Tropicana Avenue and east of Las Vegas Boulevard South within Paradise.  JG/nm/kh  (For possible action)</t>
+    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>2026-07-24 | Clark County</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weston Urban leisure development: Discussion and possible action to authorize execution of a Master Economic Incentive Agreement between Weston Urban, LLC and the City of San Antonio as a source of funding for public improvements related to the redevelopment of the property located at 322 W. Commerce, for an amount up to $250,000.
+</t>
+  </si>
+  <si>
+    <t>2021-09-20 | San Antonio</t>
+  </si>
+  <si>
+    <t>https://sanantonio.legistar.com/gateway.aspx?M=l&amp;ID=43966</t>
+  </si>
+  <si>
+    <t>World Buddhism Association Headquarters &amp; MGM-Grand Bally's integrated resort: 4. AR-26-400041 (UC-25-0544)-WORLD BUDDHISM ASSOCIATION HEADQUARTERS &amp; MGM-GRAND BALLY'S, LLC LEASE: USE PERMIT FIRST APPLICATION FOR REVIEW for a recreational or entertainment facility. DESIGN REVIEW</t>
+  </si>
+  <si>
+    <t>2026-07-14 | Clark County</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:35f66646-63c2-45e2-8052-2833536974fb/original/as/Winchester-Agenda-071426.pdf#item-ar-26-400041+uc-25-0544</t>
+  </si>
+  <si>
+    <t>Toll South LV leisure development: ORD-26-900159: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Toll South LV LLC for a single-family residential subdivision on 0.89 acres, generally located east of Hinson Street and north of Silverado Ranch Boulevard within Enterprise. JJ/tpd (For possible action)</t>
   </si>
   <si>
     <t>2026-07-21 | Clark County</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110434</t>
-  </si>
-  <si>
-    <t>multifamily and mixed-use development that includes a residential component as: 40. Bill No. 2026-16 - For possible action - Authorizes multifamily and mixed-use development that includes a residential component as a conditional use on property zoned for commercial use, in accord</t>
-  </si>
-  <si>
-    <t>2026-05-20 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42386#item-ha228cfd5c1c1</t>
-  </si>
-  <si>
-    <t>163 At Casino Drive casino: Approve and authorize the Chair to sign Supplemental No. 8 to the interlocal contract between Clark County and Regional Flood Control District to extend the contract term for design of the State Route 163 at Casino Drive project.  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Decatur Holding CO leisure development: PA-26-700010-SOUTH DECATUR HOLDING CO., LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 2.64 acres.  Generally located east of Decatur Boulevard and south of Moberly Avenue (alignment) within Enterprise. MN/rk (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G D Carden Entertainment museum: ET-26-400054 (UC-25-0072)-GD CARDEN ENTERTAINMENT, LLC:
-USE PERMITS FIRST EXTENSION OF TIME for the following: 1) recreational or entertainment facility; 2) museum; and 3) live entertainment. 
-WAIVERS OF DEVELOPMENT STANDARDS for the following: 1) eliminate and reduce setbacks; 2) reduce parking requirements; 3) waive full off-site improvements; 4) reduce driveway approach distance; 5) reduce driveway departure distance; and 6) reduce driveway width.
-DESIGN REVIEW for a recreational or entertainment facility and museum on 1.82 acres in an RS20 (Residential Single-Family 20) Zone within a Historic Designation (HDO) Overlay.  Generally located north of Vegas Drive and west of Valley Drive within the Lone Mountain Planning Area.  WM/rr/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shamaim Henderson family entertainment centre: UC-26-0309-SHAMAIM HENDERSON, LLC:
-USE PERMITS for the following: 1) an avocational or vocational training facility; and 2) a recreational or entertainment facility on a portion of 5.11 acres in an IL (Industrial Light) Zone and an IP (Industrial Park) Zone within the Airport Environs (AE-60 &amp; AE-65) Overlay. Generally located south of Pilot Road and west of Bermuda Road within Enterprise.  MN/hw/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-07-20 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110386</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110431</t>
+  </si>
+  <si>
+    <t>BDA South leisure development: ORD-26-900280: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with BDA South, LLC for a vehicle wash on 1.08 acres, generally located north of Wigwam Avenue and east of Arville Street within Enterprise. JJ/tpd (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110432</t>
+  </si>
+  <si>
+    <t>12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
+  </si>
+  <si>
+    <t>2026-08-03 | Nashville</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20788</t>
+  </si>
+  <si>
+    <t>to authorize building material restrictions and requirements for BL2026-1474: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from IR to SP zoning for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001).</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
+DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110419</t>
   </si>
   <si>
     <t>By market</t>
   </si>
   <si>
-    <t>Clark County | LV Warm Springs by its General Partner LV Warm Springs LV leisure development: ORD-26-900492: Introduce an ordinance to consider adoption of a Development Agreement with LV Warm Springs by its’ General Partner LV Warm Springs  LV Warm Springs CP LLC by Flex GP holding Corp Owner for a warehouse and distribution center on 6.47 acres, generally located west of Tenaya Way and south of Arby Avenue within Spring Valley. MN/rp (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110572</t>
-  </si>
-  <si>
-    <t>Clark County | HD Oleta leisure development: ORD-26-900429: Introduce an ordinance to consider adoption of a Development Agreement with HD OLETA LLC and LAS VEGAS PAVING CORP for an office/warehouse complex on 9.67 acres, generally located south of Oleta Avenue and west of Jones Boulevard within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Nevada Palace resort: PA-26-700023-NEVADA PALACE, LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Entertainment Mixed-Use (EM) to Compact Neighborhood (CN) on 29.46 acres. Generally located northeast of Boulder Highway and southeast of Harmon Avenue within Sunrise Manor and Whitney. JG/gc (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Southern Highlands Golf Club leisure development: UC-26-0350-SOUTHERN HIGHLANDS GOLF CLUB:
-USE PERMITS for the following: 1) multi-family residential development; 2) modified development standards.
-DESIGN REVIEW for a multi-family residential development in conjunction with an existing golf course on a 1.7 acre portion of 8.05 acres in a C-2 (General Commercial District) Zone within the Southern Highlands Planned Community (PCO) Overlay.  Generally located north of Robert Trent Jones Lane and west of Southern Highlands Parkway within Enterprise.  JJ/bb/kh  (For possible action)</t>
-  </si>
-  <si>
-    <t>Clark County | 163 At Casino Drive casino: Approve and authorize the Chair to sign Supplemental No. 8 to the interlocal contract between Clark County and Regional Flood Control District to extend the contract term for design of the State Route 163 at Casino Drive project.  (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Visible Noise family entertainment centre: UC-26-0303-VISIBLE NOISE, LLC:
-HOLDOVER USE PERMIT for a proposed recreational or entertainment facility within an existing office/warehouse complex on a portion of 5.31 acres in an IP (Industrial Park) Zone within the Airport Environs (AE-60) Overlay. Generally located west of Tenaya Way and north of Sunset Road within Spring Valley.  MN/rp/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>Clark County | Hilton Resorts resort: 3. UC-26-0373-HILTON RESORTS CORPORATION: USE PERMIT for a monorail on approximately 21 acres in an RM50 (Residential Multi-Family 50) Zone, a CR (Commercial Resort) Zone, and an IL (Industrial Light)</t>
+    <t>Phoenix | Rezoning Application Z-15-26-2 - Southwest Corner of 56th Street and Ranger: Public Hearing and Ordinance Adoption - Rezoning Application Z-15-26-2 - Southwest Corner of 56th Street and Ranger Drive (Ordinance G-7525) - District 2</t>
+  </si>
+  <si>
+    <t>2026-06-30 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35401</t>
+  </si>
+  <si>
+    <t>Phoenix | North Phoenix Growers, LLC et. al leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-25-26-1-2 - Approximately 430 Feet South of the Southeast Corner of 19th Avenue and Jomax Road (Ordinance G-7529) - Districts 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35400</t>
+  </si>
+  <si>
+    <t>Phoenix | Children's Museum of Phoenix: Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35482</t>
+  </si>
+  <si>
+    <t>Phoenix | Woodland Plaza, LLC, et.al leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-145-24-1 - Approximately 200 Feet North of the Northwest Corner of 35th Avenue and Bell Road (Ordinance G-7528) - District 1</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35398</t>
+  </si>
+  <si>
+    <t>Phoenix | Randy Raskin, 43rd Ave leisure development: Amend City Code - Ordinance Adoption - Rezoning Application PHO-1-26--Z-29-23-7(8) - Approximately 300 Feet East of the Northeast Corner of 43rd Avenue and Baseline Road (Ordinance G-7531) - District 8</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35415</t>
+  </si>
+  <si>
+    <t>Phoenix | Larry Miller, Matrix at Dobbins leisure development: Amend City Code - Ordinance Adoption - Rezoning Application PHO-1-26--Z-45-22-8 - Southeast Corner of 59th Avenue and Dobbins Road (Ordinance G-7532) - District 8</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35416</t>
+  </si>
+  <si>
+    <t>Phoenix | VTHQ leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-27-26-8 - Southwest Corner of 14th Street and Hess Avenue (Ordinance G-7530) - District 8</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35403</t>
+  </si>
+  <si>
+    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>2026-06-16 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
+  </si>
+  <si>
+    <t>Phoenix | Laveen Baseline leisure development: Amend Ordinance S-47581 and Development Agreement (City Contract 157059) with Laveen Baseline LLC (Ordinance S-53031) - Districts 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35236</t>
+  </si>
+  <si>
+    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
+  </si>
+  <si>
+    <t>2026-05-19 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
+  </si>
+  <si>
+    <t>Clark County | Club 36 Master Association integrated resort: 4. UC-26-0383-BG CLUB 36 MASTER ASSOCIATION: USE PERMIT for a monorail on approximately 80 acres in a CR (Commercial Resort) Zone and a CG (Commercial General) Zone within the Airport Environs (AE-60,</t>
   </si>
   <si>
     <t>2026-07-28 | Clark County</t>
   </si>
   <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-uc-26-0373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Buona Vita resort: 2. AR-26-400068 (ET-25-400074(UC-23-0659))-BUONA VITA, LLC: USE PERMIT FIRST APPLICATION FOR REVIEW for daycare and school. WAIVERS OF DEVELOPMENT STANDARDS for the following: 1) trash enclosure; and </t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-ar-26-400068+et-25-400074+uc-23-0659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Tropicana Land resort: WS-26-0113-TROPICANA LAND, LLC:
-HOLDOVER WAIVER OF DEVELOPMENT STANDARDS for modified driveway geometrics.
-DESIGN REVIEW for a resort hotel on a 26.11 acre portion of 35.11 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay. Generally located south of Tropicana Avenue and east of Las Vegas Boulevard South within Paradise.  JG/nm/kh  (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | South Decatur Holding CO leisure development: PA-26-700010-SOUTH DECATUR HOLDING CO., LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 2.64 acres.  Generally located east of Decatur Boulevard and south of Moberly Avenue (alignment) within Enterprise. MN/rk (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Church Searchlight Community leisure development: PA-26-700019-CHURCH SEARCHLIGHT COMMUNITY:
-PLAN AMENDMENT to redesignate the existing land use category from Public Use (PU) to Neighborhood commercial (NC) on 4.8 acres.   Generally located west of US Highway 95 and north of State Route 164 within Searchlight. MN/rk  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | G D Carden Entertainment museum: ET-26-400054 (UC-25-0072)-GD CARDEN ENTERTAINMENT, LLC:
-USE PERMITS FIRST EXTENSION OF TIME for the following: 1) recreational or entertainment facility; 2) museum; and 3) live entertainment. 
-WAIVERS OF DEVELOPMENT STANDARDS for the following: 1) eliminate and reduce setbacks; 2) reduce parking requirements; 3) waive full off-site improvements; 4) reduce driveway approach distance; 5) reduce driveway departure distance; and 6) reduce driveway width.
-DESIGN REVIEW for a recreational or entertainment facility and museum on 1.82 acres in an RS20 (Residential Single-Family 20) Zone within a Historic Designation (HDO) Overlay.  Generally located north of Vegas Drive and west of Valley Drive within the Lone Mountain Planning Area.  WM/rr/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Beltway 101, LLC &amp; Blue 10 leisure development: PA-26-700025-BELTWAY 101, LLC &amp; BLUE 10, LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Compact Neighborhood (CN) on 4.51 acres. Generally located north of Blue Diamond Road and west of Montessouri Street (alignment) within Enterprise. JJ/gc (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Shamaim Henderson family entertainment centre: UC-26-0309-SHAMAIM HENDERSON, LLC:
-USE PERMITS for the following: 1) an avocational or vocational training facility; and 2) a recreational or entertainment facility on a portion of 5.11 acres in an IL (Industrial Light) Zone and an IP (Industrial Park) Zone within the Airport Environs (AE-60 &amp; AE-65) Overlay. Generally located south of Pilot Road and west of Bermuda Road within Enterprise.  MN/hw/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | BOLOGNESE, JOSEPH &amp; VIVI A: PLAN AMENDMENT to redesignate the existing land use: PA-26-700026-BOLOGNESE, JOSEPH &amp; VIVI A:
-PLAN AMENDMENT to redesignate the existing land use category from Corridor Mixed-Use (CM) to Compact Neighborhood (CN) on 1.93 acres.  Generally located north of Serene Avenue and east of Grand Canyon Drive within Enterprise. JJ/rk (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Diamond Quail leisure development: PA-26-700018-DIAMOND QUAIL, LLC:
-PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Business Employment (BE) on 1.24 acres.   Generally located north of Quail Avenue and east of Santa Margarita Street (alignment) within Spring Valley. MN/gc (For possible action)</t>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-uc-26-0383</t>
+  </si>
+  <si>
+    <t>Clark County | Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark County | Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
+DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
+  </si>
+  <si>
+    <t>Clark County | Toll South LV leisure development: ORD-26-900159: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Toll South LV LLC for a single-family residential subdivision on 0.89 acres, generally located east of Hinson Street and north of Silverado Ranch Boulevard within Enterprise. JJ/tpd (For possible action)</t>
+  </si>
+  <si>
+    <t>Clark County | BDA South leisure development: ORD-26-900280: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with BDA South, LLC for a vehicle wash on 1.08 acres, generally located north of Wigwam Avenue and east of Arville Street within Enterprise. JJ/tpd (For possible action)</t>
+  </si>
+  <si>
+    <t>Clark County | World Buddhism Association Headquarters &amp; MGM-Grand Bally's integrated resort: 4. AR-26-400041 (UC-25-0544)-WORLD BUDDHISM ASSOCIATION HEADQUARTERS &amp; MGM-GRAND BALLY'S, LLC LEASE: USE PERMIT FIRST APPLICATION FOR REVIEW for a recreational or entertainment facility. DESIGN REVIEW</t>
+  </si>
+  <si>
+    <t>Clark County | ZL II leisure development: ORD-26-900259: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with ZL II, LLC for an avocational or vocational training facility and parking lot expansion on 12.04 acres, generally located east of El Camino Road and north of Rafael Rivera Way within Enterprise. MN/jl (For possible action)</t>
   </si>
   <si>
     <t>2026-07-07 | Clark County</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | RDXNWP family entertainment centre: UC-26-0302-RDXNWP, LLC:
-USE PERMIT to allow outdoor storage. 
-WAIVERS OF DEVELOPMENT STANDARDS for the following: 1) eliminate electric vehicle charging spaces; and 2) modified driveway geometrics.
-DESIGN REVIEW for a proposed recreational and entertainment facility (ice rink) within an existing shopping center on a 7.02 acre portion of 10.85 acres in a CG (Commercial General) Zone within the Airport Environs (AE-60) Overlay. Generally located south of Russell Road and west of Decatur Boulevard within Spring Valley.  MN/bb/kh  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Sustainable Development Fund 1 leisure development: PA-26-700021-SUSTAINABLE DEVELOPMENT FUND 1, LLC:
-HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Neighborhood Commercial (NC) to Business Employment (BE) on 0.95 acres.  Generally located east of Decatur Boulevard and north of Eldorado Lane within Enterprise. MN/rk  (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-07-06 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | CITY OF LAS VEGAS: HOLDOVER PLAN AMENDMENT to redesignate the existing land use: PA-26-700022-CITY OF LAS VEGAS:
-HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Public Use (PU) to Urban Neighborhood (UN) on a 15.20 acre portion of a 31.58 acre site. Generally located south of Vegas Valley Drive and west of Tree Line Drive (alignment) within Sunrise Manor. TS/gc (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Buffalo Amigos, LLC Etal &amp; Silver Serene leisure development: PA-26-700004-BUFFALO AMIGOS, LLC ETAL &amp; SILVER SERENE, LLC:
-AMENDED HOLDOVER PLAN AMENDMENT to redesignate the existing land use category from Ranch Estate Neighborhood (RN) to Low-Intensity Suburban Neighborhood (LN) on 5.10 acres (previously notified as 5.0 acres). Generally located west of Buffalo Drive and north of Torino Avenue within Enterprise.  JJ/rk (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110255</t>
-  </si>
-  <si>
-    <t>Clark County | 215 And Windmill Lane leisure development: Approve and authorize the Community Housing Administrator to nominate a 20-acre site known as APN# 177-11-401-004, a Bureau of Land Management (BLM) site reserved by the County for affordable housing located at the northeast corner of I-215 and Windmill Lane, for use as affordable housing pursuant to Section 7(b) of the Southern Nevada Public Lands Management Act; approve and authorize the Director of Real Property Management to accept conveyance of the site from the BLM, and subsequently transfer the site via quitclaim deed and disposition and development agreement to Coordinated Living of Southern Nevada for the development of affordable housing; and authorize the Director of Real Property Management, or her designee, to sign any documents related thereto (For possible action.)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Horizon West Homes leisure development: PA-26-700017-HORIZON WEST HOMES, LLC:
-HOLDOVER PLAN AMENDMENT to redesignate the land use category from Mid-Intensity Suburban Neighborhood (MN) to Compact Neighborhood (CN) on 1.44 acres.  Generally located east of Hualapai Way and north of Serene Avenue within Enterprise.  JJ/rk  (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110264</t>
-  </si>
-  <si>
-    <t>Clark County | REFRIGERATION SUPPLIES DISTRIBUTOR: DESIGN REVIEW for a proposed: 6. DR-26-0236-REFRIGERATION SUPPLIES DISTRIBUTOR: DESIGN REVIEW for a proposed office/warehouse building on 1.91 acres in an IL (Industrial Light) Zone within the Airport Environs (AE-60) Overlay. Gen</t>
-  </si>
-  <si>
-    <t>2026-05-12 | Clark County</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:d8194047-38e8-4588-b3c6-cfb5682e7f84/original/as/Paradise-Minutes-051226.pdf#item-dr-26-0236</t>
-  </si>
-  <si>
-    <t>Clark County | LV Diamond Property I resort: 6. AR-26-400027 (UC-22-0556)-LV DIAMOND PROPERTY I, LLC: WAIVER OF DEVELOPMENT STANDARDS SECOND APPLICATION FOR REVIEW to eliminate street landscaping for an existing racetrack, recreational facility,</t>
-  </si>
-  <si>
-    <t>2026-04-28 | Clark County</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:f1a4b305-a7fb-49f7-a5fe-06ab39312955/original/as/Paradise-Minutes-042826.pdf#item-ar-26-400027+uc-22-0556</t>
-  </si>
-  <si>
-    <t>Clark County | MGM Resorts Festival Grounds museum: 8. VS-26-0213-MGM RESORTS FESTIVAL GROUNDS, LLC: VACATE AND ABANDON easements of interest to Clark County located between Reno Avenue and Mandalay Bay Road, and Giles Street and Las Vegas Boulevard So</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:f1a4b305-a7fb-49f7-a5fe-06ab39312955/original/as/Paradise-Minutes-042826.pdf#item-vs-26-0213</t>
-  </si>
-  <si>
-    <t>Las Vegas | Top Gun Las Vegas: Top Gun Vegas Locks South Strip Site at 4815 Las Vegas ...</t>
-  </si>
-  <si>
-    <t>Las Vegas | Plaza Hotel &amp; Casino casino: 14. For possible action to approve the ratification of the Commission for the Las Vegas Centennial funding allocation to be used for the planning and running of the 2027, 2028, and 2029 Las Vegas Days</t>
-  </si>
-  <si>
-    <t>2026-07-01 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42864#item-h34a32883beda</t>
-  </si>
-  <si>
-    <t>Las Vegas | possible action to approve the ratification of the Commission for the Las Vegas: 11. For possible action to approve the ratification of the Commission for the Las Vegas Centennial award of $160,000 to the Neon Museum for the costs associated with the planning and running of a four</t>
-  </si>
-  <si>
-    <t>2026-06-03 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42406#item-h437a333ac173</t>
-  </si>
-  <si>
-    <t>Las Vegas | multifamily and mixed-use development that includes a residential component as: 40. Bill No. 2026-16 - For possible action - Authorizes multifamily and mixed-use development that includes a residential component as a conditional use on property zoned for commercial use, in accord</t>
-  </si>
-  <si>
-    <t>Las Vegas | various provisions of LVMC Title 19 to establish the Transit Oriented: 36. Bill No. 2026-13 - For possible action - Amends various provisions of LVMC Title 19 to establish the Transit Oriented Development Overlay District and make parallel adjustments. Sponsored by: Coun</t>
-  </si>
-  <si>
-    <t>2026-05-06 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42376#item-ha8f0435b0451</t>
-  </si>
-  <si>
-    <t>Las Vegas | Brandywine Bookmaking casino: 18. For possible action to approve a new Non Restricted Gaming license for BRANDYWINE BOOKMAKING LLC dba WILLIAM HILL RACE &amp; SPORTS BOOK dba PLAZA HOTEL &amp; CASINO at 1 South Main Street - Ward 5 (Summe</t>
-  </si>
-  <si>
-    <t>2026-04-15 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h2667b1bb6acb</t>
-  </si>
-  <si>
-    <t>Las Vegas | 2000 South Las Vegas Boulevard casino: 14. For possible action to approve a new Non Restricted Gaming license for WILLIAM HILL l dba WILLIAM HILL RACE &amp; SPORTS BOOK db at THE STRAT, HOTEL, CASINO &amp; TOWER at 2000 South Las Vegas Boulevard -</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h836f352fe1c5</t>
-  </si>
-  <si>
-    <t>Las Vegas | WILLIAM HILL ll casino: 15. For possible action to approve a new Non Restricted Gaming license for WILLIAM HILL ll dba WILLIAM HILL RACE &amp; SPORTS BOOK dba FOUR QUEENS HOTEL AND CASINO at 202 Fremont Street - Ward 3 (Diaz) Ag</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-ha1a186745a91</t>
-  </si>
-  <si>
-    <t>Las Vegas | 221 North Rampart Boulevard casino: 19. For possible action to approve a new Non Restricted Gaming license for WILLIAM HILL1 dba CAESARS SPORTSBOOK db at THE RESORT AT SUMMERLIN at 221 North Rampart Boulevard - Ward 2 (Kelley) Agenda Su</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42356#item-h2fea74770792</t>
-  </si>
-  <si>
-    <t>Las Vegas | Fifth Street Gaming casino: 10. For possible action to approve a One-Day Opening for a Non-Restricted Gaming license for FIFTH STREET GAMING LLC dba FIFTH STREET GAMING LLC db at WESTERN HOTEL &amp; CASINO at 899 Fremont Street - Wa</t>
-  </si>
-  <si>
-    <t>2026-03-18 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42326#item-h28eb1d558fc2</t>
-  </si>
-  <si>
-    <t>Las Vegas | 000 For The Maryland Parkway leisure development: 25. For possible action to approve Supplemental No. 6 to Interlocal Contract 1164 between the Cities of Las Vegas (CLV), North Las Vegas, Henderson, Boulder City and Mesquite, Clark County, and the Re</t>
-  </si>
-  <si>
-    <t>2026-01-21 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42256#item-hfcc9035cbd00</t>
-  </si>
-  <si>
-    <t>Las Vegas | Proview Series 39 casino: 15. For possible action to approve a Parking Lease Agreement between Proview Series 39, LLC, and the City of Las Vegas (City) where the City will manage and operate a fifty-nine (59) space parking lot</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42256#item-h70b1f823b194</t>
-  </si>
-  <si>
-    <t>Las Vegas | KLA Capital Series 7 casino: 16. For possible action to approve a Parking Lease Agreement between KLA Capital Series 7, LLC, and the City of Las Vegas (City) where the City will manage and operate a nineteen (19) space parking lo</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42256#item-he8c543b347e4</t>
-  </si>
-  <si>
-    <t>Las Vegas | Nevada Test Site Historical Foundation museum: 11. For possible action to approve the ratification of the Commission for the Las Vegas Centennial funding allocation for the creation and installation of a permanent educational museum exhibit and to</t>
-  </si>
-  <si>
-    <t>2026-01-07 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42246#item-h2e63d4603e2f</t>
-  </si>
-  <si>
-    <t>Las Vegas | 2427 South Las Vegas Boulevard casino: 12. For possible action to approve a One-Day Opening for a Non-Restricted Gaming License for UNITED COIN MACHINE dba CENTURY GAMING TECHNOLOGIES db at HOLY COW! CASINO CAFE at 2427 South Las Vegas Bou</t>
-  </si>
-  <si>
-    <t>2025-12-17 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=42132#item-h9540a7706bbe</t>
-  </si>
-  <si>
-    <t>Las Vegas | possible action to approve the Third Amendment to Lease and Operating Agreement: 18. For possible action to approve the Third Amendment to Lease and Operating Agreement between The Smith Center for Performing Arts and the City of Las Vegas (City) where the parking facility informa</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110310</t>
+  </si>
+  <si>
+    <t>Clark County | Cimarron Spring Deux LLC, A &amp; A Revocable Living Trust leisure development: ORD-26-900221: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Cimarron Spring Deux LLC, A &amp; A Revocable Living Trust, and A &amp; A III LLC for a single-family development on 2.54 acres, generally located west of Hinson Street and south of Richmar Avenue within Enterprise. JJ/tpd (For possible action)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110308</t>
+  </si>
+  <si>
+    <t>Clark County | Ruby Holdings museum: 5. UC-26-0156-RUBY HOLDINGS, LLC: USE PERMITS for the following: 1) museum; and 2) office as a primary use. WAIVER OF DEVELOPMENT STANDARDS to reduce parking. DESIGN REVIEW for a proposed museum in co</t>
+  </si>
+  <si>
+    <t>2026-04-14 | Clark County</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+  </si>
+  <si>
+    <t>Nashville | 12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
+  </si>
+  <si>
+    <t>Nashville | amending Chapter 17.08 of the Metropolitan Code of Laws to modify the Zoning: An ordinance amending Chapter 17.08 of the Metropolitan Code of Laws to modify the Zoning District Land Use Table to reflect recent amendments to the Zoning Code (Proposal No. 2026Z-014-TX-001).</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20861</t>
+  </si>
+  <si>
+    <t>Nashville | approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1: An ordinance approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1 to the Bordeaux Redevelopment Plan, Amendment No. 1 to the Central State Redevelopment Plan, Amendment No. 6 to the Phillips-Jackson Redevelopment Plan, Amendment No. 9 to the Rutledge Hill Redevelopment Plan, and Amendment No. 1 to the Skyline Redevelopment Plan. (Proposal No. 2026M-002OT-001)</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20850</t>
+  </si>
+  <si>
+    <t>Nashville | to authorize building material restrictions and requirements for BL2026-1474: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from IR to SP zoning for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001).</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | 10450 Turkey Lake Road leisure development: Contract between CFTOD and Tower Engineering Inc. approved by the Board at the November 21, 2025, meeting</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-9.1-p276</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
+  </si>
+  <si>
+    <t>Anaheim | OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
+  </si>
+  <si>
+    <t>Las Vegas | 500 North Casino Center Drive casino: 24. For possible action to approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization, located at 500 North Casino Center Drive - Depa</t>
   </si>
   <si>
     <t>2025-10-15 | Las Vegas</t>
   </si>
   <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-h511ab179299a</t>
+    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
+  </si>
+  <si>
+    <t>Bonita Springs | 8910 Terrene Ct leisure development: Bonita Bay Lake 21 Restoration (250609-53694_36-114553-P)</t>
+  </si>
+  <si>
+    <t>2025-10-14 | Bonita Springs</t>
+  </si>
+  <si>
+    <t>https://www.sfwmd.gov/regpermitting#erp-250609-53694_36-114553-P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio | Weston Urban leisure development: Discussion and possible action to authorize execution of a Master Economic Incentive Agreement between Weston Urban, LLC and the City of San Antonio as a source of funding for public improvements related to the redevelopment of the property located at 322 W. Commerce, for an amount up to $250,000.
+</t>
   </si>
   <si>
     <t>Coverage note</t>
   </si>
   <si>
-    <t>Coverage is limited to Clark County, Las Vegas. Projects outside it exist in our register and are not reported here.</t>
+    <t>Coverage is limited to Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World. Projects outside it exist in our register and are not reported here.</t>
   </si>
   <si>
     <t>The period is July 2026. Activity outside it is not included even where it concerns the same project.</t>
@@ -832,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -925,919 +818,732 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
         <v>37</v>
       </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
         <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
         <v>50</v>
       </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
         <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="s">
-        <v>118</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" t="s">
-        <v>116</v>
-      </c>
-      <c r="E57" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="s">
-        <v>125</v>
-      </c>
-      <c r="D59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E59" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="s">
-        <v>128</v>
-      </c>
-      <c r="D60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>132</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>131</v>
-      </c>
-      <c r="B62" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" t="s">
-        <v>133</v>
-      </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" t="s">
         <v>14</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="93">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -25,10 +25,10 @@
     <t>Period: July 2026</t>
   </si>
   <si>
-    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Leisure Destination | venue: Mixed-Use Development</t>
-  </si>
-  <si>
-    <t>Basis: 29 projects, 86 records</t>
+    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
+  </si>
+  <si>
+    <t>Basis: 16 projects, 74 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -52,7 +52,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 29 projects and 86 captured records. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 16 projects and 74 captured records. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t/>
@@ -82,6 +82,12 @@
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
   </si>
   <si>
+    <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
+  </si>
+  <si>
     <t>PRESS</t>
   </si>
   <si>
@@ -94,47 +100,58 @@
     <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
   </si>
   <si>
-    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
+    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
+  </si>
+  <si>
+    <t>2026-07-27 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
   </si>
   <si>
     <t>2026-01-23 | Central Florida Tourism Oversight District</t>
   </si>
   <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weston Urban leisure development: Discussion and possible action to authorize execution of a Master Economic Incentive Agreement between Weston Urban, LLC and the City of San Antonio as a source of funding for public improvements related to the redevelopment of the property located at 322 W. Commerce, for an amount up to $250,000.
-</t>
-  </si>
-  <si>
-    <t>2021-09-20 | San Antonio</t>
-  </si>
-  <si>
-    <t>https://sanantonio.legistar.com/gateway.aspx?M=l&amp;ID=43966</t>
-  </si>
-  <si>
-    <t>World Buddhism Association Headquarters &amp; MGM-Grand Bally's integrated resort: 4. AR-26-400041 (UC-25-0544)-WORLD BUDDHISM ASSOCIATION HEADQUARTERS &amp; MGM-GRAND BALLY'S, LLC LEASE: USE PERMIT FIRST APPLICATION FOR REVIEW for a recreational or entertainment facility. DESIGN REVIEW</t>
-  </si>
-  <si>
-    <t>2026-07-14 | Clark County</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:35f66646-63c2-45e2-8052-2833536974fb/original/as/Winchester-Agenda-071426.pdf#item-ar-26-400041+uc-25-0544</t>
-  </si>
-  <si>
-    <t>Toll South LV leisure development: ORD-26-900159: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Toll South LV LLC for a single-family residential subdivision on 0.89 acres, generally located east of Hinson Street and north of Silverado Ranch Boulevard within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-07-21 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110431</t>
-  </si>
-  <si>
-    <t>BDA South leisure development: ORD-26-900280: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with BDA South, LLC for a vehicle wash on 1.08 acres, generally located north of Wigwam Avenue and east of Arville Street within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110432</t>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
+  </si>
+  <si>
+    <t>2026-01-12 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
+  </si>
+  <si>
+    <t>2026-06-22 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
   </si>
   <si>
     <t>12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
@@ -146,7 +163,13 @@
     <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20788</t>
   </si>
   <si>
-    <t>to authorize building material restrictions and requirements for BL2026-1474: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from IR to SP zoning for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001).</t>
+    <t xml:space="preserve">   An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County...</t>
+  </si>
+  <si>
+    <t>Specific Plan Zoning District: An ordinance to authorize building material restrictions and requirements for BL2026-1474, a proposed Specific Plan Zoning District for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001). THE PROPOSED ORDINANCE REQUIRES CERTAIN MATERIALS TO BE RESTRICTED IN THE CONSTRUCTION OF BUILDINGS.</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20783</t>
   </si>
   <si>
     <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20782</t>
@@ -156,88 +179,55 @@
 DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
   </si>
   <si>
+    <t>2026-07-21 | Clark County</t>
+  </si>
+  <si>
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110419</t>
   </si>
   <si>
+    <t>Children's Museum of Phoenix: Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>2026-06-30 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
+  </si>
+  <si>
     <t>By market</t>
   </si>
   <si>
-    <t>Phoenix | Rezoning Application Z-15-26-2 - Southwest Corner of 56th Street and Ranger: Public Hearing and Ordinance Adoption - Rezoning Application Z-15-26-2 - Southwest Corner of 56th Street and Ranger Drive (Ordinance G-7525) - District 2</t>
-  </si>
-  <si>
-    <t>2026-06-30 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35401</t>
-  </si>
-  <si>
-    <t>Phoenix | North Phoenix Growers, LLC et. al leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-25-26-1-2 - Approximately 430 Feet South of the Southeast Corner of 19th Avenue and Jomax Road (Ordinance G-7529) - Districts 1 &amp; 2</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35400</t>
-  </si>
-  <si>
-    <t>Phoenix | Children's Museum of Phoenix: Children's Museum of Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35482</t>
-  </si>
-  <si>
-    <t>Phoenix | Woodland Plaza, LLC, et.al leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-145-24-1 - Approximately 200 Feet North of the Northwest Corner of 35th Avenue and Bell Road (Ordinance G-7528) - District 1</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35398</t>
-  </si>
-  <si>
-    <t>Phoenix | Randy Raskin, 43rd Ave leisure development: Amend City Code - Ordinance Adoption - Rezoning Application PHO-1-26--Z-29-23-7(8) - Approximately 300 Feet East of the Northeast Corner of 43rd Avenue and Baseline Road (Ordinance G-7531) - District 8</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35415</t>
-  </si>
-  <si>
-    <t>Phoenix | Larry Miller, Matrix at Dobbins leisure development: Amend City Code - Ordinance Adoption - Rezoning Application PHO-1-26--Z-45-22-8 - Southeast Corner of 59th Avenue and Dobbins Road (Ordinance G-7532) - District 8</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35416</t>
-  </si>
-  <si>
-    <t>Phoenix | VTHQ leisure development: Amend City Code - Ordinance Adoption - Rezoning Application Z-27-26-8 - Southwest Corner of 14th Street and Hess Avenue (Ordinance G-7530) - District 8</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35403</t>
-  </si>
-  <si>
-    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>2026-06-16 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
-  </si>
-  <si>
-    <t>Phoenix | Laveen Baseline leisure development: Amend Ordinance S-47581 and Development Agreement (City Contract 157059) with Laveen Baseline LLC (Ordinance S-53031) - Districts 7 &amp; 8</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35236</t>
-  </si>
-  <si>
-    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
-  </si>
-  <si>
-    <t>2026-05-19 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
-  </si>
-  <si>
-    <t>Clark County | Club 36 Master Association integrated resort: 4. UC-26-0383-BG CLUB 36 MASTER ASSOCIATION: USE PERMIT for a monorail on approximately 80 acres in a CR (Commercial Resort) Zone and a CG (Commercial General) Zone within the Airport Environs (AE-60,</t>
-  </si>
-  <si>
-    <t>2026-07-28 | Clark County</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:7592f7a2-1607-4db1-84fd-1e20f3737ec6/original/as/Winchester-Agenda-072826.pdf#item-uc-26-0383</t>
+    <t>Anaheim | Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
+  </si>
+  <si>
+    <t>Anaheim | OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaheim | Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
+  </si>
+  <si>
+    <t>Anaheim | OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaheim | 10 To The Beach Boulevard theme park: ITEM NO. 3 DEVELOPMENT APPLICATION NO. 2025-00041, ADJUSTMENT NO. 17 TO THE DISNEYLAND RESORT SPECIFIC PLAN NO. 92-1, ADJUSTMENT NO. 15 TO THE ANAHEIM RESORT SPECIFIC PLAN NO. 92-2, ADJUSTMENT NO. 16 </t>
+  </si>
+  <si>
+    <t>2025-11-16 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
+  </si>
+  <si>
+    <t>Nashville | 12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
+  </si>
+  <si>
+    <t>Nashville | Specific Plan Zoning District: An ordinance to authorize building material restrictions and requirements for BL2026-1474, a proposed Specific Plan Zoning District for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001). THE PROPOSED ORDINANCE REQUIRES CERTAIN MATERIALS TO BE RESTRICTED IN THE CONSTRUCTION OF BUILDINGS.</t>
+  </si>
+  <si>
+    <t>Nashville | approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1: An ordinance approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1 to the Bordeaux Redevelopment Plan, Amendment No. 1 to the Central State Redevelopment Plan, Amendment No. 6 to the Phillips-Jackson Redevelopment Plan, Amendment No. 9 to the Rutledge Hill Redevelopment Plan, and Amendment No. 1 to the Skyline Redevelopment Plan. (Proposal No. 2026M-002OT-001)</t>
+  </si>
+  <si>
+    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20850</t>
   </si>
   <si>
     <t>Clark County | Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
@@ -247,30 +237,6 @@
 DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
   </si>
   <si>
-    <t>Clark County | Toll South LV leisure development: ORD-26-900159: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Toll South LV LLC for a single-family residential subdivision on 0.89 acres, generally located east of Hinson Street and north of Silverado Ranch Boulevard within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>Clark County | BDA South leisure development: ORD-26-900280: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with BDA South, LLC for a vehicle wash on 1.08 acres, generally located north of Wigwam Avenue and east of Arville Street within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>Clark County | World Buddhism Association Headquarters &amp; MGM-Grand Bally's integrated resort: 4. AR-26-400041 (UC-25-0544)-WORLD BUDDHISM ASSOCIATION HEADQUARTERS &amp; MGM-GRAND BALLY'S, LLC LEASE: USE PERMIT FIRST APPLICATION FOR REVIEW for a recreational or entertainment facility. DESIGN REVIEW</t>
-  </si>
-  <si>
-    <t>Clark County | ZL II leisure development: ORD-26-900259: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with ZL II, LLC for an avocational or vocational training facility and parking lot expansion on 12.04 acres, generally located east of El Camino Road and north of Rafael Rivera Way within Enterprise. MN/jl (For possible action)</t>
-  </si>
-  <si>
-    <t>2026-07-07 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110310</t>
-  </si>
-  <si>
-    <t>Clark County | Cimarron Spring Deux LLC, A &amp; A Revocable Living Trust leisure development: ORD-26-900221: Conduct a public hearing on an ordinance to consider adoption of a Development Agreement with Cimarron Spring Deux LLC, A &amp; A Revocable Living Trust, and A &amp; A III LLC for a single-family development on 2.54 acres, generally located west of Hinson Street and south of Richmar Avenue within Enterprise. JJ/tpd (For possible action)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110308</t>
-  </si>
-  <si>
     <t>Clark County | Ruby Holdings museum: 5. UC-26-0156-RUBY HOLDINGS, LLC: USE PERMITS for the following: 1) museum; and 2) office as a primary use. WAIVER OF DEVELOPMENT STANDARDS to reduce parking. DESIGN REVIEW for a proposed museum in co</t>
   </si>
   <si>
@@ -280,34 +246,28 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
   </si>
   <si>
-    <t>Nashville | 12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
-  </si>
-  <si>
-    <t>Nashville | amending Chapter 17.08 of the Metropolitan Code of Laws to modify the Zoning: An ordinance amending Chapter 17.08 of the Metropolitan Code of Laws to modify the Zoning District Land Use Table to reflect recent amendments to the Zoning Code (Proposal No. 2026Z-014-TX-001).</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20861</t>
-  </si>
-  <si>
-    <t>Nashville | approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1: An ordinance approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1 to the Bordeaux Redevelopment Plan, Amendment No. 1 to the Central State Redevelopment Plan, Amendment No. 6 to the Phillips-Jackson Redevelopment Plan, Amendment No. 9 to the Rutledge Hill Redevelopment Plan, and Amendment No. 1 to the Skyline Redevelopment Plan. (Proposal No. 2026M-002OT-001)</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20850</t>
-  </si>
-  <si>
-    <t>Nashville | to authorize building material restrictions and requirements for BL2026-1474: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from IR to SP zoning for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001).</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | 10450 Turkey Lake Road leisure development: Contract between CFTOD and Tower Engineering Inc. approved by the Board at the November 21, 2025, meeting</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-9.1-p276</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
-  </si>
-  <si>
-    <t>Anaheim | OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
+    <t>Phoenix | Children's Museum of Phoenix: Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>2026-06-16 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35274</t>
+  </si>
+  <si>
+    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
+  </si>
+  <si>
+    <t>2026-05-19 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
   </si>
   <si>
     <t>Las Vegas | 500 North Casino Center Drive casino: 24. For possible action to approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization, located at 500 North Casino Center Drive - Depa</t>
@@ -317,19 +277,6 @@
   </si>
   <si>
     <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
-  </si>
-  <si>
-    <t>Bonita Springs | 8910 Terrene Ct leisure development: Bonita Bay Lake 21 Restoration (250609-53694_36-114553-P)</t>
-  </si>
-  <si>
-    <t>2025-10-14 | Bonita Springs</t>
-  </si>
-  <si>
-    <t>https://www.sfwmd.gov/regpermitting#erp-250609-53694_36-114553-P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio | Weston Urban leisure development: Discussion and possible action to authorize execution of a Master Economic Incentive Agreement between Weston Urban, LLC and the City of San Antonio as a source of funding for public improvements related to the redevelopment of the property located at 322 W. Commerce, for an amount up to $250,000.
-</t>
   </si>
   <si>
     <t>Coverage note</t>
@@ -725,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -838,16 +785,16 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
         <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -855,16 +802,16 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -875,13 +822,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -892,13 +839,13 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
         <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -909,13 +856,13 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -926,13 +873,13 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
         <v>37</v>
-      </c>
-      <c r="E17" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -943,13 +890,13 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -960,13 +907,13 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -977,573 +924,471 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>50</v>
-      </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
         <v>48</v>
       </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
         <v>48</v>
       </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>37</v>
-      </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E38" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="E41" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>105</v>
-      </c>
-      <c r="B51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" t="s">
         <v>14</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="85">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 16 projects, 74 records</t>
+    <t>Basis: 13 projects, 69 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -52,7 +52,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 16 projects and 74 captured records. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 69 captured records. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t/>
@@ -76,10 +76,25 @@
     <t>Headline finds</t>
   </si>
   <si>
-    <t>OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+    <t>PRESS</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>2026-07-24 | Clark County</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
   </si>
   <si>
     <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
@@ -88,22 +103,28 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>PRESS</t>
-  </si>
-  <si>
-    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
-  </si>
-  <si>
-    <t>2026-07-24 | Clark County</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+    <t xml:space="preserve">Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
+  </si>
+  <si>
+    <t>2026-06-22 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
   </si>
   <si>
     <t>Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
@@ -116,63 +137,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
-    <t>OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
-  </si>
-  <si>
-    <t>2026-01-12 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
-  </si>
-  <si>
-    <t>2026-06-22 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
-  </si>
-  <si>
-    <t>12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
-  </si>
-  <si>
-    <t>2026-08-03 | Nashville</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County...</t>
-  </si>
-  <si>
-    <t>Specific Plan Zoning District: An ordinance to authorize building material restrictions and requirements for BL2026-1474, a proposed Specific Plan Zoning District for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001). THE PROPOSED ORDINANCE REQUIRES CERTAIN MATERIALS TO BE RESTRICTED IN THE CONSTRUCTION OF BUILDINGS.</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20783</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20782</t>
   </si>
   <si>
     <t xml:space="preserve">Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
@@ -185,6 +149,30 @@
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110419</t>
   </si>
   <si>
+    <t>Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>2026-06-16 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
+  </si>
+  <si>
+    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
+  </si>
+  <si>
+    <t>2026-05-19 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
+  </si>
+  <si>
     <t>Children's Museum of Phoenix: Children's Museum of Phoenix</t>
   </si>
   <si>
@@ -194,18 +182,30 @@
     <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
   </si>
   <si>
+    <t>OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
+  </si>
+  <si>
+    <t>2026-01-12 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
+  </si>
+  <si>
     <t>By market</t>
   </si>
   <si>
+    <t xml:space="preserve">Anaheim | OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaheim | Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
+  </si>
+  <si>
     <t>Anaheim | Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
   </si>
   <si>
-    <t>Anaheim | OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anaheim | Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
-  </si>
-  <si>
     <t>Anaheim | OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
   </si>
   <si>
@@ -216,18 +216,6 @@
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
-  </si>
-  <si>
-    <t>Nashville | 12802 Old Hickory Boulevard mixed-use development: An ordinance to amend Title 17 of the Metropolitan Code of Laws, the Zoning Ordinance of The Metropolitan Government of Nashville and Davidson County, by changing from AR2a to SP zoning for property located at 12802 Old Hickory Boulevard, approximately 148 feet southwest of Logistics Way (3.6 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-025-001).</t>
-  </si>
-  <si>
-    <t>Nashville | Specific Plan Zoning District: An ordinance to authorize building material restrictions and requirements for BL2026-1474, a proposed Specific Plan Zoning District for property located at 1205 2nd Avenue North, approximately 129 feet north of Madison Street (0.46 acres), to permit a mixed use development, all of which is described herein (Proposal No. 2026SP-024-001). THE PROPOSED ORDINANCE REQUIRES CERTAIN MATERIALS TO BE RESTRICTED IN THE CONSTRUCTION OF BUILDINGS.</t>
-  </si>
-  <si>
-    <t>Nashville | approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1: An ordinance approving Amendment No. 6 to the Arts Center Redevelopment Plan, Amendment No. 1 to the Bordeaux Redevelopment Plan, Amendment No. 1 to the Central State Redevelopment Plan, Amendment No. 6 to the Phillips-Jackson Redevelopment Plan, Amendment No. 9 to the Rutledge Hill Redevelopment Plan, and Amendment No. 1 to the Skyline Redevelopment Plan. (Proposal No. 2026M-002OT-001)</t>
-  </si>
-  <si>
-    <t>https://nashville.legistar.com/gateway.aspx?M=l&amp;ID=20850</t>
   </si>
   <si>
     <t>Clark County | Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
@@ -246,28 +234,16 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
   </si>
   <si>
+    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
+  </si>
+  <si>
     <t>Phoenix | Children's Museum of Phoenix: Children's Museum of Phoenix</t>
   </si>
   <si>
-    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>2026-06-16 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35274</t>
-  </si>
-  <si>
-    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
-  </si>
-  <si>
-    <t>2026-05-19 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
   </si>
   <si>
     <t>Las Vegas | 500 North Casino Center Drive casino: 24. For possible action to approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization, located at 500 North Casino Center Drive - Depa</t>
@@ -672,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -768,16 +744,16 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -788,13 +764,13 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -802,16 +778,16 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -822,13 +798,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,13 +815,13 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -856,13 +832,13 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
         <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -944,10 +920,10 @@
         <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -958,10 +934,10 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
@@ -978,10 +954,10 @@
         <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,13 +968,13 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1009,13 +985,13 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,30 +1002,30 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,13 +1036,13 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
         <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,13 +1053,13 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,13 +1070,13 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,13 +1087,13 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,16 +1101,16 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,13 +1121,13 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,13 +1138,13 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,13 +1155,13 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,16 +1169,16 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,13 +1189,13 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" t="s">
         <v>55</v>
-      </c>
-      <c r="E37" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1230,13 +1206,13 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1250,145 +1226,77 @@
         <v>77</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" t="s">
         <v>14</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="206">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Section</t>
   </si>
   <si>
+    <t>Project</t>
+  </si>
+  <si>
     <t>Provenance</t>
   </si>
   <si>
@@ -49,13 +52,13 @@
     <t>Scope of this report</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>ASSESSMENT</t>
   </si>
   <si>
     <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 69 captured records. Anything outside that geography or period is not covered here.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>What moved</t>
@@ -197,62 +200,421 @@
     <t>By market</t>
   </si>
   <si>
-    <t xml:space="preserve">Anaheim | OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anaheim | Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
-  </si>
-  <si>
-    <t>Anaheim | Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
-  </si>
-  <si>
-    <t>Anaheim | OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anaheim | 10 To The Beach Boulevard theme park: ITEM NO. 3 DEVELOPMENT APPLICATION NO. 2025-00041, ADJUSTMENT NO. 17 TO THE DISNEYLAND RESORT SPECIFIC PLAN NO. 92-1, ADJUSTMENT NO. 15 TO THE ANAHEIM RESORT SPECIFIC PLAN NO. 92-2, ADJUSTMENT NO. 16 </t>
-  </si>
-  <si>
-    <t>2025-11-16 | Anaheim</t>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVIBE Residential Phase I</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVIBE Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVIBE | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>Players: Anaheim Real Estate Partners, LLC (applicant)</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVIBE Site Master Plan project</t>
+  </si>
+  <si>
+    <t>Players: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE) (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 3 filings on the first amended and restated development agreement between 2025-06-16 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
+  </si>
+  <si>
+    <t>Players: Walt Disney Parks and Resorts U.S., Inc. (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
+    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
+  </si>
+  <si>
+    <t>$10,030,000 | Players: Walt Disney Parks and Resorts U.S., Inc. (applicant)</t>
+  </si>
+  <si>
+    <t>2026-06-22. Determination of good faith compliance with terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
+  </si>
+  <si>
+    <t>Players: Walt Disney Parks and Resorts US, Inc. (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro</t>
+  </si>
+  <si>
+    <t>Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+  </si>
+  <si>
+    <t>Records show 8 filings on the development application between 2025-04-21 and 2026-07-27.</t>
+  </si>
+  <si>
+    <t>2025-04-21. Adopt 2021-2029 Housing Element; update General Plan Land Use, Circulation, and Environmental Justice Elements; amend Title 18 (Zoning) of Anaheim Municipal Code; reclassify zoning; amend Platinum Triangle Master Land Use Plan; adjust Anaheim Canyon Specific Plan No. 2015-1 and Beach Boulevard Specific Plan No...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00002</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3384#item-h5b6c84ab98c9</t>
+  </si>
+  <si>
+    <t>2025-05-12. (ADOPTION) AN ORDINANCE OF THE CITY OF ANAHEIM; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
+  </si>
+  <si>
+    <t>ORDINANCE No. 6609</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
+  </si>
+  <si>
+    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+  </si>
+  <si>
+    <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3461#item-h4e3dc2abd4c4</t>
+  </si>
+  <si>
+    <t>2025-12-15. Determine non-compliance with Amended and Restated Development Agreement and direct staff to provide notice of intent to establish new development timeframes</t>
+  </si>
+  <si>
+    <t>Players: PT Metro, LLC (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h4d8938c8638b</t>
+  </si>
+  <si>
+    <t>2026-01-26. Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>Players: PT Metro, LLC and Joey Caucas (applicant) | Contact: Joey Caucas. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t>2026-06-14. City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_716824770c824daa2c4a8d0c4c4a6bf3.pdf&amp;view=1#item-h1711c29b4251</t>
+  </si>
+  <si>
+    <t>2026-07-27. General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022</t>
+  </si>
+  <si>
+    <t>OTR, an Ohio Partnership mixed-use development</t>
+  </si>
+  <si>
+    <t>The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
+  </si>
+  <si>
+    <t>Records show the general plan amendment amended more than once.</t>
+  </si>
+  <si>
+    <t>2025-11-16. General Plan Amendment, Specific Plan Amendment, Zoning Code Amendment, Final Site Plan, and Development Agreement</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2023-00043</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h7d81d1e8a4e3</t>
+  </si>
+  <si>
+    <t>2025-12-15. Specific Plan Amendment to Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
+  </si>
+  <si>
+    <t>16.2 acres | Players: OTR, an Ohio Partnership (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h0d73a75a9eca</t>
+  </si>
+  <si>
+    <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
+    <t>2026-01-12. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>2026-01-12. Specific Plan Amendment to amend Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-h0d73a75a9eca</t>
+  </si>
+  <si>
+    <t>10 To The Beach Boulevard theme park</t>
+  </si>
+  <si>
+    <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
   </si>
   <si>
-    <t>Clark County | Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark County | Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
-DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
-  </si>
-  <si>
-    <t>Clark County | Ruby Holdings museum: 5. UC-26-0156-RUBY HOLDINGS, LLC: USE PERMITS for the following: 1) museum; and 2) office as a primary use. WAIVER OF DEVELOPMENT STANDARDS to reduce parking. DESIGN REVIEW for a proposed museum in co</t>
-  </si>
-  <si>
-    <t>2026-04-14 | Clark County</t>
+    <t>Records show 1 filing, dated 2025-11-16.</t>
+  </si>
+  <si>
+    <t>2025-11-16. Amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters including Single-Family Residential Zones, Multiple-Family Residential Zones, Commercial Zones, Industrial Zone, Mixed-Use Zone, Public and Special-Purpose Zones, and associated zoning and development standards; Adjustment No...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by)</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River</t>
+  </si>
+  <si>
+    <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>Clark County | approved</t>
+  </si>
+  <si>
+    <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
+  </si>
+  <si>
+    <t>2026-05-26. VACATE AND ABANDON easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
+  </si>
+  <si>
+    <t>2026-05-26. TENTATIVE MAP approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
+  </si>
+  <si>
+    <t>2026-07-21. VACATE AND ABANDON easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative)</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative) | Contact: Nancy Amundsen. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
+  </si>
+  <si>
+    <t>2026-07-21. HOLDOVER USE PERMITS to expand the gaming enterprise district, resort hotel, and recreational facility; WAIVER OF DEVELOPMENT STANDARDS to allow non-standard improvements in the right-of-way; DESIGN REVIEW for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative) | Contact: Nancy Amundsen. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
+  </si>
+  <si>
+    <t>https://ggbmagazine.com/articles/las-vegas-approves-heart-shaped-casino-on-skyvue-site/</t>
+  </si>
+  <si>
+    <t>2026-07-23. Resort project replacing failed Las Vegas Strip observation ...</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
+  </si>
+  <si>
+    <t>2026-07-24. Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>Mirage Propco casino</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-07-21.</t>
+  </si>
+  <si>
+    <t>2026-07-21. DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel</t>
+  </si>
+  <si>
+    <t>DR-26-0313 | 76.93 acres | Players: Mirage Propco, LLC (applicant); Kaempfer Crowell, Jennifer Lazovich (representative) | Contact: Jennifer Lazovich. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-04-14.</t>
+  </si>
+  <si>
+    <t>2026-04-14. USE PERMITS for museum and office as primary use; WAIVER OF DEVELOPMENT STANDARDS to reduce parking; DESIGN REVIEW for proposed museum</t>
+  </si>
+  <si>
+    <t>UC-26-0156 | Players: Ruby Holdings, LLC (applicant)</t>
   </si>
   <si>
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
   </si>
   <si>
-    <t>Phoenix | Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>Phoenix | ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
-  </si>
-  <si>
-    <t>Phoenix | Children's Museum of Phoenix: Children's Museum of Phoenix</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
-  </si>
-  <si>
-    <t>Las Vegas | 500 North Casino Center Drive casino: 24. For possible action to approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization, located at 500 North Casino Center Drive - Depa</t>
-  </si>
-  <si>
-    <t>2025-10-15 | Las Vegas</t>
+    <t>Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>Phoenix | approved</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-16.</t>
+  </si>
+  <si>
+    <t>2026-06-16. Liquor License</t>
+  </si>
+  <si>
+    <t>Players: Fire N Ice Arena (applicant)</t>
+  </si>
+  <si>
+    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900)</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-05-19.</t>
+  </si>
+  <si>
+    <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
+  </si>
+  <si>
+    <t>Players: Tohono O'odham Nation (applicant)</t>
+  </si>
+  <si>
+    <t>Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-30.</t>
+  </si>
+  <si>
+    <t>2026-06-30. Payment Ordinance</t>
+  </si>
+  <si>
+    <t>Players: Children's Museum of Phoenix (applicant)</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World</t>
+  </si>
+  <si>
+    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | under construction</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.45)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p45</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>Players: Walt Disney Parks &amp; Resorts U.S. Inc. (applicant); Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>500 North Casino Center Drive casino</t>
+  </si>
+  <si>
+    <t>Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization...</t>
+  </si>
+  <si>
+    <t>Las Vegas | approved</t>
   </si>
   <si>
     <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2025-10-15.</t>
+  </si>
+  <si>
+    <t>2025-10-15. Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to WESTAR ARCHITECTURAL GROUP NEVADA, INC</t>
+  </si>
+  <si>
+    <t>Players: Department of Public Works (presented by)</t>
   </si>
   <si>
     <t>Coverage note</t>
@@ -648,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -688,7 +1050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -704,30 +1066,36 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -738,13 +1106,16 @@
       <c r="E10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -755,67 +1126,79 @@
       <c r="E11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
         <v>31</v>
@@ -823,33 +1206,39 @@
       <c r="E15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
         <v>36</v>
@@ -857,16 +1246,19 @@
       <c r="E17" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
@@ -874,33 +1266,39 @@
       <c r="E18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
         <v>41</v>
       </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
@@ -908,16 +1306,19 @@
       <c r="E20" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
@@ -925,33 +1326,39 @@
       <c r="E21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
         <v>51</v>
@@ -959,16 +1366,19 @@
       <c r="E23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -976,16 +1386,19 @@
       <c r="E24" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
         <v>57</v>
@@ -993,311 +1406,1368 @@
       <c r="E25" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
         <v>59</v>
       </c>
-      <c r="D26" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" t="s">
+        <v>90</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>122</v>
+      </c>
+      <c r="E54" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" t="s">
+        <v>126</v>
+      </c>
+      <c r="F55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" t="s">
+        <v>126</v>
+      </c>
+      <c r="F58" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" t="s">
+        <v>64</v>
+      </c>
+      <c r="F59" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" t="s">
+        <v>141</v>
+      </c>
+      <c r="F62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" t="s">
+        <v>144</v>
+      </c>
+      <c r="F64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" t="s">
+        <v>147</v>
+      </c>
+      <c r="F65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" t="s">
+        <v>149</v>
+      </c>
+      <c r="F66" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" t="s">
+        <v>155</v>
+      </c>
+      <c r="F68" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>157</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" t="s">
+        <v>161</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>163</v>
+      </c>
+      <c r="E72" t="s">
+        <v>141</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>164</v>
+      </c>
+      <c r="E73" t="s">
+        <v>165</v>
+      </c>
+      <c r="F73" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>167</v>
+      </c>
+      <c r="E74" t="s">
+        <v>141</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>168</v>
+      </c>
+      <c r="E75" t="s">
+        <v>169</v>
+      </c>
+      <c r="F75" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" t="s">
+        <v>172</v>
+      </c>
+      <c r="F76" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" t="s">
+        <v>172</v>
+      </c>
+      <c r="F77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>174</v>
+      </c>
+      <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" t="s">
+        <v>172</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" t="s">
+        <v>178</v>
+      </c>
+      <c r="E80" t="s">
+        <v>179</v>
+      </c>
+      <c r="F80" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>61</v>
+      </c>
+      <c r="B81" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E81" t="s">
+        <v>172</v>
+      </c>
+      <c r="F81" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" t="s">
+        <v>182</v>
+      </c>
+      <c r="E82" t="s">
+        <v>183</v>
+      </c>
+      <c r="F82" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>185</v>
+      </c>
+      <c r="E83" t="s">
+        <v>186</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
+        <v>187</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
+        <v>189</v>
+      </c>
+      <c r="E85" t="s">
+        <v>190</v>
+      </c>
+      <c r="F85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" t="s">
+        <v>192</v>
+      </c>
+      <c r="F86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>61</v>
+      </c>
+      <c r="B87" t="s">
+        <v>194</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
+        <v>195</v>
+      </c>
+      <c r="E87" t="s">
+        <v>196</v>
+      </c>
+      <c r="F87" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>61</v>
+      </c>
+      <c r="B88" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>198</v>
+      </c>
+      <c r="E88" t="s">
+        <v>196</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
+        <v>199</v>
+      </c>
+      <c r="E89" t="s">
+        <v>200</v>
+      </c>
+      <c r="F89" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
         <v>14</v>
       </c>
-      <c r="E26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D90" t="s">
+        <v>202</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>201</v>
+      </c>
+      <c r="B91" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" t="s">
         <v>14</v>
       </c>
-      <c r="E40" t="s">
+      <c r="D91" t="s">
+        <v>203</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D92" t="s">
+        <v>204</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>201</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
         <v>14</v>
       </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
+      <c r="D93" t="s">
+        <v>205</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="202">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -212,19 +212,19 @@
     <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
   </si>
   <si>
-    <t>2026-02-06. OCVIBE Residential Phase I</t>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
   </si>
   <si>
     <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
   </si>
   <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVIBE Project; and authorize the Finance Director to execute the amendment</t>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
   </si>
   <si>
-    <t>2026-05-05. OCVIBE | The new heart of Orange County</t>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
   </si>
   <si>
     <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
@@ -254,13 +254,7 @@
     <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
   </si>
   <si>
-    <t>2026-07-13. Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVIBE Site Master Plan project</t>
-  </si>
-  <si>
-    <t>Players: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE) (applicant)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
   </si>
   <si>
     <t>Disneyland Resort</t>
@@ -287,13 +281,7 @@
     <t>$10,030,000 | Players: Walt Disney Parks and Resorts U.S., Inc. (applicant)</t>
   </si>
   <si>
-    <t>2026-06-22. Determination of good faith compliance with terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
-  </si>
-  <si>
-    <t>Players: Walt Disney Parks and Resorts US, Inc. (applicant)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
   </si>
   <si>
     <t>Platinum Triangle / PT Metro</t>
@@ -314,7 +302,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3384#item-h5b6c84ab98c9</t>
   </si>
   <si>
-    <t>2025-05-12. (ADOPTION) AN ORDINANCE OF THE CITY OF ANAHEIM; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
+    <t>2025-05-12. (Adoption) An ordinance of the city of anaheim; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
   </si>
   <si>
     <t>ORDINANCE No. 6609</t>
@@ -443,7 +431,7 @@
     <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
   </si>
   <si>
-    <t>2026-05-26. VACATE AND ABANDON easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
+    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
   </si>
   <si>
     <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
@@ -452,13 +440,13 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
   </si>
   <si>
-    <t>2026-05-26. TENTATIVE MAP approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
+    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
   </si>
   <si>
     <t>TM-26-500056 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
   </si>
   <si>
-    <t>2026-07-21. VACATE AND ABANDON easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
   </si>
   <si>
     <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative)</t>
@@ -476,7 +464,7 @@
     <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
   </si>
   <si>
-    <t>2026-07-21. HOLDOVER USE PERMITS to expand the gaming enterprise district, resort hotel, and recreational facility; WAIVER OF DEVELOPMENT STANDARDS to allow non-standard improvements in the right-of-way; DESIGN REVIEW for a proposed resort hotel and recreational facility</t>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
   </si>
   <si>
     <t>UC-26-0219 | 11.95 acres | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative) | Contact: Nancy Amundsen. No phone or email in the record.</t>
@@ -506,7 +494,7 @@
     <t>Records show 1 filing, dated 2026-07-21.</t>
   </si>
   <si>
-    <t>2026-07-21. DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel</t>
+    <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel</t>
   </si>
   <si>
     <t>DR-26-0313 | 76.93 acres | Players: Mirage Propco, LLC (applicant); Kaempfer Crowell, Jennifer Lazovich (representative) | Contact: Jennifer Lazovich. No phone or email in the record.</t>
@@ -518,7 +506,7 @@
     <t>Records show 1 filing, dated 2026-04-14.</t>
   </si>
   <si>
-    <t>2026-04-14. USE PERMITS for museum and office as primary use; WAIVER OF DEVELOPMENT STANDARDS to reduce parking; DESIGN REVIEW for proposed museum</t>
+    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
   </si>
   <si>
     <t>UC-26-0156 | Players: Ruby Holdings, LLC (applicant)</t>
@@ -611,7 +599,7 @@
     <t>Records show 1 filing, dated 2025-10-15.</t>
   </si>
   <si>
-    <t>2025-10-15. Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to WESTAR ARCHITECTURAL GROUP NEVADA, INC</t>
+    <t>2025-10-15. Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to Westar architectural group nevada, INC</t>
   </si>
   <si>
     <t>Players: Department of Public Works (presented by)</t>
@@ -1624,10 +1612,10 @@
         <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,13 +1623,13 @@
         <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
         <v>64</v>
@@ -1655,13 +1643,13 @@
         <v>61</v>
       </c>
       <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
         <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>85</v>
       </c>
       <c r="E38" t="s">
         <v>64</v>
@@ -1675,19 +1663,19 @@
         <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
         <v>86</v>
-      </c>
-      <c r="E39" t="s">
-        <v>87</v>
-      </c>
-      <c r="F39" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1695,16 +1683,16 @@
         <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F40" t="s">
         <v>35</v>
@@ -1715,19 +1703,19 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1735,13 +1723,13 @@
         <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
         <v>64</v>
@@ -1755,13 +1743,13 @@
         <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
         <v>64</v>
@@ -1775,19 +1763,19 @@
         <v>61</v>
       </c>
       <c r="B44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" t="s">
         <v>94</v>
       </c>
-      <c r="C44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" t="s">
-        <v>98</v>
-      </c>
       <c r="F44" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,19 +1783,19 @@
         <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,19 +1803,19 @@
         <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E46" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1835,19 +1823,19 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1855,19 +1843,19 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F48" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,19 +1863,19 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1895,19 +1883,19 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1915,16 +1903,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F51" t="s">
         <v>41</v>
@@ -1935,13 +1923,13 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E52" t="s">
         <v>64</v>
@@ -1955,13 +1943,13 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E53" t="s">
         <v>64</v>
@@ -1975,19 +1963,19 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" t="s">
         <v>119</v>
       </c>
-      <c r="C54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" t="s">
-        <v>122</v>
-      </c>
-      <c r="E54" t="s">
-        <v>123</v>
-      </c>
       <c r="F54" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1995,19 +1983,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2015,19 +2003,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E56" t="s">
         <v>13</v>
       </c>
       <c r="F56" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2035,13 +2023,13 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E57" t="s">
         <v>13</v>
@@ -2055,19 +2043,19 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F58" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2075,19 +2063,19 @@
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E59" t="s">
         <v>64</v>
       </c>
       <c r="F59" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,13 +2083,13 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E60" t="s">
         <v>64</v>
@@ -2115,19 +2103,19 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
         <v>133</v>
       </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" t="s">
-        <v>137</v>
-      </c>
       <c r="E61" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,16 +2123,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E62" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F62" t="s">
         <v>27</v>
@@ -2155,16 +2143,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -2175,19 +2163,19 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
         <v>139</v>
       </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>143</v>
-      </c>
       <c r="E64" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,16 +2183,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
@@ -2215,19 +2203,19 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E66" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F66" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2235,19 +2223,19 @@
         <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F67" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,19 +2243,19 @@
         <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E68" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F68" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,19 +2263,19 @@
         <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E69" t="s">
         <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2295,19 +2283,19 @@
         <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E70" t="s">
         <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,13 +2303,13 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E71" t="s">
         <v>13</v>
@@ -2335,16 +2323,16 @@
         <v>61</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -2355,16 +2343,16 @@
         <v>61</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E73" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F73" t="s">
         <v>45</v>
@@ -2375,16 +2363,16 @@
         <v>61</v>
       </c>
       <c r="B74" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E74" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -2395,19 +2383,19 @@
         <v>61</v>
       </c>
       <c r="B75" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>164</v>
+      </c>
+      <c r="E75" t="s">
+        <v>165</v>
+      </c>
+      <c r="F75" t="s">
         <v>166</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>168</v>
-      </c>
-      <c r="E75" t="s">
-        <v>169</v>
-      </c>
-      <c r="F75" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,16 +2403,16 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E76" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
         <v>50</v>
@@ -2435,16 +2423,16 @@
         <v>61</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E77" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
@@ -2455,16 +2443,16 @@
         <v>61</v>
       </c>
       <c r="B78" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>170</v>
+      </c>
+      <c r="E78" t="s">
         <v>171</v>
-      </c>
-      <c r="C78" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" t="s">
-        <v>174</v>
-      </c>
-      <c r="E78" t="s">
-        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -2475,16 +2463,16 @@
         <v>61</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C79" t="s">
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -2495,16 +2483,16 @@
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>53</v>
@@ -2515,16 +2503,16 @@
         <v>61</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E81" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -2535,16 +2523,16 @@
         <v>61</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E82" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F82" t="s">
         <v>56</v>
@@ -2555,16 +2543,16 @@
         <v>61</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E83" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -2575,19 +2563,19 @@
         <v>61</v>
       </c>
       <c r="B84" t="s">
+        <v>180</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
         <v>184</v>
-      </c>
-      <c r="C84" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" t="s">
-        <v>187</v>
-      </c>
-      <c r="E84" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2595,16 +2583,16 @@
         <v>61</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
         <v>38</v>
@@ -2615,19 +2603,19 @@
         <v>61</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E86" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2635,19 +2623,19 @@
         <v>61</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E87" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F87" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2655,16 +2643,16 @@
         <v>61</v>
       </c>
       <c r="B88" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
         <v>194</v>
       </c>
-      <c r="C88" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" t="s">
-        <v>198</v>
-      </c>
       <c r="E88" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
@@ -2675,24 +2663,24 @@
         <v>61</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E89" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F89" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -2701,7 +2689,7 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
@@ -2712,7 +2700,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -2721,7 +2709,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
@@ -2732,7 +2720,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -2741,7 +2729,7 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E92" t="s">
         <v>13</v>
@@ -2752,7 +2740,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -2761,7 +2749,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="203">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -58,7 +58,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 69 captured records. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 69 captured records. Of those projects, 13 are described in full, selected by significance. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>What moved</t>
@@ -615,6 +615,9 @@
   </si>
   <si>
     <t>Dormant projects are excluded from this report.</t>
+  </si>
+  <si>
+    <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
   </si>
   <si>
     <t>Records are captured from published sources. A matter that has not been published, or that is published somewhere we do not yet capture, will not appear.</t>
@@ -998,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2758,6 +2761,26 @@
         <v>13</v>
       </c>
     </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>197</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>202</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="178">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 13 projects, 69 records</t>
+    <t>Basis: 13 projects, 56 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -58,7 +58,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 69 captured records. Of those projects, 13 are described in full, selected by significance. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 56 captured records. Of those projects, 12 are described in full, selected by significance; 1 project filed nothing in this period. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>What moved</t>
@@ -67,7 +67,19 @@
     <t>RECORD</t>
   </si>
   <si>
-    <t>OCVibe: filed to approved</t>
+    <t>Disneyland Resort: under construction to approved</t>
+  </si>
+  <si>
+    <t>2026-07-27 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://www.parksavers.com/new-disneylandforward/</t>
+  </si>
+  <si>
+    <t>Headline finds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
   </si>
   <si>
     <t>2026-07-13 | Anaheim</t>
@@ -76,30 +88,6 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
   </si>
   <si>
-    <t>Headline finds</t>
-  </si>
-  <si>
-    <t>PRESS</t>
-  </si>
-  <si>
-    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
-  </si>
-  <si>
-    <t>2026-07-24 | Clark County</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
-  </si>
-  <si>
     <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
   </si>
   <si>
@@ -131,9 +119,6 @@
   </si>
   <si>
     <t>Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
-  </si>
-  <si>
-    <t>2026-07-27 | Anaheim</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
@@ -158,15 +143,12 @@
     <t>2026-06-16 | Phoenix</t>
   </si>
   <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35274</t>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
   </si>
   <si>
     <t xml:space="preserve">   Liquor License - Fire N Ice Arena - District 2</t>
   </si>
   <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
-  </si>
-  <si>
     <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
   </si>
   <si>
@@ -182,7 +164,7 @@
     <t>2026-06-30 | Phoenix</t>
   </si>
   <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35482</t>
   </si>
   <si>
     <t>OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
@@ -206,63 +188,72 @@
     <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
   </si>
   <si>
+    <t>Anaheim | under construction</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>PRESS</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>Players: Anaheim Real Estate Partners, LLC (applicant)</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
     <t>Anaheim | approved</t>
   </si>
   <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>Players: Anaheim Real Estate Partners, LLC (applicant)</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
     <t>Records show 3 filings on the first amended and restated development agreement between 2025-06-16 and 2026-06-22.</t>
   </si>
   <si>
@@ -311,7 +302,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
   </si>
   <si>
-    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
+    <t>2025-08-10. City-initiated clarifying technical amendments related to implementation of the Sixth Cycle Housing Element, including a General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations)...</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by)</t>
@@ -344,10 +335,10 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
   </si>
   <si>
-    <t>2026-06-14. City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: City of Anaheim (presented by)</t>
+    <t>2026-06-14. City-initiated General Plan Amendment to update the General Plan Land Use Element and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by)</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_716824770c824daa2c4a8d0c4c4a6bf3.pdf&amp;view=1#item-h1711c29b4251</t>
@@ -377,6 +368,12 @@
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h7d81d1e8a4e3</t>
   </si>
   <si>
+    <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
     <t>2025-12-15. Specific Plan Amendment to Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
   </si>
   <si>
@@ -386,12 +383,6 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h0d73a75a9eca</t>
   </si>
   <si>
-    <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
-  </si>
-  <si>
     <t>2026-01-12. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
   </si>
   <si>
@@ -413,88 +404,61 @@
     <t>Records show 1 filing, dated 2025-11-16.</t>
   </si>
   <si>
-    <t>2025-11-16. Amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters including Single-Family Residential Zones, Multiple-Family Residential Zones, Commercial Zones, Industrial Zone, Mixed-Use Zone, Public and Special-Purpose Zones, and associated zoning and development standards; Adjustment No...</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by)</t>
-  </si>
-  <si>
-    <t>Heart Hotel / Kulik River</t>
-  </si>
-  <si>
-    <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+    <t>2025-11-16. Amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters related to zoning and development standards, and adjustments to specific plans</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>Phoenix | approved</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-16.</t>
+  </si>
+  <si>
+    <t>2026-06-16. Liquor License</t>
+  </si>
+  <si>
+    <t>Players: Fire N Ice Arena (applicant)</t>
+  </si>
+  <si>
+    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900)</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-05-19.</t>
+  </si>
+  <si>
+    <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
+  </si>
+  <si>
+    <t>Players: Tohono O'odham Nation (applicant)</t>
+  </si>
+  <si>
+    <t>Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-30.</t>
+  </si>
+  <si>
+    <t>2026-06-30. Payment Ordinance</t>
+  </si>
+  <si>
+    <t>Players: Children's Museum of Phoenix (applicant)</t>
+  </si>
+  <si>
+    <t>Mirage Propco casino</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-07-21.</t>
   </si>
   <si>
     <t>Clark County | approved</t>
   </si>
   <si>
-    <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
-  </si>
-  <si>
-    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
-  </si>
-  <si>
-    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
-  </si>
-  <si>
-    <t>TM-26-500056 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative on the project's filings)</t>
-  </si>
-  <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative)</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover tentative map</t>
-  </si>
-  <si>
-    <t>TM-26-500056 | 11.95 acres | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative) | Contact: Nancy Amundsen. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
-  </si>
-  <si>
-    <t>UC-26-0219 | 11.95 acres | Players: Kulik River Capital, LLC (applicant); Nancy Amundsen, Brown, Brown, &amp; Premsrirut (representative) | Contact: Nancy Amundsen. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
-  </si>
-  <si>
-    <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
-  </si>
-  <si>
-    <t>https://ggbmagazine.com/articles/las-vegas-approves-heart-shaped-casino-on-skyvue-site/</t>
-  </si>
-  <si>
-    <t>2026-07-23. Resort project replacing failed Las Vegas Strip observation ...</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
-  </si>
-  <si>
-    <t>2026-07-24. Las Vegas Topic Kulik River Capital</t>
-  </si>
-  <si>
-    <t>Mirage Propco casino</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-07-21.</t>
-  </si>
-  <si>
-    <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel</t>
+    <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
   </si>
   <si>
     <t>DR-26-0313 | 76.93 acres | Players: Mirage Propco, LLC (applicant); Kaempfer Crowell, Jennifer Lazovich (representative) | Contact: Jennifer Lazovich. No phone or email in the record.</t>
@@ -515,45 +479,6 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
   </si>
   <si>
-    <t>Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>Phoenix | approved</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-06-16.</t>
-  </si>
-  <si>
-    <t>2026-06-16. Liquor License</t>
-  </si>
-  <si>
-    <t>Players: Fire N Ice Arena (applicant)</t>
-  </si>
-  <si>
-    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900)</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-05-19.</t>
-  </si>
-  <si>
-    <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
-  </si>
-  <si>
-    <t>Players: Tohono O'odham Nation (applicant)</t>
-  </si>
-  <si>
-    <t>Children's Museum of Phoenix</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-06-30.</t>
-  </si>
-  <si>
-    <t>2026-06-30. Payment Ordinance</t>
-  </si>
-  <si>
-    <t>Players: Children's Museum of Phoenix (applicant)</t>
-  </si>
-  <si>
     <t>CFTOD / Walt Disney World</t>
   </si>
   <si>
@@ -563,16 +488,16 @@
     <t>Central Florida Tourism Oversight District | under construction</t>
   </si>
   <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.45)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p45</t>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.16)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p16</t>
   </si>
   <si>
     <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
-    <t>Players: Walt Disney Parks &amp; Resorts U.S. Inc. (applicant); Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
+    <t>Players: Walt Disney Parks &amp; Resorts, U.S. Inc (applicant); Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
   </si>
   <si>
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
@@ -1001,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1109,16 +1034,16 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,13 +1057,13 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
         <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,13 +1077,13 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,13 +1097,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,13 +1117,13 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1212,13 +1137,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1232,13 +1157,13 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
         <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1252,13 +1177,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
         <v>39</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>40</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1272,13 +1197,13 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
         <v>42</v>
       </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1292,13 +1217,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
         <v>43</v>
-      </c>
-      <c r="E20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1312,13 +1237,13 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" t="s">
         <v>46</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>47</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1332,10 +1257,10 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
         <v>49</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>50</v>
@@ -1375,18 +1300,18 @@
         <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1398,78 +1323,78 @@
         <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F27" t="s">
         <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
         <v>64</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
         <v>66</v>
@@ -1483,10 +1408,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -1495,21 +1420,21 @@
         <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
@@ -1523,33 +1448,33 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
       </c>
       <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
         <v>73</v>
-      </c>
-      <c r="F32" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -1563,13 +1488,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
         <v>76</v>
@@ -1578,435 +1503,435 @@
         <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
         <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
         <v>81</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>82</v>
       </c>
-      <c r="E37" t="s">
-        <v>64</v>
-      </c>
       <c r="F37" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
         <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
         <v>90</v>
       </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>91</v>
       </c>
-      <c r="E42" t="s">
-        <v>64</v>
-      </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E49" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F49" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
         <v>115</v>
       </c>
-      <c r="C52" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>116</v>
       </c>
-      <c r="E52" t="s">
-        <v>64</v>
-      </c>
       <c r="F52" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E53" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E54" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
@@ -2015,7 +1940,7 @@
         <v>124</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F56" t="s">
         <v>125</v>
@@ -2023,50 +1948,50 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
@@ -2075,78 +2000,78 @@
         <v>130</v>
       </c>
       <c r="E59" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
+        <v>134</v>
+      </c>
+      <c r="E61" t="s">
         <v>133</v>
       </c>
-      <c r="E61" t="s">
-        <v>134</v>
-      </c>
       <c r="F61" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B62" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
         <v>135</v>
       </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>136</v>
       </c>
-      <c r="E62" t="s">
-        <v>137</v>
-      </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -2155,7 +2080,7 @@
         <v>138</v>
       </c>
       <c r="E63" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -2163,10 +2088,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
@@ -2178,175 +2103,175 @@
         <v>140</v>
       </c>
       <c r="F64" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
         <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
+        <v>143</v>
+      </c>
+      <c r="E66" t="s">
         <v>144</v>
       </c>
-      <c r="E66" t="s">
-        <v>145</v>
-      </c>
       <c r="F66" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" t="s">
         <v>147</v>
       </c>
-      <c r="E67" t="s">
-        <v>148</v>
-      </c>
       <c r="F67" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E68" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F68" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="F70" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
+        <v>156</v>
+      </c>
+      <c r="E71" t="s">
         <v>157</v>
       </c>
-      <c r="E71" t="s">
-        <v>13</v>
-      </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B72" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
         <v>158</v>
       </c>
-      <c r="C72" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
         <v>159</v>
-      </c>
-      <c r="E72" t="s">
-        <v>137</v>
-      </c>
-      <c r="F72" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -2358,124 +2283,124 @@
         <v>161</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
         <v>162</v>
       </c>
-      <c r="C74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>163</v>
       </c>
-      <c r="E74" t="s">
-        <v>137</v>
-      </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E75" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F75" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B76" t="s">
+        <v>165</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>169</v>
+      </c>
+      <c r="E76" t="s">
         <v>167</v>
       </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" t="s">
-        <v>167</v>
-      </c>
-      <c r="E76" t="s">
-        <v>168</v>
-      </c>
       <c r="F76" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77" t="s">
         <v>168</v>
-      </c>
-      <c r="F77" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E78" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -2483,39 +2408,39 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
         <v>176</v>
       </c>
-      <c r="C81" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" t="s">
-        <v>177</v>
-      </c>
       <c r="E81" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -2523,261 +2448,21 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E82" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>61</v>
-      </c>
-      <c r="B83" t="s">
-        <v>180</v>
-      </c>
-      <c r="C83" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" t="s">
-        <v>181</v>
-      </c>
-      <c r="E83" t="s">
-        <v>182</v>
-      </c>
-      <c r="F83" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" t="s">
-        <v>180</v>
-      </c>
-      <c r="C84" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" t="s">
-        <v>183</v>
-      </c>
-      <c r="E84" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>61</v>
-      </c>
-      <c r="B85" t="s">
-        <v>180</v>
-      </c>
-      <c r="C85" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" t="s">
-        <v>185</v>
-      </c>
-      <c r="E85" t="s">
-        <v>186</v>
-      </c>
-      <c r="F85" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>61</v>
-      </c>
-      <c r="B86" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" t="s">
-        <v>188</v>
-      </c>
-      <c r="F86" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>61</v>
-      </c>
-      <c r="B87" t="s">
-        <v>190</v>
-      </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" t="s">
-        <v>191</v>
-      </c>
-      <c r="E87" t="s">
-        <v>192</v>
-      </c>
-      <c r="F87" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" t="s">
-        <v>194</v>
-      </c>
-      <c r="E88" t="s">
-        <v>192</v>
-      </c>
-      <c r="F88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>61</v>
-      </c>
-      <c r="B89" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" t="s">
-        <v>195</v>
-      </c>
-      <c r="E89" t="s">
-        <v>196</v>
-      </c>
-      <c r="F89" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>197</v>
-      </c>
-      <c r="B90" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" t="s">
-        <v>14</v>
-      </c>
-      <c r="D90" t="s">
-        <v>198</v>
-      </c>
-      <c r="E90" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>197</v>
-      </c>
-      <c r="B91" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" t="s">
-        <v>14</v>
-      </c>
-      <c r="D91" t="s">
-        <v>199</v>
-      </c>
-      <c r="E91" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>197</v>
-      </c>
-      <c r="B92" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" t="s">
-        <v>14</v>
-      </c>
-      <c r="D92" t="s">
-        <v>200</v>
-      </c>
-      <c r="E92" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>197</v>
-      </c>
-      <c r="B93" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="D93" t="s">
-        <v>201</v>
-      </c>
-      <c r="E93" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>197</v>
-      </c>
-      <c r="B94" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" t="s">
-        <v>14</v>
-      </c>
-      <c r="D94" t="s">
-        <v>202</v>
-      </c>
-      <c r="E94" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="200">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -194,15 +194,27 @@
     <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
   </si>
   <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
     <t>2026-02-06. OCVibe Residential Phase I</t>
   </si>
   <si>
     <t>Players: City of Anaheim (presented by)</t>
   </si>
   <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
     <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
   </si>
   <si>
@@ -221,9 +233,6 @@
     <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
   </si>
   <si>
-    <t>Players: Anaheim Real Estate Partners, LLC (applicant)</t>
-  </si>
-  <si>
     <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
   </si>
   <si>
@@ -257,19 +266,19 @@
     <t>Records show 3 filings on the first amended and restated development agreement between 2025-06-16 and 2026-06-22.</t>
   </si>
   <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
     <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
   </si>
   <si>
-    <t>Players: Walt Disney Parks and Resorts U.S., Inc. (applicant)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
-  </si>
-  <si>
     <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
   </si>
   <si>
-    <t>$10,030,000 | Players: Walt Disney Parks and Resorts U.S., Inc. (applicant)</t>
+    <t>$10,030,000</t>
   </si>
   <si>
     <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
@@ -284,6 +293,27 @@
     <t>Records show 8 filings on the development application between 2025-04-21 and 2026-07-27.</t>
   </si>
   <si>
+    <t>Party: PT Metro</t>
+  </si>
+  <si>
+    <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t>Party: Christine Nguyen</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+  </si>
+  <si>
+    <t>Party: Joey Caucas</t>
+  </si>
+  <si>
+    <t>contact named in the record | No phone or email in the record.</t>
+  </si>
+  <si>
     <t>2025-04-21. Adopt 2021-2029 Housing Element; update General Plan Land Use, Circulation, and Environmental Justice Elements; amend Title 18 (Zoning) of Anaheim Municipal Code; reclassify zoning; amend Platinum Triangle Master Land Use Plan; adjust Anaheim Canyon Specific Plan No. 2015-1 and Beach Boulevard Specific Plan No...</t>
   </si>
   <si>
@@ -302,15 +332,12 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
   </si>
   <si>
-    <t>2025-08-10. City-initiated clarifying technical amendments related to implementation of the Sixth Cycle Housing Element, including a General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations)...</t>
+    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by)</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
-  </si>
-  <si>
     <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
   </si>
   <si>
@@ -329,13 +356,10 @@
     <t>2026-01-26. Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
   </si>
   <si>
-    <t>Players: PT Metro, LLC and Joey Caucas (applicant) | Contact: Joey Caucas. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t>2026-06-14. City-initiated General Plan Amendment to update the General Plan Land Use Element and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+    <t>Contact: Joey Caucas. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-06-14. A City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by)</t>
@@ -359,6 +383,12 @@
     <t>Records show the general plan amendment amended more than once.</t>
   </si>
   <si>
+    <t>Party: OTR, an Ohio Partnership</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h0d73a75a9eca</t>
+  </si>
+  <si>
     <t>2025-11-16. General Plan Amendment, Specific Plan Amendment, Zoning Code Amendment, Final Site Plan, and Development Agreement</t>
   </si>
   <si>
@@ -368,21 +398,18 @@
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h7d81d1e8a4e3</t>
   </si>
   <si>
+    <t>2025-12-15. Specific Plan Amendment to Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
+  </si>
+  <si>
+    <t>16.2 acres</t>
+  </si>
+  <si>
     <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
   </si>
   <si>
-    <t>2025-12-15. Specific Plan Amendment to Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
-  </si>
-  <si>
-    <t>16.2 acres | Players: OTR, an Ohio Partnership (applicant)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h0d73a75a9eca</t>
-  </si>
-  <si>
     <t>2026-01-12. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
   </si>
   <si>
@@ -404,10 +431,13 @@
     <t>Records show 1 filing, dated 2025-11-16.</t>
   </si>
   <si>
-    <t>2025-11-16. Amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters related to zoning and development standards, and adjustments to specific plans</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: City of Anaheim (presented by)</t>
+    <t>Party: Sean Nicholas</t>
+  </si>
+  <si>
+    <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by)</t>
   </si>
   <si>
     <t>Liquor License - Fire N Ice Arena - District 2</t>
@@ -419,36 +449,36 @@
     <t>Records show 1 filing, dated 2026-06-16.</t>
   </si>
   <si>
+    <t>Party: Fire N Ice Arena</t>
+  </si>
+  <si>
     <t>2026-06-16. Liquor License</t>
   </si>
   <si>
-    <t>Players: Fire N Ice Arena (applicant)</t>
-  </si>
-  <si>
     <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900)</t>
   </si>
   <si>
     <t>Records show 1 filing, dated 2026-05-19.</t>
   </si>
   <si>
+    <t>Party: Tohono O'odham Nation</t>
+  </si>
+  <si>
     <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
   </si>
   <si>
-    <t>Players: Tohono O'odham Nation (applicant)</t>
-  </si>
-  <si>
     <t>Children's Museum of Phoenix</t>
   </si>
   <si>
     <t>Records show 1 filing, dated 2026-06-30.</t>
   </si>
   <si>
+    <t>Party: Children's Museum of Phoenix</t>
+  </si>
+  <si>
     <t>2026-06-30. Payment Ordinance</t>
   </si>
   <si>
-    <t>Players: Children's Museum of Phoenix (applicant)</t>
-  </si>
-  <si>
     <t>Mirage Propco casino</t>
   </si>
   <si>
@@ -458,10 +488,25 @@
     <t>Clark County | approved</t>
   </si>
   <si>
+    <t>Party: Mirage Propco, LLC</t>
+  </si>
+  <si>
+    <t>Party: Kaempfer Crowell</t>
+  </si>
+  <si>
+    <t>representative | Jennifer Lazovich | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Jennifer Lazovich</t>
+  </si>
+  <si>
+    <t>contact named in the record | Kaempfer Crowell | No phone or email in the record.</t>
+  </si>
+  <si>
     <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
   </si>
   <si>
-    <t>DR-26-0313 | 76.93 acres | Players: Mirage Propco, LLC (applicant); Kaempfer Crowell, Jennifer Lazovich (representative) | Contact: Jennifer Lazovich. No phone or email in the record.</t>
+    <t>DR-26-0313 | 76.93 acres | Contact: Jennifer Lazovich, Kaempfer Crowell. No phone or email in the record.</t>
   </si>
   <si>
     <t>Ruby Holdings museum</t>
@@ -470,13 +515,16 @@
     <t>Records show 1 filing, dated 2026-04-14.</t>
   </si>
   <si>
+    <t>Party: Ruby Holdings, LLC</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+  </si>
+  <si>
     <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
   </si>
   <si>
-    <t>UC-26-0156 | Players: Ruby Holdings, LLC (applicant)</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+    <t>UC-26-0156</t>
   </si>
   <si>
     <t>CFTOD / Walt Disney World</t>
@@ -488,16 +536,34 @@
     <t>Central Florida Tourism Oversight District | under construction</t>
   </si>
   <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.16)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p16</t>
+    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
+  </si>
+  <si>
+    <t>Party: Craig Sandt</t>
+  </si>
+  <si>
+    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>Party: Katherine Luetzow</t>
+  </si>
+  <si>
+    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.36)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p36</t>
   </si>
   <si>
     <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
-    <t>Players: Walt Disney Parks &amp; Resorts, U.S. Inc (applicant); Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
+    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
   </si>
   <si>
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
@@ -506,9 +572,6 @@
     <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
   </si>
   <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
     <t>500 North Casino Center Drive casino</t>
   </si>
   <si>
@@ -522,6 +585,9 @@
   </si>
   <si>
     <t>Records show 1 filing, dated 2025-10-15.</t>
+  </si>
+  <si>
+    <t>Party: Department of Public Works</t>
   </si>
   <si>
     <t>2025-10-15. Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to Westar architectural group nevada, INC</t>
@@ -926,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1363,7 +1429,7 @@
         <v>61</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1377,10 +1443,10 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
         <v>63</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
@@ -1394,16 +1460,16 @@
         <v>56</v>
       </c>
       <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
         <v>65</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>66</v>
       </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1417,13 +1483,13 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
         <v>68</v>
-      </c>
-      <c r="E30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1434,7 +1500,7 @@
         <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
@@ -1454,7 +1520,7 @@
         <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
@@ -1463,7 +1529,7 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1474,16 +1540,16 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
         <v>74</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1494,16 +1560,16 @@
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
         <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,19 +1577,19 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
         <v>77</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
         <v>78</v>
-      </c>
-      <c r="E35" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1531,19 +1597,19 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1551,7 +1617,7 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -1563,7 +1629,7 @@
         <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1571,19 +1637,19 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1591,19 +1657,19 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1611,19 +1677,19 @@
         <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1631,19 +1697,19 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
         <v>87</v>
       </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>89</v>
-      </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1651,19 +1717,19 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,19 +1737,19 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1691,19 +1757,19 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1711,19 +1777,19 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1731,19 +1797,19 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1751,19 +1817,19 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F47" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1771,19 +1837,19 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F48" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,19 +1857,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,19 +1877,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,19 +1897,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1851,19 +1917,19 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" t="s">
+        <v>111</v>
+      </c>
+      <c r="F52" t="s">
         <v>112</v>
-      </c>
-      <c r="C52" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" t="s">
-        <v>115</v>
-      </c>
-      <c r="E52" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1871,19 +1937,19 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="F53" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1891,19 +1957,19 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E54" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1911,19 +1977,19 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1931,19 +1997,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1951,19 +2017,19 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1971,19 +2037,19 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1991,19 +2057,19 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" t="s">
         <v>126</v>
       </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E59" t="s">
-        <v>131</v>
-      </c>
       <c r="F59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2011,19 +2077,19 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F60" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2031,19 +2097,19 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2051,19 +2117,19 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
         <v>132</v>
       </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" t="s">
-        <v>135</v>
-      </c>
       <c r="E62" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2071,19 +2137,19 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2091,19 +2157,19 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" t="s">
+        <v>82</v>
+      </c>
+      <c r="F64" t="s">
         <v>137</v>
-      </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>139</v>
-      </c>
-      <c r="E64" t="s">
-        <v>140</v>
-      </c>
-      <c r="F64" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,16 +2177,16 @@
         <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E65" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -2131,19 +2197,19 @@
         <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="F66" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,19 +2217,19 @@
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E67" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,19 +2237,19 @@
         <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E68" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F68" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2191,16 +2257,16 @@
         <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -2211,19 +2277,19 @@
         <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,19 +2297,19 @@
         <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,19 +2317,19 @@
         <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="F72" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2271,19 +2337,19 @@
         <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="F73" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2291,19 +2357,19 @@
         <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E74" t="s">
-        <v>163</v>
+        <v>13</v>
       </c>
       <c r="F74" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2311,19 +2377,19 @@
         <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E75" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="F75" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2331,19 +2397,19 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E76" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,36 +2417,36 @@
         <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E77" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -2388,81 +2454,461 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" t="s">
+        <v>164</v>
+      </c>
+      <c r="F82" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>166</v>
+      </c>
+      <c r="E83" t="s">
+        <v>157</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
+        <v>167</v>
+      </c>
+      <c r="E84" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B85" t="s">
+        <v>165</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
+        <v>169</v>
+      </c>
+      <c r="E85" t="s">
+        <v>170</v>
+      </c>
+      <c r="F85" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
         <v>172</v>
       </c>
-      <c r="B82" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="E86" t="s">
+        <v>173</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
+        <v>174</v>
+      </c>
+      <c r="E87" t="s">
+        <v>61</v>
+      </c>
+      <c r="F87" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>55</v>
+      </c>
+      <c r="B88" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" t="s">
+        <v>175</v>
+      </c>
+      <c r="E88" t="s">
+        <v>176</v>
+      </c>
+      <c r="F88" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>55</v>
+      </c>
+      <c r="B89" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
+        <v>178</v>
+      </c>
+      <c r="E89" t="s">
+        <v>179</v>
+      </c>
+      <c r="F89" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>55</v>
+      </c>
+      <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" t="s">
+        <v>180</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>55</v>
+      </c>
+      <c r="B91" t="s">
+        <v>171</v>
+      </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
+        <v>182</v>
+      </c>
+      <c r="E91" t="s">
+        <v>183</v>
+      </c>
+      <c r="F91" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>184</v>
+      </c>
+      <c r="E92" t="s">
+        <v>185</v>
+      </c>
+      <c r="F92" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
+        <v>187</v>
+      </c>
+      <c r="E93" t="s">
+        <v>188</v>
+      </c>
+      <c r="F93" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>55</v>
+      </c>
+      <c r="B94" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>190</v>
+      </c>
+      <c r="E94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>191</v>
+      </c>
+      <c r="E95" t="s">
+        <v>63</v>
+      </c>
+      <c r="F95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>55</v>
+      </c>
+      <c r="B96" t="s">
+        <v>186</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" t="s">
+        <v>193</v>
+      </c>
+      <c r="F96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
         <v>14</v>
       </c>
-      <c r="D82" t="s">
-        <v>177</v>
-      </c>
-      <c r="E82" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="D97" t="s">
+        <v>195</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>197</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
+        <v>198</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" t="s">
+        <v>199</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="201">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -305,6 +305,9 @@
     <t>Party: Christine Nguyen</t>
   </si>
   <si>
+    <t>presented by | No phone or email in the record. | Also presenter on 1 other project in our register: 1 in Anaheim.</t>
+  </si>
+  <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
   </si>
   <si>
@@ -494,7 +497,7 @@
     <t>Party: Kaempfer Crowell</t>
   </si>
   <si>
-    <t>representative | Jennifer Lazovich | No phone or email in the record.</t>
+    <t>representative | Jennifer Lazovich | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
   </si>
   <si>
     <t>Party: Jennifer Lazovich</t>
@@ -1806,10 +1809,10 @@
         <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,10 +1826,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>95</v>
@@ -1843,13 +1846,13 @@
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,13 +1866,13 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,13 +1886,13 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1903,13 +1906,13 @@
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,13 +1926,13 @@
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,10 +1946,10 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F53" t="s">
         <v>95</v>
@@ -1963,13 +1966,13 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1983,10 +1986,10 @@
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F55" t="s">
         <v>36</v>
@@ -1997,13 +2000,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
         <v>82</v>
@@ -2017,13 +2020,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s">
         <v>82</v>
@@ -2037,19 +2040,19 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E58" t="s">
         <v>61</v>
       </c>
       <c r="F58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2057,19 +2060,19 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2077,19 +2080,19 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2097,19 +2100,19 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E61" t="s">
         <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2117,13 +2120,13 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s">
         <v>13</v>
@@ -2137,19 +2140,19 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2157,19 +2160,19 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E64" t="s">
         <v>82</v>
       </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2177,13 +2180,13 @@
         <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E65" t="s">
         <v>82</v>
@@ -2197,19 +2200,19 @@
         <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
         <v>63</v>
       </c>
       <c r="F66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2217,19 +2220,19 @@
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2237,16 +2240,16 @@
         <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F68" t="s">
         <v>43</v>
@@ -2257,16 +2260,16 @@
         <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" t="s">
         <v>144</v>
-      </c>
-      <c r="E69" t="s">
-        <v>143</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -2277,13 +2280,13 @@
         <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E70" t="s">
         <v>61</v>
@@ -2297,13 +2300,13 @@
         <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E71" t="s">
         <v>13</v>
@@ -2317,16 +2320,16 @@
         <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -2337,13 +2340,13 @@
         <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E73" t="s">
         <v>61</v>
@@ -2357,13 +2360,13 @@
         <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
         <v>13</v>
@@ -2377,16 +2380,16 @@
         <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
@@ -2397,13 +2400,13 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E76" t="s">
         <v>61</v>
@@ -2417,13 +2420,13 @@
         <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E77" t="s">
         <v>13</v>
@@ -2437,16 +2440,16 @@
         <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -2457,13 +2460,13 @@
         <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E79" t="s">
         <v>61</v>
@@ -2477,16 +2480,16 @@
         <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F80" t="s">
         <v>40</v>
@@ -2497,16 +2500,16 @@
         <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E81" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F81" t="s">
         <v>40</v>
@@ -2517,16 +2520,16 @@
         <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
         <v>40</v>
@@ -2537,16 +2540,16 @@
         <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -2557,19 +2560,19 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E84" t="s">
         <v>61</v>
       </c>
       <c r="F84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2577,19 +2580,19 @@
         <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
+        <v>170</v>
+      </c>
+      <c r="E85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85" t="s">
         <v>169</v>
-      </c>
-      <c r="E85" t="s">
-        <v>170</v>
-      </c>
-      <c r="F85" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2597,16 +2600,16 @@
         <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F86" t="s">
         <v>13</v>
@@ -2617,13 +2620,13 @@
         <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E87" t="s">
         <v>61</v>
@@ -2637,19 +2640,19 @@
         <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E88" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2657,16 +2660,16 @@
         <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F89" t="s">
         <v>34</v>
@@ -2677,19 +2680,19 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2697,16 +2700,16 @@
         <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>34</v>
@@ -2717,19 +2720,19 @@
         <v>55</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2737,19 +2740,19 @@
         <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E93" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F93" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2757,16 +2760,16 @@
         <v>55</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
@@ -2777,19 +2780,19 @@
         <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E95" t="s">
         <v>63</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -2797,24 +2800,24 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F96" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2823,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E97" t="s">
         <v>13</v>
@@ -2834,7 +2837,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -2843,7 +2846,7 @@
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E98" t="s">
         <v>13</v>
@@ -2854,7 +2857,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -2863,7 +2866,7 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E99" t="s">
         <v>13</v>
@@ -2874,7 +2877,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -2883,7 +2886,7 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
@@ -2894,7 +2897,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -2903,7 +2906,7 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E101" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="204">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -79,13 +79,13 @@
     <t>Headline finds</t>
   </si>
   <si>
-    <t xml:space="preserve">OCVibe: 4. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVIBE), that the property owner has complied in good faith with the terms and </t>
+    <t>OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
   </si>
   <si>
     <t>2026-07-13 | Anaheim</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
   </si>
   <si>
     <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
@@ -94,13 +94,13 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t xml:space="preserve">Disneyland Resort: 8. Determine that on the basis of the evidence submitted by Walt Disney Parks and Resorts U.S., Inc., that the property owner has complied in good faith with the terms and conditions of First Amended </t>
+    <t>Disneyland Resort: 8. Determinar que, sobre la base de la evidencia presentada por Walt Disney Parks and Resorts US, Inc., el propietario de la propiedad ha cumplido de buena fe con los términos y condiciones del Primer</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
   </si>
   <si>
     <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
@@ -109,13 +109,13 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
   </si>
   <si>
-    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement to Walt Disney Parks &amp; Resorts, U.S. Inc for underground communication lines</t>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
   </si>
   <si>
     <t>2026-01-23 | Central Florida Tourism Oversight District</t>
   </si>
   <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
   </si>
   <si>
     <t>Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
@@ -254,6 +254,9 @@
     <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
   </si>
   <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
     <t>Disneyland Resort</t>
   </si>
   <si>
@@ -284,6 +287,9 @@
     <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
   </si>
   <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
     <t>Platinum Triangle / PT Metro</t>
   </si>
   <si>
@@ -305,7 +311,7 @@
     <t>Party: Christine Nguyen</t>
   </si>
   <si>
-    <t>presented by | No phone or email in the record. | Also presenter on 1 other project in our register: 1 in Anaheim.</t>
+    <t>presented by; contact named in the record | CNguyen2@anaheim.net | Also presenter on 1 other project in our register: 1 in Anaheim.</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
@@ -338,7 +344,7 @@
     <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
   </si>
   <si>
-    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by)</t>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
   </si>
   <si>
     <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
@@ -365,7 +371,7 @@
     <t>2026-06-14. A City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
   </si>
   <si>
-    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by)</t>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_716824770c824daa2c4a8d0c4c4a6bf3.pdf&amp;view=1#item-h1711c29b4251</t>
@@ -437,10 +443,13 @@
     <t>Party: Sean Nicholas</t>
   </si>
   <si>
+    <t>presented by; contact named in the record | SNicholas@anaheim.net</t>
+  </si>
+  <si>
     <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
   </si>
   <si>
-    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by)</t>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
   </si>
   <si>
     <t>Liquor License - Fire N Ice Arena - District 2</t>
@@ -542,37 +551,37 @@
     <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
   </si>
   <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
     <t>Party: Craig Sandt</t>
   </si>
   <si>
     <t>presented by | Director of Construction Management | No phone or email in the record.</t>
   </si>
   <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
     <t>Party: Katherine Luetzow</t>
   </si>
   <si>
     <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
   </si>
   <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.36)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p36</t>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.45)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p45</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
   </si>
   <si>
     <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
     <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
   </si>
   <si>
     <t>500 North Casino Center Drive casino</t>
@@ -1612,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1620,16 +1629,16 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
@@ -1640,16 +1649,16 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="E38" t="s">
-        <v>82</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -1660,19 +1669,19 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
         <v>61</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1680,19 +1689,19 @@
         <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
         <v>86</v>
-      </c>
-      <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1700,16 +1709,16 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F41" t="s">
         <v>31</v>
@@ -1720,19 +1729,19 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
         <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,16 +1749,16 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F43" t="s">
         <v>36</v>
@@ -1760,16 +1769,16 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -1780,19 +1789,19 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1800,19 +1809,19 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1820,19 +1829,19 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1840,19 +1849,19 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1860,19 +1869,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1880,19 +1889,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E50" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1900,19 +1909,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E51" t="s">
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,19 +1929,19 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F52" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1940,19 +1949,19 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1960,19 +1969,19 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1980,16 +1989,16 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
         <v>36</v>
@@ -2000,16 +2009,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
         <v>53</v>
@@ -2020,16 +2029,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
@@ -2040,19 +2049,19 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E58" t="s">
         <v>61</v>
       </c>
       <c r="F58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2060,19 +2069,19 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2080,19 +2089,19 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,19 +2109,19 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E61" t="s">
         <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,13 +2129,13 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
         <v>13</v>
@@ -2140,19 +2149,19 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F63" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2160,19 +2169,19 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2180,16 +2189,16 @@
         <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E65" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -2200,19 +2209,19 @@
         <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" t="s">
+        <v>143</v>
+      </c>
+      <c r="F66" t="s">
         <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2220,19 +2229,19 @@
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E67" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F67" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2240,16 +2249,16 @@
         <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F68" t="s">
         <v>43</v>
@@ -2260,16 +2269,16 @@
         <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -2280,13 +2289,13 @@
         <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E70" t="s">
         <v>61</v>
@@ -2300,13 +2309,13 @@
         <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E71" t="s">
         <v>13</v>
@@ -2320,16 +2329,16 @@
         <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E72" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -2340,13 +2349,13 @@
         <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E73" t="s">
         <v>61</v>
@@ -2360,13 +2369,13 @@
         <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E74" t="s">
         <v>13</v>
@@ -2380,16 +2389,16 @@
         <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
@@ -2400,13 +2409,13 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
         <v>61</v>
@@ -2420,13 +2429,13 @@
         <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E77" t="s">
         <v>13</v>
@@ -2440,16 +2449,16 @@
         <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E78" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -2460,13 +2469,13 @@
         <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E79" t="s">
         <v>61</v>
@@ -2480,16 +2489,16 @@
         <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
         <v>40</v>
@@ -2500,16 +2509,16 @@
         <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E81" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F81" t="s">
         <v>40</v>
@@ -2520,16 +2529,16 @@
         <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E82" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F82" t="s">
         <v>40</v>
@@ -2540,16 +2549,16 @@
         <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E83" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -2560,19 +2569,19 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
         <v>61</v>
       </c>
       <c r="F84" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2580,19 +2589,19 @@
         <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F85" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2600,16 +2609,16 @@
         <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F86" t="s">
         <v>13</v>
@@ -2620,19 +2629,19 @@
         <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E87" t="s">
         <v>61</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2640,19 +2649,19 @@
         <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F88" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2660,19 +2669,19 @@
         <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
+        <v>182</v>
+      </c>
+      <c r="E89" t="s">
+        <v>183</v>
+      </c>
+      <c r="F89" t="s">
         <v>179</v>
-      </c>
-      <c r="E89" t="s">
-        <v>180</v>
-      </c>
-      <c r="F89" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2680,19 +2689,19 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2700,16 +2709,16 @@
         <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F91" t="s">
         <v>34</v>
@@ -2720,19 +2729,19 @@
         <v>55</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E92" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2740,19 +2749,19 @@
         <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E93" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F93" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2760,16 +2769,16 @@
         <v>55</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E94" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
@@ -2780,19 +2789,19 @@
         <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E95" t="s">
         <v>63</v>
       </c>
       <c r="F95" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,24 +2809,24 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
       </c>
       <c r="D96" t="s">
+        <v>196</v>
+      </c>
+      <c r="E96" t="s">
+        <v>197</v>
+      </c>
+      <c r="F96" t="s">
         <v>193</v>
-      </c>
-      <c r="E96" t="s">
-        <v>194</v>
-      </c>
-      <c r="F96" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2826,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E97" t="s">
         <v>13</v>
@@ -2837,7 +2846,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -2846,7 +2855,7 @@
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E98" t="s">
         <v>13</v>
@@ -2857,7 +2866,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -2866,7 +2875,7 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E99" t="s">
         <v>13</v>
@@ -2877,7 +2886,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -2886,7 +2895,7 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
@@ -2897,7 +2906,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -2906,7 +2915,7 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E101" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -506,13 +506,13 @@
     <t>Party: Kaempfer Crowell</t>
   </si>
   <si>
-    <t>representative | Jennifer Lazovich | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
+    <t>representative | Jennifer Lazovich | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
   </si>
   <si>
     <t>Party: Jennifer Lazovich</t>
   </si>
   <si>
-    <t>contact named in the record | Kaempfer Crowell | No phone or email in the record.</t>
+    <t>contact named in the record | Kaempfer Crowell | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record.</t>
   </si>
   <si>
     <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="248">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 13 projects, 56 records</t>
+    <t>Basis: 15 projects, 70 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -58,7 +58,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 56 captured records. Of those projects, 12 are described in full, selected by significance; 1 project filed nothing in this period. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 15 projects and 70 captured records. Of those projects, 14 are described in full, selected by significance; 1 project filed nothing in this period. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>What moved</t>
@@ -76,9 +76,30 @@
     <t>https://www.parksavers.com/new-disneylandforward/</t>
   </si>
   <si>
+    <t>Heart Hotel / Kulik River: stalled to approved</t>
+  </si>
+  <si>
+    <t>2026-07-24 | Clark County</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
+  </si>
+  <si>
     <t>Headline finds</t>
   </si>
   <si>
+    <t>PRESS</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+  </si>
+  <si>
     <t>OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
   </si>
   <si>
@@ -118,13 +139,16 @@
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
   </si>
   <si>
-    <t>Platinum Triangle / PT Metro: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+    <t xml:space="preserve">Platinum Triangle / PT Metro: 15. DEVELOPMENT AGREEMENT NO. 2005-00008 ADDENDUM NO. 4 TO PLATINUM TRIANGLE EXPANSION PROJECT MITIGATION MONITORING PLAN NO. 321 APPLICANT : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125, </t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
   </si>
   <si>
     <t xml:space="preserve">Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
@@ -134,7 +158,7 @@
     <t>2026-07-21 | Clark County</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110419</t>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110419</t>
   </si>
   <si>
     <t>Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
@@ -149,6 +173,15 @@
     <t xml:space="preserve">   Liquor License - Fire N Ice Arena - District 2</t>
   </si>
   <si>
+    <t>1475 South State College Boulevard: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+  </si>
+  <si>
     <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
   </si>
   <si>
@@ -164,231 +197,252 @@
     <t>2026-06-30 | Phoenix</t>
   </si>
   <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35482</t>
-  </si>
-  <si>
-    <t>OTR, an Ohio Partnership mixed-use development: 5. The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium. The Mixed-Use Medium land use designation allows for residential developme</t>
-  </si>
-  <si>
-    <t>2026-01-12 | Anaheim</t>
+    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
+  </si>
+  <si>
+    <t>By market</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
+    <t>Party: Disneyland</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
+  </si>
+  <si>
+    <t>2024-05-08. DisneylandForward Project</t>
+  </si>
+  <si>
+    <t>Players: Disneyland (applicant); City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
+  </si>
+  <si>
+    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
+  </si>
+  <si>
+    <t>$10,030,000</t>
+  </si>
+  <si>
+    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro</t>
+  </si>
+  <si>
+    <t>Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Records show 8 filings between 2025-01-13 and 2026-01-26.</t>
+  </si>
+  <si>
+    <t>Party: PT Metro</t>
+  </si>
+  <si>
+    <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Christine Nguyen</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | CNguyen2@anaheim.net | Also presenter on 1 other project in our register: 1 in Anaheim.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+  </si>
+  <si>
+    <t>Party: Joey Caucas</t>
+  </si>
+  <si>
+    <t>contact named in the record | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2025-01-13. Adoption of Ordinance No. 6601 amending multiple chapters of Title 18 (Zoning) of the Anaheim Municipal Code and adjustments to multiple specific plans</t>
+  </si>
+  <si>
+    <t>ORDINANCE No. 6601</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3305#item-h9b4b4aa880b3</t>
+  </si>
+  <si>
+    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, and adopt a new Environmental Justice Element; amendments to Title 18 (Zoning) of the Anaheim Municipal Code; Zoning Reclassification; amendments to the Platinum Triangle Master Land Use Plan...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_e5a905658061a35b9fb393c9f24d881a.pdf&amp;view=1#item-h0ec28bc385d7</t>
+  </si>
+  <si>
+    <t>2025-04-21. Adopt 2021-2029 Housing Element; update General Plan Land Use, Circulation, and Environmental Justice Elements; amend Title 18 (Zoning) of Anaheim Municipal Code; reclassify zoning; amend Platinum Triangle Master Land Use Plan; adjust Anaheim Canyon Specific Plan No. 2015-1 and Beach Boulevard Specific Plan No...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00002</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3384#item-h5b6c84ab98c9</t>
+  </si>
+  <si>
+    <t>2025-05-12. (Adoption) An ordinance of the city of anaheim; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
+  </si>
+  <si>
+    <t>ORDINANCE No. 6609</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
+  </si>
+  <si>
+    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
+  </si>
+  <si>
+    <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3461#item-h4e3dc2abd4c4</t>
+  </si>
+  <si>
+    <t>2025-12-15. Determine non-compliance with Amended and Restated Development Agreement and direct staff to provide notice of intent to establish new development timeframes</t>
+  </si>
+  <si>
+    <t>Players: PT Metro, LLC (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h4d8938c8638b</t>
+  </si>
+  <si>
+    <t>2026-01-26. Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>Contact: Joey Caucas. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>1475 South State College Boulevard</t>
+  </si>
+  <si>
+    <t>Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+  </si>
+  <si>
+    <t>Records show the development application amended more than once.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_716824770c824daa2c4a8d0c4c4a6bf3.pdf&amp;view=1#item-h1711c29b4251</t>
+  </si>
+  <si>
+    <t>2026-06-14. A City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
+  </si>
+  <si>
+    <t>2026-07-27. General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2026-00022</t>
+  </si>
+  <si>
+    <t>OTR, an Ohio Partnership</t>
+  </si>
+  <si>
+    <t>The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
   </si>
   <si>
-    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
-  </si>
-  <si>
-    <t>By market</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | under construction</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: City of Anaheim</t>
-  </si>
-  <si>
-    <t>presented by | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>Players: City of Anaheim (presented by)</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>PRESS</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 3 filings on the first amended and restated development agreement between 2025-06-16 and 2026-06-22.</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
-  </si>
-  <si>
-    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
-  </si>
-  <si>
-    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
-  </si>
-  <si>
-    <t>$10,030,000</t>
-  </si>
-  <si>
-    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
-  </si>
-  <si>
-    <t>Platinum Triangle / PT Metro</t>
-  </si>
-  <si>
-    <t>Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
-  </si>
-  <si>
-    <t>Records show 8 filings on the development application between 2025-04-21 and 2026-07-27.</t>
-  </si>
-  <si>
-    <t>Party: PT Metro</t>
-  </si>
-  <si>
-    <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t>Party: Christine Nguyen</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | CNguyen2@anaheim.net | Also presenter on 1 other project in our register: 1 in Anaheim.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
-  </si>
-  <si>
-    <t>Party: Joey Caucas</t>
-  </si>
-  <si>
-    <t>contact named in the record | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2025-04-21. Adopt 2021-2029 Housing Element; update General Plan Land Use, Circulation, and Environmental Justice Elements; amend Title 18 (Zoning) of Anaheim Municipal Code; reclassify zoning; amend Platinum Triangle Master Land Use Plan; adjust Anaheim Canyon Specific Plan No. 2015-1 and Beach Boulevard Specific Plan No...</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2021-00002</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3384#item-h5b6c84ab98c9</t>
-  </si>
-  <si>
-    <t>2025-05-12. (Adoption) An ordinance of the city of anaheim; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
-  </si>
-  <si>
-    <t>ORDINANCE No. 6609</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
-  </si>
-  <si>
-    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
-  </si>
-  <si>
-    <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3461#item-h4e3dc2abd4c4</t>
-  </si>
-  <si>
-    <t>2025-12-15. Determine non-compliance with Amended and Restated Development Agreement and direct staff to provide notice of intent to establish new development timeframes</t>
-  </si>
-  <si>
-    <t>Players: PT Metro, LLC (applicant)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h4d8938c8638b</t>
-  </si>
-  <si>
-    <t>2026-01-26. Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>Contact: Joey Caucas. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-06-14. A City-initiated General Plan Amendment to update the General Plan Land Use Element (including an amendment to Table LU-2), and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2026-00022 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_716824770c824daa2c4a8d0c4c4a6bf3.pdf&amp;view=1#item-h1711c29b4251</t>
-  </si>
-  <si>
-    <t>2026-07-27. General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2026-00022</t>
-  </si>
-  <si>
-    <t>OTR, an Ohio Partnership mixed-use development</t>
-  </si>
-  <si>
-    <t>The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
-  </si>
-  <si>
     <t>Records show the general plan amendment amended more than once.</t>
   </si>
   <si>
@@ -428,7 +482,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-h0d73a75a9eca</t>
   </si>
   <si>
-    <t>10 To The Beach Boulevard theme park</t>
+    <t>10 To The Beach Boulevard</t>
   </si>
   <si>
     <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
@@ -452,6 +506,132 @@
     <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
   </si>
   <si>
+    <t>Heart Hotel / Kulik River</t>
+  </si>
+  <si>
+    <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>Clark County | approved</t>
+  </si>
+  <si>
+    <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
+  </si>
+  <si>
+    <t>Party: Kulik River Capital, LLC</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
+  </si>
+  <si>
+    <t>Party: Nancy Amundsen</t>
+  </si>
+  <si>
+    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4TH STREET, LAS VEGAS, NV 89101 | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
+  </si>
+  <si>
+    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
+  </si>
+  <si>
+    <t>VS-26-0218</t>
+  </si>
+  <si>
+    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
+  </si>
+  <si>
+    <t>UC-26-0219</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
+  </si>
+  <si>
+    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
+  </si>
+  <si>
+    <t>https://ggbmagazine.com/articles/las-vegas-approves-heart-shaped-casino-on-skyvue-site/</t>
+  </si>
+  <si>
+    <t>2026-07-24. Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>Mirage Propco casino</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-07-21.</t>
+  </si>
+  <si>
+    <t>Party: Mirage Propco, LLC</t>
+  </si>
+  <si>
+    <t>Party: Kaempfer Crowell</t>
+  </si>
+  <si>
+    <t>representative | Jennifer Lazovich | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
+  </si>
+  <si>
+    <t>Party: Jennifer Lazovich</t>
+  </si>
+  <si>
+    <t>contact named in the record | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-07-21. Design Review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
+  </si>
+  <si>
+    <t>DR-26-0313 | 76.93 acres | Contact: Jennifer Lazovich. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-04-14.</t>
+  </si>
+  <si>
+    <t>Party: Ruby Holdings, LLC</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+  </si>
+  <si>
+    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
+  </si>
+  <si>
+    <t>UC-26-0156</t>
+  </si>
+  <si>
     <t>Liquor License - Fire N Ice Arena - District 2</t>
   </si>
   <si>
@@ -491,54 +671,6 @@
     <t>2026-06-30. Payment Ordinance</t>
   </si>
   <si>
-    <t>Mirage Propco casino</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-07-21.</t>
-  </si>
-  <si>
-    <t>Clark County | approved</t>
-  </si>
-  <si>
-    <t>Party: Mirage Propco, LLC</t>
-  </si>
-  <si>
-    <t>Party: Kaempfer Crowell</t>
-  </si>
-  <si>
-    <t>representative | Jennifer Lazovich | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
-  </si>
-  <si>
-    <t>Party: Jennifer Lazovich</t>
-  </si>
-  <si>
-    <t>contact named in the record | Kaempfer Crowell | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-07-21. Design review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
-  </si>
-  <si>
-    <t>DR-26-0313 | 76.93 acres | Contact: Jennifer Lazovich, Kaempfer Crowell. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Ruby Holdings museum</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-04-14.</t>
-  </si>
-  <si>
-    <t>Party: Ruby Holdings, LLC</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
-  </si>
-  <si>
-    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
-  </si>
-  <si>
-    <t>UC-26-0156</t>
-  </si>
-  <si>
     <t>CFTOD / Walt Disney World</t>
   </si>
   <si>
@@ -566,10 +698,10 @@
     <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
   </si>
   <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.45)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p45</t>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.48)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p48</t>
   </si>
   <si>
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
@@ -1004,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1106,47 +1238,47 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1158,15 +1290,15 @@
         <v>27</v>
       </c>
       <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
         <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1175,10 +1307,10 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
@@ -1186,7 +1318,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1198,15 +1330,15 @@
         <v>32</v>
       </c>
       <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
         <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1215,10 +1347,10 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
         <v>35</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
@@ -1226,7 +1358,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1241,12 +1373,12 @@
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1255,18 +1387,18 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1275,18 +1407,18 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1295,18 +1427,18 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
         <v>44</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1315,18 +1447,18 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1335,18 +1467,18 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -1355,18 +1487,18 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
         <v>51</v>
-      </c>
-      <c r="E23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -1375,121 +1507,121 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
         <v>54</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
         <v>55</v>
       </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>57</v>
-      </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
         <v>56</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>59</v>
-      </c>
       <c r="E26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" t="s">
         <v>58</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
       <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
         <v>60</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>61</v>
-      </c>
-      <c r="F27" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
         <v>65</v>
       </c>
-      <c r="E29" t="s">
-        <v>66</v>
-      </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -1498,27 +1630,27 @@
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
         <v>69</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>70</v>
-      </c>
-      <c r="E31" t="s">
-        <v>13</v>
       </c>
       <c r="F31" t="s">
         <v>71</v>
@@ -1526,10 +1658,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -1538,81 +1670,81 @@
         <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
         <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
       </c>
       <c r="F35" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
         <v>79</v>
@@ -1626,50 +1758,50 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
         <v>81</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
         <v>82</v>
-      </c>
-      <c r="E37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
         <v>84</v>
-      </c>
-      <c r="E38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -1678,7 +1810,7 @@
         <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
         <v>86</v>
@@ -1686,50 +1818,50 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -1738,7 +1870,7 @@
         <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
         <v>91</v>
@@ -1746,610 +1878,610 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
         <v>92</v>
       </c>
-      <c r="C43" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43" t="s">
         <v>93</v>
-      </c>
-      <c r="E43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F43" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" t="s">
         <v>95</v>
       </c>
-      <c r="E45" t="s">
-        <v>96</v>
-      </c>
       <c r="F45" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E49" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="F49" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="F50" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F51" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F54" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
         <v>123</v>
       </c>
-      <c r="C58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" t="s">
-        <v>126</v>
-      </c>
       <c r="E58" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E59" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="F59" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="F61" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="E64" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F64" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B66" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
         <v>138</v>
       </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" t="s">
-        <v>142</v>
-      </c>
       <c r="E66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
         <v>146</v>
       </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" t="s">
-        <v>149</v>
-      </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" t="s">
         <v>150</v>
       </c>
-      <c r="E71" t="s">
-        <v>13</v>
-      </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
         <v>151</v>
       </c>
-      <c r="C72" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
         <v>152</v>
-      </c>
-      <c r="E72" t="s">
-        <v>147</v>
-      </c>
-      <c r="F72" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -2358,18 +2490,18 @@
         <v>153</v>
       </c>
       <c r="E73" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
@@ -2378,527 +2510,527 @@
         <v>154</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="F74" t="s">
-        <v>47</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E76" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F76" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" t="s">
         <v>158</v>
-      </c>
-      <c r="E77" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E79" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="F79" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F80" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E81" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="F81" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E82" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" t="s">
+        <v>174</v>
+      </c>
+      <c r="F83" t="s">
         <v>169</v>
-      </c>
-      <c r="C83" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" t="s">
-        <v>170</v>
-      </c>
-      <c r="E83" t="s">
-        <v>161</v>
-      </c>
-      <c r="F83" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E84" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E85" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E86" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E87" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="F87" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E88" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F88" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E89" t="s">
-        <v>183</v>
+        <v>13</v>
       </c>
       <c r="F89" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E91" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E92" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="F92" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E93" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F93" t="s">
-        <v>193</v>
+        <v>48</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E94" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E95" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="F95" t="s">
-        <v>193</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E96" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="F96" t="s">
-        <v>193</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E97" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E98" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E99" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -2906,21 +3038,481 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" t="s">
+        <v>209</v>
+      </c>
+      <c r="E101" t="s">
+        <v>68</v>
+      </c>
+      <c r="F101" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>62</v>
+      </c>
+      <c r="B102" t="s">
+        <v>206</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>62</v>
+      </c>
+      <c r="B103" t="s">
+        <v>211</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" t="s">
+        <v>207</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>62</v>
+      </c>
+      <c r="B104" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>213</v>
+      </c>
+      <c r="E104" t="s">
+        <v>68</v>
+      </c>
+      <c r="F104" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B105" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
+        <v>214</v>
+      </c>
+      <c r="E105" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>62</v>
+      </c>
+      <c r="B106" t="s">
+        <v>215</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" t="s">
+        <v>216</v>
+      </c>
+      <c r="E106" t="s">
+        <v>207</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>62</v>
+      </c>
+      <c r="B107" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>217</v>
+      </c>
+      <c r="E107" t="s">
+        <v>68</v>
+      </c>
+      <c r="F107" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>62</v>
+      </c>
+      <c r="B108" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" t="s">
+        <v>218</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" t="s">
+        <v>220</v>
+      </c>
+      <c r="E109" t="s">
+        <v>221</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" t="s">
+        <v>219</v>
+      </c>
+      <c r="C110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" t="s">
+        <v>222</v>
+      </c>
+      <c r="E110" t="s">
+        <v>68</v>
+      </c>
+      <c r="F110" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" t="s">
+        <v>219</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" t="s">
+        <v>226</v>
+      </c>
+      <c r="E112" t="s">
+        <v>227</v>
+      </c>
+      <c r="F112" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" t="s">
+        <v>219</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" t="s">
+        <v>228</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" t="s">
+        <v>219</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>230</v>
+      </c>
+      <c r="E114" t="s">
+        <v>231</v>
+      </c>
+      <c r="F114" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" t="s">
+        <v>219</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>232</v>
+      </c>
+      <c r="E115" t="s">
+        <v>233</v>
+      </c>
+      <c r="F115" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>62</v>
+      </c>
+      <c r="B116" t="s">
+        <v>234</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>235</v>
+      </c>
+      <c r="E116" t="s">
+        <v>236</v>
+      </c>
+      <c r="F116" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>62</v>
+      </c>
+      <c r="B117" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>238</v>
+      </c>
+      <c r="E117" t="s">
+        <v>236</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>62</v>
+      </c>
+      <c r="B118" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>239</v>
+      </c>
+      <c r="E118" t="s">
+        <v>70</v>
+      </c>
+      <c r="F118" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>62</v>
+      </c>
+      <c r="B119" t="s">
+        <v>234</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>240</v>
+      </c>
+      <c r="E119" t="s">
+        <v>241</v>
+      </c>
+      <c r="F119" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>242</v>
+      </c>
+      <c r="B120" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" t="s">
         <v>14</v>
       </c>
-      <c r="D101" t="s">
-        <v>203</v>
-      </c>
-      <c r="E101" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="D120" t="s">
+        <v>243</v>
+      </c>
+      <c r="E120" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" t="s">
+        <v>244</v>
+      </c>
+      <c r="E121" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" t="s">
+        <v>14</v>
+      </c>
+      <c r="D122" t="s">
+        <v>245</v>
+      </c>
+      <c r="E122" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" t="s">
+        <v>246</v>
+      </c>
+      <c r="E123" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>242</v>
+      </c>
+      <c r="B124" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" t="s">
+        <v>14</v>
+      </c>
+      <c r="D124" t="s">
+        <v>247</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="266">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -100,7 +100,7 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
   </si>
   <si>
-    <t>OCVibe: 4. Determinar sobre la base de la evidencia presentada por Anaheim Real Estate Partners, LLC, TS Anaheim, LLC y FCD, LLC (OCVIBE), que el propietario de la propiedad ha cumplido de buena fe con los té</t>
+    <t>OCVibe: Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVibe Site Master Plan project</t>
   </si>
   <si>
     <t>2026-07-13 | Anaheim</t>
@@ -115,7 +115,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>Disneyland Resort: 8. Determinar que, sobre la base de la evidencia presentada por Walt Disney Parks and Resorts US, Inc., el propietario de la propiedad ha cumplido de buena fe con los términos y condiciones del Primer</t>
+    <t>Disneyland Resort: Determination that the property owner has complied in good faith with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
@@ -139,7 +139,7 @@
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
   </si>
   <si>
-    <t xml:space="preserve">Platinum Triangle / PT Metro: 15. DEVELOPMENT AGREEMENT NO. 2005-00008 ADDENDUM NO. 4 TO PLATINUM TRIANGLE EXPANSION PROJECT MITIGATION MONITORING PLAN NO. 321 APPLICANT : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125, </t>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
   </si>
   <si>
     <t>2026-01-26 | Anaheim</t>
@@ -151,8 +151,7 @@
     <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
   </si>
   <si>
-    <t xml:space="preserve">Mirage Propco casino: DR-26-0313-MIRAGE PROPCO, LLC:
-DESIGN REVIEW for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino) on a portion of 76.93 acres in a CR (Commercial Resort) Zone. Generally located west of Las Vegas Boulevard South and south of Spring Mountain Road within Paradise.  TS/hw/cv  (For possible action)</t>
+    <t>Mirage Propco casino: DR-26-0313: Design Review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
   </si>
   <si>
     <t>2026-07-21 | Clark County</t>
@@ -161,7 +160,7 @@
     <t>https://clark.legistar.com/Legislation.aspx#matter-110419</t>
   </si>
   <si>
-    <t>Liquor License - Fire N Ice Arena - District 2: Liquor License - Fire N Ice Arena - District 2</t>
+    <t>Fire N Ice Arena: Liquor License</t>
   </si>
   <si>
     <t>2026-06-16 | Phoenix</t>
@@ -173,7 +172,7 @@
     <t xml:space="preserve">   Liquor License - Fire N Ice Arena - District 2</t>
   </si>
   <si>
-    <t>1475 South State College Boulevard: 16. DEVELOPMENT APPLICATION NO. 2026-00022 (DEV2026-00022) GENERAL PLAN AMENDMENT TO THE LAND USE ELEMENT ADJUSTMENT NO. 17 TO THE FESTIVAL SPECIFIC PLAN NO. 90-1 ADJUSTMENT NO. 5 TO THE MOUNTAIN PARK</t>
+    <t>1475 South State College Boulevard: DEVELOPMENT APPLICATION No. 2026-00022: General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
@@ -182,7 +181,7 @@
     <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
   </si>
   <si>
-    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900): ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900) - Citywide</t>
+    <t>Tohono O'odham Nation Tribal 2025 Gaming Grants: Ordinance adoption for tribal 2025 gaming grants</t>
   </si>
   <si>
     <t>2026-05-19 | Phoenix</t>
@@ -191,7 +190,7 @@
     <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
   </si>
   <si>
-    <t>Children's Museum of Phoenix: Children's Museum of Phoenix</t>
+    <t>Children's Museum of Phoenix: Payment Ordinance</t>
   </si>
   <si>
     <t>2026-06-30 | Phoenix</t>
@@ -200,7 +199,52 @@
     <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
   </si>
   <si>
-    <t>By market</t>
+    <t>OTR, an Ohio Partnership: General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>2026-01-12 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum: UC-26-0156: Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
+  </si>
+  <si>
+    <t>2026-04-14 | Clark County</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+  </si>
+  <si>
+    <t>500 North Casino Center Drive: Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to Westar architectural group nevada, INC</t>
+  </si>
+  <si>
+    <t>2025-10-15 | Las Vegas</t>
+  </si>
+  <si>
+    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization...</t>
+  </si>
+  <si>
+    <t>10 To The Beach Boulevard: DEVELOPMENT APPLICATION No. 2025-00041: City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
+  </si>
+  <si>
+    <t>2025-11-16 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
   </si>
   <si>
     <t>OCVibe</t>
@@ -317,6 +361,108 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
   </si>
   <si>
+    <t>10 To The Beach Boulevard</t>
+  </si>
+  <si>
+    <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2025-11-16.</t>
+  </si>
+  <si>
+    <t>Party: Sean Nicholas</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | SNicholas@anaheim.net</t>
+  </si>
+  <si>
+    <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-04-14.</t>
+  </si>
+  <si>
+    <t>Clark County | approved</t>
+  </si>
+  <si>
+    <t>Party: Ruby Holdings, LLC</t>
+  </si>
+  <si>
+    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
+  </si>
+  <si>
+    <t>UC-26-0156</t>
+  </si>
+  <si>
+    <t>Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-30.</t>
+  </si>
+  <si>
+    <t>Phoenix | approved</t>
+  </si>
+  <si>
+    <t>Party: Children's Museum of Phoenix</t>
+  </si>
+  <si>
+    <t>2026-06-30. Payment Ordinance</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World</t>
+  </si>
+  <si>
+    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | under construction</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
+    <t>Party: Craig Sandt</t>
+  </si>
+  <si>
+    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Katherine Luetzow</t>
+  </si>
+  <si>
+    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.48)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p48</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
+  </si>
+  <si>
+    <t>Mixed-Use/Real Estate</t>
+  </si>
+  <si>
     <t>Platinum Triangle / PT Metro</t>
   </si>
   <si>
@@ -440,9 +586,6 @@
     <t>The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
-  </si>
-  <si>
     <t>Records show the general plan amendment amended more than once.</t>
   </si>
   <si>
@@ -482,28 +625,25 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-h0d73a75a9eca</t>
   </si>
   <si>
-    <t>10 To The Beach Boulevard</t>
-  </si>
-  <si>
-    <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2025-11-16.</t>
-  </si>
-  <si>
-    <t>Party: Sean Nicholas</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | SNicholas@anaheim.net</t>
-  </si>
-  <si>
-    <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Fire N Ice Arena</t>
+  </si>
+  <si>
+    <t>Liquor License - Fire N Ice Arena - District 2</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-06-16.</t>
+  </si>
+  <si>
+    <t>Party: Fire N Ice Arena</t>
+  </si>
+  <si>
+    <t>2026-06-16. Liquor License</t>
+  </si>
+  <si>
+    <t>Hospitality/Tourism</t>
   </si>
   <si>
     <t>Heart Hotel / Kulik River</t>
@@ -512,9 +652,6 @@
     <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
   </si>
   <si>
-    <t>Clark County | approved</t>
-  </si>
-  <si>
     <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
   </si>
   <si>
@@ -527,7 +664,7 @@
     <t>Party: Nancy Amundsen</t>
   </si>
   <si>
-    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4TH STREET, LAS VEGAS, NV 89101 | No phone or email in the record.</t>
+    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
   </si>
   <si>
     <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
@@ -599,13 +736,13 @@
     <t>Party: Kaempfer Crowell</t>
   </si>
   <si>
-    <t>representative | Jennifer Lazovich | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
+    <t>representative | Jennifer Lazovich | 1980 Festival Plaza Drive #650, Las Vegas, NV 89135 | No phone or email in the record. | Also representative on 1 other project in our register: 1 in Clark County.</t>
   </si>
   <si>
     <t>Party: Jennifer Lazovich</t>
   </si>
   <si>
-    <t>contact named in the record | 1980 FESTIVAL PLAZA DRIVE #650, LAS VEGAS, NV 89135 | No phone or email in the record.</t>
+    <t>contact named in the record | 1980 Festival Plaza Drive #650, Las Vegas, NV 89135 | No phone or email in the record.</t>
   </si>
   <si>
     <t>2026-07-21. Design Review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
@@ -614,40 +751,7 @@
     <t>DR-26-0313 | 76.93 acres | Contact: Jennifer Lazovich. No phone or email in the record.</t>
   </si>
   <si>
-    <t>Ruby Holdings museum</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-04-14.</t>
-  </si>
-  <si>
-    <t>Party: Ruby Holdings, LLC</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
-  </si>
-  <si>
-    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
-  </si>
-  <si>
-    <t>UC-26-0156</t>
-  </si>
-  <si>
-    <t>Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>Phoenix | approved</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-06-16.</t>
-  </si>
-  <si>
-    <t>Party: Fire N Ice Arena</t>
-  </si>
-  <si>
-    <t>2026-06-16. Liquor License</t>
-  </si>
-  <si>
-    <t>ADD-ON - Tohono O'odham Nation Tribal 2025 Gaming Grants (Ordinance S-52900)</t>
+    <t>Tohono O'odham Nation Tribal 2025 Gaming Grants</t>
   </si>
   <si>
     <t>Records show 1 filing, dated 2026-05-19.</t>
@@ -659,64 +763,7 @@
     <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
   </si>
   <si>
-    <t>Children's Museum of Phoenix</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-06-30.</t>
-  </si>
-  <si>
-    <t>Party: Children's Museum of Phoenix</t>
-  </si>
-  <si>
-    <t>2026-06-30. Payment Ordinance</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World</t>
-  </si>
-  <si>
-    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | under construction</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
-  </si>
-  <si>
-    <t>Party: Craig Sandt</t>
-  </si>
-  <si>
-    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Katherine Luetzow</t>
-  </si>
-  <si>
-    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.48)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p48</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
-  </si>
-  <si>
-    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
-  </si>
-  <si>
-    <t>500 North Casino Center Drive casino</t>
+    <t>500 North Casino Center Drive</t>
   </si>
   <si>
     <t>Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization...</t>
@@ -725,9 +772,6 @@
     <t>Las Vegas | approved</t>
   </si>
   <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
-  </si>
-  <si>
     <t>Records show 1 filing, dated 2025-10-15.</t>
   </si>
   <si>
@@ -753,6 +797,15 @@
   </si>
   <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
+  </si>
+  <si>
+    <t>1 further project in scope had no filing captured during July 2026, so it is not described in any category section. It remains on the register.</t>
+  </si>
+  <si>
+    <t>10 further filings on the projects described are in scope but not printed, because each project shows its most recent filings only.</t>
+  </si>
+  <si>
+    <t>15 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
   </si>
   <si>
     <t>Records are captured from published sources. A matter that has not been published, or that is published somewhere we do not yet capture, will not appear.</t>
@@ -1136,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1578,70 +1631,70 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" t="s">
+      <c r="E28" t="s">
         <v>63</v>
       </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>64</v>
-      </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
       </c>
       <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
         <v>67</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>68</v>
-      </c>
-      <c r="F30" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -1658,10 +1711,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -1670,7 +1723,7 @@
         <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>71</v>
@@ -1678,19 +1731,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
       </c>
       <c r="D33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" t="s">
         <v>74</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
       </c>
       <c r="F33" t="s">
         <v>75</v>
@@ -1698,13 +1751,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
         <v>76</v>
@@ -1713,24 +1766,24 @@
         <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
@@ -1738,79 +1791,79 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F36" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="F39" t="s">
         <v>86</v>
@@ -1818,159 +1871,159 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
         <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F47" t="s">
         <v>38</v>
@@ -1978,99 +2031,99 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E49" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F52" t="s">
         <v>108</v>
@@ -2078,50 +2131,50 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E53" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
@@ -2130,18 +2183,18 @@
         <v>114</v>
       </c>
       <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
         <v>115</v>
-      </c>
-      <c r="F55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
@@ -2150,147 +2203,147 @@
         <v>117</v>
       </c>
       <c r="E56" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F56" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F58" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="F59" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F60" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="F61" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E63" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -2298,699 +2351,699 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
         <v>132</v>
       </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>106</v>
-      </c>
       <c r="E64" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F64" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="F65" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E67" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F67" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>139</v>
+      </c>
+      <c r="E68" t="s">
         <v>140</v>
       </c>
-      <c r="C68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" t="s">
-        <v>143</v>
-      </c>
-      <c r="E68" t="s">
-        <v>65</v>
-      </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="F69" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E70" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="F72" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F73" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F74" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E75" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="F75" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>155</v>
+      </c>
+      <c r="E76" t="s">
         <v>156</v>
       </c>
-      <c r="C76" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" t="s">
-        <v>159</v>
-      </c>
-      <c r="E76" t="s">
-        <v>65</v>
-      </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E77" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F77" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
       </c>
       <c r="D78" t="s">
+        <v>160</v>
+      </c>
+      <c r="E78" t="s">
+        <v>161</v>
+      </c>
+      <c r="F78" t="s">
         <v>162</v>
-      </c>
-      <c r="E78" t="s">
-        <v>163</v>
-      </c>
-      <c r="F78" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B79" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" t="s">
+        <v>163</v>
+      </c>
+      <c r="E79" t="s">
         <v>164</v>
       </c>
-      <c r="C79" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="F79" t="s">
         <v>165</v>
-      </c>
-      <c r="E79" t="s">
-        <v>166</v>
-      </c>
-      <c r="F79" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
+        <v>166</v>
+      </c>
+      <c r="E80" t="s">
         <v>167</v>
       </c>
-      <c r="E80" t="s">
-        <v>166</v>
-      </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E81" t="s">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="F81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F82" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E83" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="F85" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B86" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E86" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="F86" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E87" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="F87" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B88" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="E88" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="F88" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E89" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
       <c r="F89" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E90" t="s">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="F90" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B91" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E91" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B92" t="s">
+        <v>189</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
         <v>191</v>
       </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" t="s">
-        <v>193</v>
-      </c>
       <c r="E92" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F92" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B93" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E93" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="F93" t="s">
-        <v>48</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
       </c>
       <c r="D94" t="s">
+        <v>194</v>
+      </c>
+      <c r="E94" t="s">
+        <v>195</v>
+      </c>
+      <c r="F94" t="s">
         <v>196</v>
-      </c>
-      <c r="E94" t="s">
-        <v>197</v>
-      </c>
-      <c r="F94" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" t="s">
         <v>198</v>
       </c>
-      <c r="E95" t="s">
-        <v>199</v>
-      </c>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B96" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
         <v>200</v>
-      </c>
-      <c r="C96" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" t="s">
-        <v>201</v>
-      </c>
-      <c r="E96" t="s">
-        <v>166</v>
-      </c>
-      <c r="F96" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E97" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F97" t="s">
-        <v>203</v>
+        <v>64</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B98" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E98" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F98" t="s">
         <v>203</v>
@@ -2998,10 +3051,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -3010,7 +3063,7 @@
         <v>206</v>
       </c>
       <c r="E99" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="F99" t="s">
         <v>51</v>
@@ -3018,19 +3071,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="B100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E100" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -3038,19 +3091,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E101" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F101" t="s">
         <v>51</v>
@@ -3058,16 +3111,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E102" t="s">
         <v>13</v>
@@ -3078,47 +3131,47 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B103" t="s">
         <v>211</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
         <v>212</v>
       </c>
       <c r="E103" t="s">
-        <v>207</v>
+        <v>125</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s">
         <v>211</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
         <v>213</v>
       </c>
       <c r="E104" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="F104" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B105" t="s">
         <v>211</v>
@@ -3130,307 +3183,307 @@
         <v>214</v>
       </c>
       <c r="E105" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="F105" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D106" t="s">
         <v>216</v>
       </c>
       <c r="E106" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B107" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>219</v>
+      </c>
+      <c r="E107" t="s">
+        <v>220</v>
+      </c>
+      <c r="F107" t="s">
         <v>215</v>
-      </c>
-      <c r="C107" t="s">
-        <v>17</v>
-      </c>
-      <c r="D107" t="s">
-        <v>217</v>
-      </c>
-      <c r="E107" t="s">
-        <v>68</v>
-      </c>
-      <c r="F107" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E108" t="s">
-        <v>13</v>
+        <v>222</v>
       </c>
       <c r="F108" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B109" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
-        <v>221</v>
+        <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E110" t="s">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="F110" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F111" t="s">
-        <v>41</v>
+        <v>230</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C112" t="s">
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E112" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F112" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E113" t="s">
         <v>13</v>
       </c>
       <c r="F113" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E114" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="F114" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D115" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E115" t="s">
-        <v>233</v>
+        <v>125</v>
       </c>
       <c r="F115" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B116" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E116" t="s">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="F116" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B117" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E117" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B118" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E118" t="s">
-        <v>70</v>
+        <v>243</v>
       </c>
       <c r="F118" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="B119" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C119" t="s">
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E119" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F119" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E120" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -3438,81 +3491,281 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C121" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E121" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="F121" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E122" t="s">
         <v>13</v>
       </c>
       <c r="F122" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>250</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E123" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="F123" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>250</v>
       </c>
       <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" t="s">
+        <v>253</v>
+      </c>
+      <c r="E124" t="s">
+        <v>252</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>210</v>
+      </c>
+      <c r="B125" t="s">
+        <v>250</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>254</v>
+      </c>
+      <c r="E125" t="s">
+        <v>85</v>
+      </c>
+      <c r="F125" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>210</v>
+      </c>
+      <c r="B126" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>255</v>
+      </c>
+      <c r="E126" t="s">
+        <v>256</v>
+      </c>
+      <c r="F126" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>257</v>
+      </c>
+      <c r="B127" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" t="s">
         <v>14</v>
       </c>
-      <c r="D124" t="s">
-        <v>247</v>
-      </c>
-      <c r="E124" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="D127" t="s">
+        <v>258</v>
+      </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>257</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" t="s">
+        <v>259</v>
+      </c>
+      <c r="E128" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129" t="s">
+        <v>260</v>
+      </c>
+      <c r="E129" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" t="s">
+        <v>261</v>
+      </c>
+      <c r="E130" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>257</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" t="s">
+        <v>262</v>
+      </c>
+      <c r="E131" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>257</v>
+      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" t="s">
+        <v>263</v>
+      </c>
+      <c r="E132" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>257</v>
+      </c>
+      <c r="B133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" t="s">
+        <v>264</v>
+      </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>257</v>
+      </c>
+      <c r="B134" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134" t="s">
+        <v>265</v>
+      </c>
+      <c r="E134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="248">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 15 projects, 70 records</t>
+    <t>Basis: 13 projects, 67 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -58,7 +58,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 15 projects and 70 captured records. Of those projects, 14 are described in full, selected by significance; 1 project filed nothing in this period. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 13 projects and 67 captured records. Of those projects, 12 are described in full, selected by significance; 1 project filed nothing in this period. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. A further 2 projects in this geography are excluded because our capture holds no published name for them; the coverage note says where. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>What moved</t>
@@ -100,13 +100,13 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
   </si>
   <si>
-    <t>OCVibe: Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVibe Site Master Plan project</t>
+    <t>OCVibe: Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
   </si>
   <si>
     <t>2026-07-13 | Anaheim</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
   </si>
   <si>
     <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
@@ -115,13 +115,13 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>Disneyland Resort: Determination that the property owner has complied in good faith with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
+    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
   </si>
   <si>
     <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
@@ -130,274 +130,292 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
   </si>
   <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
     <t>2026-01-23 | Central Florida Tourism Oversight District</t>
   </si>
   <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Mirage Propco casino: DR-26-0313: Design Review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
+  </si>
+  <si>
+    <t>2026-07-21 | Clark County</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110419</t>
+  </si>
+  <si>
+    <t>1475 South State College Boulevard: DEVELOPMENT APPLICATION No. 2026-00022: General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
+  </si>
+  <si>
+    <t>Children's Museum of Phoenix: Payment Ordinance</t>
+  </si>
+  <si>
+    <t>2026-06-30 | Phoenix</t>
+  </si>
+  <si>
+    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35482</t>
+  </si>
+  <si>
+    <t>OTR, an Ohio Partnership: General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>2026-01-12 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum: UC-26-0156: Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
+  </si>
+  <si>
+    <t>2026-04-14 | Clark County</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
+  </si>
+  <si>
+    <t>500 North Casino Center Drive: Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to Westar architectural group nevada, INC</t>
+  </si>
+  <si>
+    <t>2025-10-15 | Las Vegas</t>
+  </si>
+  <si>
+    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization...</t>
+  </si>
+  <si>
+    <t>10 To The Beach Boulevard: DEVELOPMENT APPLICATION No. 2025-00041: City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
+  </si>
+  <si>
+    <t>2025-11-16 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
+    <t>Party: Disneyland</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
+  </si>
+  <si>
+    <t>2024-05-08. DisneylandForward Project</t>
+  </si>
+  <si>
+    <t>Players: Disneyland (applicant); City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
+  </si>
+  <si>
+    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
+  </si>
+  <si>
+    <t>$10,030,000</t>
+  </si>
+  <si>
+    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+  </si>
+  <si>
+    <t>10 To The Beach Boulevard</t>
+  </si>
+  <si>
+    <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2025-11-16.</t>
+  </si>
+  <si>
+    <t>Party: Sean Nicholas</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | SNicholas@anaheim.net</t>
+  </si>
+  <si>
+    <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
+  </si>
+  <si>
+    <t>Ruby Holdings museum</t>
+  </si>
+  <si>
+    <t>Records show 1 filing, dated 2026-04-14.</t>
+  </si>
+  <si>
+    <t>Clark County | approved</t>
+  </si>
+  <si>
+    <t>Party: Ruby Holdings, LLC</t>
+  </si>
+  <si>
+    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
+  </si>
+  <si>
+    <t>UC-26-0156</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World</t>
+  </si>
+  <si>
+    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | under construction</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
+  </si>
+  <si>
+    <t>Party: Craig Sandt</t>
+  </si>
+  <si>
+    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
+  </si>
+  <si>
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
   </si>
   <si>
-    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>2026-01-26 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
-  </si>
-  <si>
-    <t>Mirage Propco casino: DR-26-0313: Design Review for a proposed theater expansion in conjunction with a previously approved resort hotel (Hard Rock Hotel &amp; Casino)</t>
-  </si>
-  <si>
-    <t>2026-07-21 | Clark County</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110419</t>
-  </si>
-  <si>
-    <t>Fire N Ice Arena: Liquor License</t>
-  </si>
-  <si>
-    <t>2026-06-16 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>1475 South State College Boulevard: DEVELOPMENT APPLICATION No. 2026-00022: General Plan Amendment to the Land Use Element, amendments to Title 18 (Zoning) of the Anaheim Municipal Code, and Sixth Cycle Housing Element Implementation</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;event_id=1858#item-h8c9905963a9f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development application no. 2026-00022 (DEV2026-00022) General plan amendment to the land use element adjustment no. 17 To the festival specific plan no. 90-1 Adjustment no. 5 To the mountain park spe...</t>
-  </si>
-  <si>
-    <t>Tohono O'odham Nation Tribal 2025 Gaming Grants: Ordinance adoption for tribal 2025 gaming grants</t>
-  </si>
-  <si>
-    <t>2026-05-19 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/gateway.aspx?M=l&amp;ID=35247</t>
-  </si>
-  <si>
-    <t>Children's Museum of Phoenix: Payment Ordinance</t>
-  </si>
-  <si>
-    <t>2026-06-30 | Phoenix</t>
-  </si>
-  <si>
-    <t>https://phoenix.legistar.com/Legislation.aspx#matter-35482</t>
-  </si>
-  <si>
-    <t>OTR, an Ohio Partnership: General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
-  </si>
-  <si>
-    <t>2026-01-12 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-hcbfb4c6155ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   The General Plan Amendment would change the land use designation within DA 5 from Regional Commercial to Mixed-Use Medium.</t>
-  </si>
-  <si>
-    <t>Ruby Holdings museum: UC-26-0156: Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
-  </si>
-  <si>
-    <t>2026-04-14 | Clark County</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:13a91c3e-05d2-48c5-bc38-a8b251f9bf46/original/as/Paradise-Minutes-041426.pdf#item-uc-26-0156</t>
-  </si>
-  <si>
-    <t>500 North Casino Center Drive: Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization to Westar architectural group nevada, INC</t>
-  </si>
-  <si>
-    <t>2025-10-15 | Las Vegas</t>
-  </si>
-  <si>
-    <t>https://lasvegas.primegov.com/Portal/Meeting?meetingTemplateId=41822#item-hb68c01f5db23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Approve award of Contract No. 260025-JG, Prime Design Services for Fire Administration Restrooms/Central Plant Modernization...</t>
-  </si>
-  <si>
-    <t>10 To The Beach Boulevard: DEVELOPMENT APPLICATION No. 2025-00041: City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
-  </si>
-  <si>
-    <t>2025-11-16 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h4787d3edccd4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
-  </si>
-  <si>
-    <t>Entertainment/Attractions</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: City of Anaheim</t>
-  </si>
-  <si>
-    <t>presented by | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>Players: City of Anaheim (presented by)</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
-  </si>
-  <si>
-    <t>Party: Disneyland</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
-  </si>
-  <si>
-    <t>2024-05-08. DisneylandForward Project</t>
-  </si>
-  <si>
-    <t>Players: Disneyland (applicant); City of Anaheim (presented by)</t>
-  </si>
-  <si>
-    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
-  </si>
-  <si>
-    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
-  </si>
-  <si>
-    <t>$10,030,000</t>
-  </si>
-  <si>
-    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
-  </si>
-  <si>
-    <t>10 To The Beach Boulevard</t>
-  </si>
-  <si>
-    <t>Development application no. 2025-00041, Adjustment no. 17 To the disneyland resort specific plan no. 92-1, Adjustment no. 15 To the anaheim resort specific plan no. 92-2...</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2025-11-16.</t>
-  </si>
-  <si>
-    <t>Party: Sean Nicholas</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | SNicholas@anaheim.net</t>
-  </si>
-  <si>
-    <t>2025-11-16. City-initiated amendment to Title 18 (Zoning) of the Anaheim Municipal Code modifying multiple chapters regarding zoning and development standards</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2025-00041 | Players: Sean Nicholas (presented by) | Contact: Sean Nicholas. SNicholas@anaheim.net.</t>
-  </si>
-  <si>
-    <t>Ruby Holdings museum</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-04-14.</t>
-  </si>
-  <si>
-    <t>Clark County | approved</t>
-  </si>
-  <si>
-    <t>Party: Ruby Holdings, LLC</t>
-  </si>
-  <si>
-    <t>2026-04-14. Use permits for museum and office as primary use; Waiver of development standards to reduce parking; Design review for proposed museum</t>
-  </si>
-  <si>
-    <t>UC-26-0156</t>
+    <t>Party: Katherine Luetzow</t>
+  </si>
+  <si>
+    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.38)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p38</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
   </si>
   <si>
     <t>Children's Museum of Phoenix</t>
@@ -415,51 +433,6 @@
     <t>2026-06-30. Payment Ordinance</t>
   </si>
   <si>
-    <t>CFTOD / Walt Disney World</t>
-  </si>
-  <si>
-    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | under construction</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
-  </si>
-  <si>
-    <t>Party: Craig Sandt</t>
-  </si>
-  <si>
-    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Katherine Luetzow</t>
-  </si>
-  <si>
-    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.48)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p48</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
-  </si>
-  <si>
-    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
-  </si>
-  <si>
     <t>Mixed-Use/Real Estate</t>
   </si>
   <si>
@@ -604,18 +577,18 @@
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_fe1740c90f9138140c46f84136727989.pdf&amp;view=1#item-h7d81d1e8a4e3</t>
   </si>
   <si>
+    <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
+  </si>
+  <si>
     <t>2025-12-15. Specific Plan Amendment to Specific Plan No. 90-1, General Plan Land Use Element Amendment, Final Site Plan approval for 447 multiple-family units, Development Agreement approval, and certification of Final Environmental Impact Report No. 358</t>
   </si>
   <si>
     <t>16.2 acres</t>
   </si>
   <si>
-    <t>2025-12-15. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-hcbfb4c6155ca</t>
-  </si>
-  <si>
     <t>2026-01-12. General Plan Amendment to change land use designation within DA 5 from Regional Commercial to Mixed-Use Medium</t>
   </si>
   <si>
@@ -625,24 +598,6 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3552#item-h0d73a75a9eca</t>
   </si>
   <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Fire N Ice Arena</t>
-  </si>
-  <si>
-    <t>Liquor License - Fire N Ice Arena - District 2</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-06-16.</t>
-  </si>
-  <si>
-    <t>Party: Fire N Ice Arena</t>
-  </si>
-  <si>
-    <t>2026-06-16. Liquor License</t>
-  </si>
-  <si>
     <t>Hospitality/Tourism</t>
   </si>
   <si>
@@ -658,7 +613,7 @@
     <t>Party: Kulik River Capital, LLC</t>
   </si>
   <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
   </si>
   <si>
     <t>Party: Nancy Amundsen</t>
@@ -667,22 +622,43 @@
     <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
   </si>
   <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
+  </si>
+  <si>
+    <t>UC-26-0219</t>
+  </si>
+  <si>
+    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
+  </si>
+  <si>
+    <t>TM-26-500056</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
     <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
   </si>
   <si>
-    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
-  </si>
-  <si>
-    <t>VS-26-0218</t>
-  </si>
-  <si>
-    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
-  </si>
-  <si>
-    <t>UC-26-0219</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
   </si>
   <si>
     <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
@@ -691,30 +667,6 @@
     <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
   </si>
   <si>
-    <t>2026-07-21. Holdover tentative map</t>
-  </si>
-  <si>
-    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
-  </si>
-  <si>
-    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
-  </si>
-  <si>
     <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
   </si>
   <si>
@@ -751,18 +703,6 @@
     <t>DR-26-0313 | 76.93 acres | Contact: Jennifer Lazovich. No phone or email in the record.</t>
   </si>
   <si>
-    <t>Tohono O'odham Nation Tribal 2025 Gaming Grants</t>
-  </si>
-  <si>
-    <t>Records show 1 filing, dated 2026-05-19.</t>
-  </si>
-  <si>
-    <t>Party: Tohono O'odham Nation</t>
-  </si>
-  <si>
-    <t>2026-05-19. Ordinance adoption for tribal 2025 gaming grants</t>
-  </si>
-  <si>
     <t>500 North Casino Center Drive</t>
   </si>
   <si>
@@ -799,13 +739,19 @@
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
   </si>
   <si>
+    <t>2 projects in scope are not named in this document because our capture holds no published name for them - only the agenda line the matter was filed under, which is the instrument rather than the project. They are on the register and can be named by hand. By market: Phoenix (2).</t>
+  </si>
+  <si>
     <t>1 further project in scope had no filing captured during July 2026, so it is not described in any category section. It remains on the register.</t>
   </si>
   <si>
     <t>10 further filings on the projects described are in scope but not printed, because each project shows its most recent filings only.</t>
   </si>
   <si>
-    <t>15 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
+    <t>14 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
+  </si>
+  <si>
+    <t>1 project in this geography holds no live record and is excluded: every record attached to it has been dismissed on review, so there is nothing to cite.</t>
   </si>
   <si>
     <t>Records are captured from published sources. A matter that has not been published, or that is published somewhere we do not yet capture, will not appear.</t>
@@ -1189,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1523,10 +1469,10 @@
         <v>49</v>
       </c>
       <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
         <v>50</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1540,13 +1486,13 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1560,10 +1506,10 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>53</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
       </c>
       <c r="F24" t="s">
         <v>54</v>
@@ -1583,10 +1529,10 @@
         <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1600,13 +1546,13 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
         <v>57</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,18 +1649,18 @@
         <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -1723,98 +1669,98 @@
         <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
         <v>73</v>
       </c>
-      <c r="E33" t="s">
-        <v>74</v>
-      </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
       </c>
       <c r="D34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" t="s">
         <v>76</v>
       </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
         <v>77</v>
       </c>
-      <c r="B35" t="s">
+      <c r="E35" t="s">
         <v>78</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>79</v>
-      </c>
-      <c r="E35" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
         <v>81</v>
       </c>
-      <c r="E36" t="s">
-        <v>80</v>
-      </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -1823,407 +1769,407 @@
         <v>82</v>
       </c>
       <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
         <v>83</v>
-      </c>
-      <c r="F37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
         <v>84</v>
       </c>
       <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
         <v>85</v>
-      </c>
-      <c r="F38" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
         <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
         <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F44" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
         <v>77</v>
       </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" t="s">
-        <v>104</v>
-      </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49" t="s">
         <v>102</v>
       </c>
-      <c r="C49" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" t="s">
-        <v>83</v>
-      </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E50" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F51" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E56" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
         <v>116</v>
-      </c>
-      <c r="C57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" t="s">
-        <v>80</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
@@ -2231,59 +2177,59 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E58" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="F58" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -2291,350 +2237,350 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
         <v>123</v>
       </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" t="s">
-        <v>126</v>
-      </c>
       <c r="E61" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
         <v>129</v>
       </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>132</v>
-      </c>
       <c r="E64" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E65" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>133</v>
+      </c>
+      <c r="E66" t="s">
         <v>134</v>
       </c>
-      <c r="C66" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" t="s">
-        <v>136</v>
-      </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
+        <v>136</v>
+      </c>
+      <c r="E67" t="s">
         <v>137</v>
       </c>
-      <c r="E67" t="s">
-        <v>83</v>
-      </c>
       <c r="F67" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E68" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="F68" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F70" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E72" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F72" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B73" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E73" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="F73" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
         <v>149</v>
       </c>
-      <c r="B74" t="s">
+      <c r="E74" t="s">
         <v>150</v>
       </c>
-      <c r="C74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" t="s">
-        <v>152</v>
-      </c>
-      <c r="E74" t="s">
-        <v>80</v>
-      </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
+        <v>151</v>
+      </c>
+      <c r="E75" t="s">
+        <v>152</v>
+      </c>
+      <c r="F75" t="s">
         <v>153</v>
-      </c>
-      <c r="E75" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
       </c>
       <c r="D76" t="s">
+        <v>154</v>
+      </c>
+      <c r="E76" t="s">
         <v>155</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>156</v>
-      </c>
-      <c r="F76" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
+        <v>157</v>
+      </c>
+      <c r="E77" t="s">
         <v>158</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>159</v>
-      </c>
-      <c r="F77" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -2651,10 +2597,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
@@ -2666,824 +2612,824 @@
         <v>164</v>
       </c>
       <c r="F79" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
+        <v>165</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
         <v>166</v>
-      </c>
-      <c r="E80" t="s">
-        <v>167</v>
-      </c>
-      <c r="F80" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
+        <v>167</v>
+      </c>
+      <c r="E81" t="s">
+        <v>168</v>
+      </c>
+      <c r="F81" t="s">
         <v>169</v>
-      </c>
-      <c r="E81" t="s">
-        <v>170</v>
-      </c>
-      <c r="F81" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E82" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F82" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F83" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="F84" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="F85" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="F86" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E87" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" t="s">
         <v>181</v>
       </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" t="s">
-        <v>155</v>
-      </c>
       <c r="E88" t="s">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="F88" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="F89" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="F90" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B91" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E91" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="F91" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B92" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>188</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
         <v>189</v>
-      </c>
-      <c r="C92" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" t="s">
-        <v>191</v>
-      </c>
-      <c r="E92" t="s">
-        <v>80</v>
-      </c>
-      <c r="F92" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E93" t="s">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="F93" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E94" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="F94" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F95" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="B96" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E96" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="F96" t="s">
-        <v>200</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="B97" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E97" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="F97" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E98" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="F98" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B99" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E99" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="F99" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>195</v>
+      </c>
+      <c r="B100" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
         <v>204</v>
       </c>
-      <c r="B100" t="s">
+      <c r="E100" t="s">
         <v>205</v>
       </c>
-      <c r="C100" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" t="s">
-        <v>207</v>
-      </c>
-      <c r="E100" t="s">
-        <v>131</v>
-      </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E101" t="s">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="F101" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B102" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
       </c>
       <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
         <v>209</v>
       </c>
-      <c r="E102" t="s">
-        <v>13</v>
-      </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
         <v>210</v>
       </c>
-      <c r="B103" t="s">
+      <c r="E103" t="s">
         <v>211</v>
       </c>
-      <c r="C103" t="s">
-        <v>17</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
         <v>212</v>
-      </c>
-      <c r="E103" t="s">
-        <v>125</v>
-      </c>
-      <c r="F103" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
         <v>213</v>
       </c>
       <c r="E104" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E105" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F105" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E106" t="s">
-        <v>217</v>
+        <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E107" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="F107" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B108" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E108" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="F108" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B109" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E109" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="F109" t="s">
-        <v>225</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>218</v>
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E111" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F111" t="s">
-        <v>230</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B112" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C112" t="s">
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E112" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F112" t="s">
-        <v>233</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B113" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E113" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>235</v>
+        <v>64</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B114" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E114" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="F114" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B115" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D115" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E115" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="F115" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B116" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E116" t="s">
-        <v>83</v>
+        <v>236</v>
       </c>
       <c r="F116" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B117" t="s">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E117" t="s">
-        <v>241</v>
+        <v>13</v>
       </c>
       <c r="F117" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B118" t="s">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E118" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="F118" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B119" t="s">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E119" t="s">
-        <v>245</v>
+        <v>13</v>
       </c>
       <c r="F119" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B120" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E120" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -3491,79 +3437,79 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E121" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B122" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E122" t="s">
         <v>13</v>
       </c>
       <c r="F122" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E123" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B124" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E124" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -3571,201 +3517,41 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B125" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E125" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F125" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B126" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E126" t="s">
-        <v>256</v>
+        <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>257</v>
-      </c>
-      <c r="B127" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" t="s">
-        <v>14</v>
-      </c>
-      <c r="D127" t="s">
-        <v>258</v>
-      </c>
-      <c r="E127" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>257</v>
-      </c>
-      <c r="B128" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" t="s">
-        <v>14</v>
-      </c>
-      <c r="D128" t="s">
-        <v>259</v>
-      </c>
-      <c r="E128" t="s">
-        <v>13</v>
-      </c>
-      <c r="F128" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>257</v>
-      </c>
-      <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" t="s">
-        <v>14</v>
-      </c>
-      <c r="D129" t="s">
-        <v>260</v>
-      </c>
-      <c r="E129" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>257</v>
-      </c>
-      <c r="B130" t="s">
-        <v>13</v>
-      </c>
-      <c r="C130" t="s">
-        <v>14</v>
-      </c>
-      <c r="D130" t="s">
-        <v>261</v>
-      </c>
-      <c r="E130" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>257</v>
-      </c>
-      <c r="B131" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" t="s">
-        <v>14</v>
-      </c>
-      <c r="D131" t="s">
-        <v>262</v>
-      </c>
-      <c r="E131" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>257</v>
-      </c>
-      <c r="B132" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" t="s">
-        <v>14</v>
-      </c>
-      <c r="D132" t="s">
-        <v>263</v>
-      </c>
-      <c r="E132" t="s">
-        <v>13</v>
-      </c>
-      <c r="F132" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>257</v>
-      </c>
-      <c r="B133" t="s">
-        <v>13</v>
-      </c>
-      <c r="C133" t="s">
-        <v>14</v>
-      </c>
-      <c r="D133" t="s">
-        <v>264</v>
-      </c>
-      <c r="E133" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>257</v>
-      </c>
-      <c r="B134" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" t="s">
-        <v>265</v>
-      </c>
-      <c r="E134" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="249">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -737,6 +737,9 @@
   </si>
   <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
+  </si>
+  <si>
+    <t>3 projects described above have a one-line description on our register that is not printed here. Those lines were written by a model reading the filings rather than quoted from one, so there is no document to cite for them and they are not offered as Philip's assessment either. The filings under each entry are unaffected.</t>
   </si>
   <si>
     <t>2 projects in scope are not named in this document because our capture holds no published name for them - only the agenda line the matter was filed under, which is the instrument rather than the project. They are on the register and can be named by hand. By market: Phoenix (2).</t>
@@ -1135,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3555,6 +3558,26 @@
         <v>13</v>
       </c>
     </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>237</v>
+      </c>
+      <c r="B127" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" t="s">
+        <v>248</v>
+      </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -733,7 +733,7 @@
     <t>The period is July 2026. Activity outside it is not included even where it concerns the same project.</t>
   </si>
   <si>
-    <t>Dormant projects are excluded from this report.</t>
+    <t>Dormant projects are excluded from this report. None in this geography is dormant.</t>
   </si>
   <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -19,13 +19,13 @@
     <t>Prepared for Simtec Attractions by Philip Kwong</t>
   </si>
   <si>
-    <t>Geography: Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World</t>
+    <t>Geography: United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World</t>
   </si>
   <si>
     <t>Period: July 2026</t>
   </si>
   <si>
-    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Waterpark | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Arena/Stadium | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
+    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
     <t>Basis: 0 projects, 0 records</t>
@@ -58,13 +58,13 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 0 projects and 0 captured records. Of those projects, 0 are described in full, selected by significance. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 0 projects and 0 captured records. Of those projects, 0 are described in full, selected by significance. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>Coverage note</t>
   </si>
   <si>
-    <t>Coverage is limited to Altamonte Springs, Anaheim, Atlanta, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World. Projects outside it exist in our register and are not reported here.</t>
+    <t>Coverage is limited to United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World. Projects outside it exist in our register and are not reported here.</t>
   </si>
   <si>
     <t>The period is July 2026. Activity outside it is not included even where it concerns the same project.</t>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="176">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 0 projects, 0 records</t>
+    <t>Basis: 5 projects, 53 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -58,7 +58,454 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 0 projects and 0 captured records. Of those projects, 0 are described in full, selected by significance. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. 9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
+  </si>
+  <si>
+    <t>Headline finds</t>
+  </si>
+  <si>
+    <t>PRESS</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>2026-07-24 | Clark County</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+  </si>
+  <si>
+    <t>OCVibe: Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVibe Site Master Plan project</t>
+  </si>
+  <si>
+    <t>2026-07-13 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
+  </si>
+  <si>
+    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+  </si>
+  <si>
+    <t>2026-06-22 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
+  </si>
+  <si>
+    <t>Party: Lisandro Orozco</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>Party: Stacy Tran</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | STran@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
+    <t>Party: Disneyland</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+  </si>
+  <si>
+    <t>2024-05-08. DisneylandForward Project</t>
+  </si>
+  <si>
+    <t>Players: Disneyland (applicant); City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
+    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
+  </si>
+  <si>
+    <t>$10,030,000</t>
+  </si>
+  <si>
+    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World</t>
+  </si>
+  <si>
+    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | under construction</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
+    <t>Party: Craig Sandt</t>
+  </si>
+  <si>
+    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Katherine Luetzow</t>
+  </si>
+  <si>
+    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.18)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p18</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
+  </si>
+  <si>
+    <t>Mixed-Use/Real Estate</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro</t>
+  </si>
+  <si>
+    <t>Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Records show 8 filings between 2025-01-13 and 2026-01-26.</t>
+  </si>
+  <si>
+    <t>Party: PT Metro</t>
+  </si>
+  <si>
+    <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Christine Nguyen</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | CNguyen2@anaheim.net | Also presenter on 2 other projects in our register: 2 in Anaheim.</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+  </si>
+  <si>
+    <t>Party: Joey Caucas</t>
+  </si>
+  <si>
+    <t>contact named in the record | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>2025-01-13. Adoption of Ordinance No. 6601 amending multiple chapters of Title 18 (Zoning) of the Anaheim Municipal Code and adjustments to multiple specific plans</t>
+  </si>
+  <si>
+    <t>ORDINANCE No. 6601</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3305#item-h9b4b4aa880b3</t>
+  </si>
+  <si>
+    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, and adopt a new Environmental Justice Element; amendments to Title 18 (Zoning) of the Anaheim Municipal Code; Zoning Reclassification; amendments to the Platinum Triangle Master Land Use Plan...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_e5a905658061a35b9fb393c9f24d881a.pdf&amp;view=1#item-h0ec28bc385d7</t>
+  </si>
+  <si>
+    <t>2025-04-21. Adopt 2021-2029 Housing Element; update General Plan Land Use, Circulation, and Environmental Justice Elements; amend Title 18 (Zoning) of Anaheim Municipal Code; reclassify zoning; amend Platinum Triangle Master Land Use Plan; adjust Anaheim Canyon Specific Plan No. 2015-1 and Beach Boulevard Specific Plan No...</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00002</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3384#item-h5b6c84ab98c9</t>
+  </si>
+  <si>
+    <t>2025-05-12. (Adoption) An ordinance of the city of anaheim; amending Chapters 18.06 (Multiple-Family Residential Zones), 18.10 (Industrial Zone), 18.14 (Public and Special-Purpose Zones), 1...</t>
+  </si>
+  <si>
+    <t>ORDINANCE No. 6609</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
+  </si>
+  <si>
+    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
+  </si>
+  <si>
+    <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3461#item-h4e3dc2abd4c4</t>
+  </si>
+  <si>
+    <t>2025-12-15. Determine non-compliance with Amended and Restated Development Agreement and direct staff to provide notice of intent to establish new development timeframes</t>
+  </si>
+  <si>
+    <t>Players: PT Metro, LLC (applicant)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3542#item-h4d8938c8638b</t>
+  </si>
+  <si>
+    <t>2026-01-26. Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>Contact: Joey Caucas. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Hospitality/Tourism</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River</t>
+  </si>
+  <si>
+    <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>Clark County | approved</t>
+  </si>
+  <si>
+    <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
+  </si>
+  <si>
+    <t>Party: Kulik River Capital, LLC</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110425</t>
+  </si>
+  <si>
+    <t>Party: Nancy Amundsen</t>
+  </si>
+  <si>
+    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Eli Applebaum</t>
+  </si>
+  <si>
+    <t>https://www.mundovideo.com.co/en/america/ballys-chicago-and-skyvue-casino-plans-to-advance-in-illinois-and-nevada/</t>
+  </si>
+  <si>
+    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
+  </si>
+  <si>
+    <t>TM-26-500056</t>
+  </si>
+  <si>
+    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
+  </si>
+  <si>
+    <t>UC-26-0219</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
+  </si>
+  <si>
+    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
+  </si>
+  <si>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
+  </si>
+  <si>
+    <t>https://ggbmagazine.com/articles/las-vegas-approves-heart-shaped-casino-on-skyvue-site/</t>
+  </si>
+  <si>
+    <t>2026-07-24. Las Vegas Topic Kulik River Capital</t>
   </si>
   <si>
     <t>Coverage note</t>
@@ -73,7 +520,19 @@
     <t>Dormant projects are excluded from this report. None in this geography is dormant.</t>
   </si>
   <si>
+    <t>9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Confirming them on the register and regenerating is what puts them in this document.</t>
+  </si>
+  <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
+  </si>
+  <si>
+    <t>1 project described above has a one-line description on our register that is not printed here. Those lines were written by a model reading the filings rather than quoted from one, so there is no document to cite for them and they are not offered as Philip's assessment either. The filings under each entry are unaffected.</t>
+  </si>
+  <si>
+    <t>10 further filings on the projects described are in scope but not printed, because each project shows its most recent filings only.</t>
+  </si>
+  <si>
+    <t>12 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
   </si>
   <si>
     <t>1 project in this geography holds no live record and is excluded: every record attached to it has been dismissed on review, so there is nothing to cite.</t>
@@ -460,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -548,16 +1007,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -568,16 +1027,16 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -588,16 +1047,16 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -608,16 +1067,16 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -628,16 +1087,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -648,15 +1107,1435 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>100</v>
+      </c>
+      <c r="F49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>106</v>
+      </c>
+      <c r="E52" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+      <c r="F54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" t="s">
+        <v>120</v>
+      </c>
+      <c r="E58" t="s">
+        <v>121</v>
+      </c>
+      <c r="F58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" t="s">
+        <v>104</v>
+      </c>
+      <c r="C59" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" t="s">
+        <v>123</v>
+      </c>
+      <c r="E59" t="s">
+        <v>124</v>
+      </c>
+      <c r="F59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>126</v>
+      </c>
+      <c r="E60" t="s">
+        <v>127</v>
+      </c>
+      <c r="F60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" t="s">
+        <v>128</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>103</v>
+      </c>
+      <c r="B62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" t="s">
+        <v>131</v>
+      </c>
+      <c r="F62" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>133</v>
+      </c>
+      <c r="E63" t="s">
+        <v>134</v>
+      </c>
+      <c r="F63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" t="s">
+        <v>138</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" t="s">
+        <v>140</v>
+      </c>
+      <c r="E66" t="s">
+        <v>47</v>
+      </c>
+      <c r="F66" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" t="s">
+        <v>142</v>
+      </c>
+      <c r="E67" t="s">
+        <v>143</v>
+      </c>
+      <c r="F67" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>144</v>
+      </c>
+      <c r="E68" t="s">
+        <v>113</v>
+      </c>
+      <c r="F68" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" t="s">
+        <v>146</v>
+      </c>
+      <c r="E69" t="s">
+        <v>147</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" t="s">
+        <v>149</v>
+      </c>
+      <c r="F70" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" t="s">
+        <v>154</v>
+      </c>
+      <c r="F72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
+        <v>157</v>
+      </c>
+      <c r="F73" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" t="s">
+        <v>160</v>
+      </c>
+      <c r="F74" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>162</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" t="s">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D77" t="s">
+        <v>166</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>167</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>168</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>170</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>172</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>165</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>175</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -424,7 +424,7 @@
     <t>Heart Hotel / Kulik River</t>
   </si>
   <si>
-    <t>Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+    <t>Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
   </si>
   <si>
     <t>Clark County | approved</t>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="175">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -58,7 +58,7 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 1 project whose every record has been dismissed is excluded entirely, because it has no filing to cite. 9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>Headline finds</t>
@@ -100,150 +100,153 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+    <t>Disneyland Resort: Determination that the property owner has complied in good faith with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
   </si>
   <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
+  </si>
+  <si>
+    <t>Party: Lisandro Orozco</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>Party: Stacy Tran</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | STran@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
   </si>
   <si>
-    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
-    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>2026-01-26 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
-  </si>
-  <si>
-    <t>Entertainment/Attractions</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
-  </si>
-  <si>
-    <t>Party: Lisandro Orozco</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
-  </si>
-  <si>
-    <t>Party: City of Anaheim</t>
-  </si>
-  <si>
-    <t>presented by | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>Party: Stacy Tran</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | STran@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>Players: City of Anaheim (presented by)</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
-  </si>
-  <si>
     <t>Party: Disneyland</t>
   </si>
   <si>
@@ -253,9 +256,6 @@
     <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
-  </si>
-  <si>
     <t>2024-05-08. DisneylandForward Project</t>
   </si>
   <si>
@@ -304,10 +304,10 @@
     <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
   </si>
   <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.18)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p18</t>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.38)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p38</t>
   </si>
   <si>
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
@@ -436,7 +436,7 @@
     <t>Party: Kulik River Capital, LLC</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110425</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
   </si>
   <si>
     <t>Party: Nancy Amundsen</t>
@@ -451,10 +451,13 @@
     <t>https://www.mundovideo.com.co/en/america/ballys-chicago-and-skyvue-casino-plans-to-advance-in-illinois-and-nevada/</t>
   </si>
   <si>
-    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
-  </si>
-  <si>
-    <t>TM-26-500056</t>
+    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
+  </si>
+  <si>
+    <t>VS-26-0218</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
   </si>
   <si>
     <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
@@ -466,39 +469,36 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
   </si>
   <si>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
     <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
   </si>
   <si>
     <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
   </si>
   <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
     <t>2026-07-21. Holdover tentative map</t>
   </si>
   <si>
     <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
-  </si>
-  <si>
-    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
-  </si>
-  <si>
     <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
   </si>
   <si>
@@ -533,9 +533,6 @@
   </si>
   <si>
     <t>12 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
-  </si>
-  <si>
-    <t>1 project in this geography holds no live record and is excluded: every record attached to it has been dismissed on review, so there is nothing to cite.</t>
   </si>
   <si>
     <t>Records are captured from published sources. A matter that has not been published, or that is published somewhere we do not yet capture, will not appear.</t>
@@ -919,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1536,7 +1533,7 @@
         <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1550,13 +1547,13 @@
         <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1570,13 +1567,13 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1596,7 +1593,7 @@
         <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1616,7 +1613,7 @@
         <v>82</v>
       </c>
       <c r="F40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1676,7 +1673,7 @@
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2196,7 +2193,7 @@
         <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,13 +2207,13 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2227,16 +2224,16 @@
         <v>136</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2250,13 +2247,13 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E72" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2267,16 +2264,16 @@
         <v>136</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E73" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,13 +2287,13 @@
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F74" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2516,26 +2513,6 @@
         <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>165</v>
-      </c>
-      <c r="B86" t="s">
-        <v>13</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>175</v>
-      </c>
-      <c r="E86" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="176">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -100,162 +100,162 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>Disneyland Resort: Determination that the property owner has complied in good faith with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
+    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
   </si>
   <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
+  </si>
+  <si>
+    <t>Party: Lisandro Orozco</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
+  </si>
+  <si>
+    <t>Party: City of Anaheim</t>
+  </si>
+  <si>
+    <t>presented by | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>Party: Stacy Tran</t>
+  </si>
+  <si>
+    <t>presented by; contact named in the record | STran@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>Players: City of Anaheim (presented by)</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
+    <t>Party: Disneyland</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
+  </si>
+  <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
   </si>
   <si>
-    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
-    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>2026-01-26 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
-  </si>
-  <si>
-    <t>Entertainment/Attractions</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
-  </si>
-  <si>
-    <t>Party: Lisandro Orozco</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
-  </si>
-  <si>
-    <t>Party: City of Anaheim</t>
-  </si>
-  <si>
-    <t>presented by | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>Party: Stacy Tran</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the record | STran@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>Players: City of Anaheim (presented by)</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
-  </si>
-  <si>
-    <t>Party: Disneyland</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
-  </si>
-  <si>
     <t>2024-05-08. DisneylandForward Project</t>
   </si>
   <si>
@@ -436,37 +436,58 @@
     <t>Party: Kulik River Capital, LLC</t>
   </si>
   <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
+  </si>
+  <si>
+    <t>Party: Nancy Amundsen</t>
+  </si>
+  <si>
+    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Eli Applebaum</t>
+  </si>
+  <si>
+    <t>https://www.mundovideo.com.co/en/america/ballys-chicago-and-skyvue-casino-plans-to-advance-in-illinois-and-nevada/</t>
+  </si>
+  <si>
+    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
+  </si>
+  <si>
+    <t>VS-26-0218</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
+  </si>
+  <si>
+    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
+  </si>
+  <si>
+    <t>TM-26-500056</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
   </si>
   <si>
-    <t>Party: Nancy Amundsen</t>
-  </si>
-  <si>
-    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Eli Applebaum</t>
-  </si>
-  <si>
-    <t>https://www.mundovideo.com.co/en/america/ballys-chicago-and-skyvue-casino-plans-to-advance-in-illinois-and-nevada/</t>
-  </si>
-  <si>
-    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
-  </si>
-  <si>
-    <t>VS-26-0218</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
-  </si>
-  <si>
-    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards; design review</t>
-  </si>
-  <si>
-    <t>UC-26-0219</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
   </si>
   <si>
     <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
@@ -478,27 +499,6 @@
     <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
   </si>
   <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
-    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover tentative map</t>
-  </si>
-  <si>
-    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
     <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
   </si>
   <si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>2026-07-24. Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>Watch list</t>
   </si>
   <si>
     <t>Coverage note</t>
@@ -916,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1533,7 +1536,7 @@
         <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1547,13 +1550,13 @@
         <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1567,13 +1570,13 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,7 +1596,7 @@
         <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1613,7 +1616,7 @@
         <v>82</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1673,7 +1676,7 @@
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2213,7 +2216,7 @@
         <v>150</v>
       </c>
       <c r="F70" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2227,13 +2230,13 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" t="s">
         <v>152</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>153</v>
-      </c>
-      <c r="F71" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2247,13 +2250,13 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E72" t="s">
         <v>155</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>156</v>
-      </c>
-      <c r="F72" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2267,13 +2270,13 @@
         <v>17</v>
       </c>
       <c r="D73" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
         <v>158</v>
-      </c>
-      <c r="E73" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2287,13 +2290,13 @@
         <v>21</v>
       </c>
       <c r="D74" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" t="s">
         <v>160</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>161</v>
-      </c>
-      <c r="F74" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2344,21 +2347,21 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -2378,7 +2381,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2398,7 +2401,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2418,7 +2421,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2438,7 +2441,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -2458,7 +2461,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -2478,7 +2481,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2498,7 +2501,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2513,6 +2516,26 @@
         <v>13</v>
       </c>
       <c r="F85" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>175</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="178">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Period: July 2026</t>
   </si>
   <si>
-    <t>Filters: dormant excluded | context records included | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
+    <t>Filters: dormant excluded | context records included | stage: filed | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
     <t>Basis: 5 projects, 53 records</t>
@@ -58,12 +58,30 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 40 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>Headline finds</t>
   </si>
   <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>OCVibe: Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
+  </si>
+  <si>
+    <t>2026-07-13 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
+  </si>
+  <si>
     <t>PRESS</t>
   </si>
   <si>
@@ -76,94 +94,79 @@
     <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
   </si>
   <si>
-    <t>RECORD</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
   </si>
   <si>
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
   </si>
   <si>
-    <t>OCVibe: Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVibe Site Master Plan project</t>
-  </si>
-  <si>
-    <t>2026-07-13 | Anaheim</t>
+    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+  </si>
+  <si>
+    <t>2026-06-22 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
   </si>
   <si>
-    <t xml:space="preserve">   Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
-  </si>
-  <si>
-    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
-  </si>
-  <si>
-    <t>2026-06-22 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
-  </si>
-  <si>
-    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>2026-01-26 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
-  </si>
-  <si>
-    <t>Entertainment/Attractions</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
-  </si>
-  <si>
     <t>Party: Lisandro Orozco</t>
   </si>
   <si>
-    <t>presented by; contact named in the record | lorozco@anaheim.net</t>
+    <t>presented by; contact named in the filing | lorozco@anaheim.net</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
@@ -181,7 +184,7 @@
     <t>Party: Stacy Tran</t>
   </si>
   <si>
-    <t>presented by; contact named in the record | STran@anaheim.net</t>
+    <t>presented by; contact named in the filing | STran@anaheim.net</t>
   </si>
   <si>
     <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
@@ -229,9 +232,6 @@
     <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
   </si>
   <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3646#item-heb30443bfb8b</t>
-  </si>
-  <si>
     <t>Disneyland Resort</t>
   </si>
   <si>
@@ -292,22 +292,22 @@
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
   </si>
   <si>
+    <t>Party: Katherine Luetzow</t>
+  </si>
+  <si>
+    <t>presented by | Director, Planning &amp; Engineering Department: Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
     <t>Party: Craig Sandt</t>
   </si>
   <si>
     <t>presented by | Director of Construction Management | No phone or email in the record.</t>
   </si>
   <si>
-    <t>Party: Katherine Luetzow</t>
-  </si>
-  <si>
-    <t>presented by | Director, Planning &amp; Engineering Department, Public Works | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.38)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p38</t>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - recreation / tourist provisions (p.37)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p37</t>
   </si>
   <si>
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
@@ -319,7 +319,7 @@
     <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
-    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department, Public Works (presented by)</t>
+    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
   </si>
   <si>
     <t>Mixed-Use/Real Estate</t>
@@ -340,19 +340,22 @@
     <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
   </si>
   <si>
+    <t>Party: City of Anaheim Planning Staff</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+  </si>
+  <si>
     <t>Party: Christine Nguyen</t>
   </si>
   <si>
-    <t>presented by; contact named in the record | CNguyen2@anaheim.net | Also presenter on 2 other projects in our register: 2 in Anaheim.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
+    <t>contact named in the filing | CNguyen2@anaheim.net | Also presenter on 2 other projects in our register: 2 in Anaheim.</t>
   </si>
   <si>
     <t>Party: Joey Caucas</t>
   </si>
   <si>
-    <t>contact named in the record | No phone or email in the record.</t>
+    <t>contact named in the filing | No phone or email in the record.</t>
   </si>
   <si>
     <t>2025-01-13. Adoption of Ordinance No. 6601 amending multiple chapters of Title 18 (Zoning) of the Anaheim Municipal Code and adjustments to multiple specific plans</t>
@@ -364,7 +367,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3305#item-h9b4b4aa880b3</t>
   </si>
   <si>
-    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, and adopt a new Environmental Justice Element; amendments to Title 18 (Zoning) of the Anaheim Municipal Code; Zoning Reclassification; amendments to the Platinum Triangle Master Land Use Plan...</t>
+    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, adopt a new Environmental Justice Element, amend Title 18 (Zoning) of the Anaheim Municipal Code, reclassify zoning, and amend the Platinum Triangle Master Land Use Plan and specific plans...</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2021-00223</t>
@@ -391,10 +394,10 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
   </si>
   <si>
-    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: Christine Nguyen (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
+    <t>2025-08-10. General Plan Amendment and Zoning Code amendments related to implementation of the Sixth Cycle Housing Element, including updates to General Plan Land Use Element Table LU-2 and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: City of Anaheim Planning Staff (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
   </si>
   <si>
     <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
@@ -427,7 +430,7 @@
     <t>Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
   </si>
   <si>
-    <t>Clark County | approved</t>
+    <t>Clark County | filed</t>
   </si>
   <si>
     <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
@@ -442,22 +445,16 @@
     <t>Party: Nancy Amundsen</t>
   </si>
   <si>
-    <t>representative; contact named in the record | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
+    <t>representative; contact named in the filing | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
   </si>
   <si>
     <t>Party: Eli Applebaum</t>
   </si>
   <si>
-    <t>https://www.mundovideo.com.co/en/america/ballys-chicago-and-skyvue-casino-plans-to-advance-in-illinois-and-nevada/</t>
-  </si>
-  <si>
-    <t>2026-05-26. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street</t>
-  </si>
-  <si>
-    <t>VS-26-0218</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-vs-26-0218</t>
+    <t>named in press coverage | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://traveltomorrow.com/new-heart-shaped-hotel-approved-for-las-vegas-strip-sparks-debate-over-tacky-design/</t>
   </si>
   <si>
     <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
@@ -466,6 +463,39 @@
     <t>TM-26-500056</t>
   </si>
   <si>
+    <t>2026-05-26. Use Permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; Waiver of Development Standards for non-standard improvements in right-of-way; Design Review for proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
+  </si>
+  <si>
+    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
+  </si>
+  <si>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
+  </si>
+  <si>
     <t>2026-07-21. Holdover tentative map</t>
   </si>
   <si>
@@ -475,30 +505,6 @@
     <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
   </si>
   <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
-    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
-  </si>
-  <si>
-    <t>UC-26-0219 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
-  </si>
-  <si>
     <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
   </si>
   <si>
@@ -523,7 +529,7 @@
     <t>Dormant projects are excluded from this report. None in this geography is dormant.</t>
   </si>
   <si>
-    <t>9 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Confirming them on the register and regenerating is what puts them in this document.</t>
+    <t>40 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Confirming them on the register and regenerating is what puts them in this document.</t>
   </si>
   <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
@@ -919,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1027,16 +1033,16 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
         <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1047,7 +1053,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -1067,7 +1073,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -1087,7 +1093,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
@@ -1107,7 +1113,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -1127,7 +1133,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
@@ -1147,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -1167,7 +1173,7 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
@@ -1187,7 +1193,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
@@ -1196,7 +1202,7 @@
         <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1227,7 +1233,7 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
@@ -1236,7 +1242,7 @@
         <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1247,7 +1253,7 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -1256,7 +1262,7 @@
         <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1267,16 +1273,16 @@
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1287,16 +1293,16 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1307,16 +1313,16 @@
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1327,16 +1333,16 @@
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1347,16 +1353,16 @@
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
         <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1367,16 +1373,16 @@
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
         <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1387,16 +1393,16 @@
         <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1407,16 +1413,16 @@
         <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s">
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1427,16 +1433,16 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1447,16 +1453,16 @@
         <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1467,16 +1473,16 @@
         <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1487,7 +1493,7 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
         <v>74</v>
@@ -1527,7 +1533,7 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
@@ -1547,7 +1553,7 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
         <v>77</v>
@@ -1567,7 +1573,7 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
         <v>79</v>
@@ -1587,13 +1593,13 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
         <v>78</v>
@@ -1607,7 +1613,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
         <v>81</v>
@@ -1627,7 +1633,7 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
         <v>83</v>
@@ -1647,7 +1653,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
         <v>85</v>
@@ -1667,7 +1673,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
         <v>87</v>
@@ -1707,7 +1713,7 @@
         <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
         <v>91</v>
@@ -1727,7 +1733,7 @@
         <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
         <v>93</v>
@@ -1736,7 +1742,7 @@
         <v>94</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,7 +1753,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
         <v>95</v>
@@ -1756,7 +1762,7 @@
         <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1767,7 +1773,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
         <v>97</v>
@@ -1787,7 +1793,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
         <v>99</v>
@@ -1807,7 +1813,7 @@
         <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
         <v>101</v>
@@ -1827,7 +1833,7 @@
         <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
         <v>105</v>
@@ -1867,7 +1873,7 @@
         <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D53" t="s">
         <v>107</v>
@@ -1887,16 +1893,16 @@
         <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
         <v>109</v>
       </c>
       <c r="E54" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" t="s">
         <v>110</v>
-      </c>
-      <c r="F54" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,16 +1913,16 @@
         <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" t="s">
         <v>112</v>
       </c>
-      <c r="E55" t="s">
-        <v>113</v>
-      </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1927,16 +1933,16 @@
         <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
         <v>114</v>
       </c>
-      <c r="E56" t="s">
-        <v>115</v>
-      </c>
       <c r="F56" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1947,16 +1953,16 @@
         <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" t="s">
         <v>117</v>
-      </c>
-      <c r="E57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1967,16 +1973,16 @@
         <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" t="s">
         <v>120</v>
-      </c>
-      <c r="E58" t="s">
-        <v>121</v>
-      </c>
-      <c r="F58" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1987,16 +1993,16 @@
         <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" t="s">
         <v>123</v>
-      </c>
-      <c r="E59" t="s">
-        <v>124</v>
-      </c>
-      <c r="F59" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2007,16 +2013,16 @@
         <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
+        <v>124</v>
+      </c>
+      <c r="E60" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" t="s">
         <v>126</v>
-      </c>
-      <c r="E60" t="s">
-        <v>127</v>
-      </c>
-      <c r="F60" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2027,16 +2033,16 @@
         <v>104</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
+        <v>127</v>
+      </c>
+      <c r="E61" t="s">
         <v>128</v>
       </c>
-      <c r="E61" t="s">
-        <v>13</v>
-      </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,16 +2053,16 @@
         <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
         <v>130</v>
-      </c>
-      <c r="E62" t="s">
-        <v>131</v>
-      </c>
-      <c r="F62" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,213 +2073,213 @@
         <v>104</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" t="s">
+        <v>132</v>
+      </c>
+      <c r="F63" t="s">
         <v>133</v>
-      </c>
-      <c r="E63" t="s">
-        <v>134</v>
-      </c>
-      <c r="F63" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E64" t="s">
         <v>135</v>
       </c>
-      <c r="B64" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64" t="s">
-        <v>21</v>
-      </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
-      <c r="E64" t="s">
-        <v>138</v>
-      </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" t="s">
         <v>139</v>
       </c>
-      <c r="E65" t="s">
-        <v>138</v>
-      </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
         <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67" t="s">
+        <v>47</v>
+      </c>
+      <c r="F67" t="s">
         <v>142</v>
-      </c>
-      <c r="E67" t="s">
-        <v>143</v>
-      </c>
-      <c r="F67" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" t="s">
         <v>144</v>
       </c>
-      <c r="E68" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" t="s">
         <v>146</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>147</v>
-      </c>
-      <c r="F69" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" t="s">
         <v>149</v>
       </c>
-      <c r="E70" t="s">
-        <v>150</v>
-      </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
         <v>151</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>152</v>
-      </c>
-      <c r="F71" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" t="s">
         <v>154</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>155</v>
-      </c>
-      <c r="F72" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
         <v>157</v>
-      </c>
-      <c r="E73" t="s">
-        <v>13</v>
       </c>
       <c r="F73" t="s">
         <v>158</v>
@@ -2281,39 +2287,39 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
         <v>160</v>
-      </c>
-      <c r="F74" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
+        <v>161</v>
+      </c>
+      <c r="E75" t="s">
         <v>162</v>
-      </c>
-      <c r="E75" t="s">
-        <v>13</v>
       </c>
       <c r="F75" t="s">
         <v>163</v>
@@ -2321,13 +2327,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
         <v>164</v>
@@ -2336,72 +2342,72 @@
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2421,7 +2427,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2441,7 +2447,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -2461,7 +2467,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -2481,7 +2487,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2501,7 +2507,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2521,7 +2527,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -2536,6 +2542,46 @@
         <v>13</v>
       </c>
       <c r="F86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>176</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" t="s">
+        <v>177</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="179">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>presented by | Director, Planning &amp; Engineering Department: Public Works | No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-10-p4</t>
   </si>
   <si>
     <t>Party: Craig Sandt</t>
@@ -1742,7 +1745,7 @@
         <v>94</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,10 +1759,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F47" t="s">
         <v>36</v>
@@ -1776,13 +1779,13 @@
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E48" t="s">
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1796,10 +1799,10 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F49" t="s">
         <v>36</v>
@@ -1816,10 +1819,10 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s">
         <v>92</v>
@@ -1827,16 +1830,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
@@ -1847,16 +1850,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" t="s">
         <v>44</v>
@@ -1867,19 +1870,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -1887,59 +1890,59 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E54" t="s">
         <v>54</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" t="s">
         <v>111</v>
-      </c>
-      <c r="E55" t="s">
-        <v>112</v>
-      </c>
-      <c r="F55" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -1947,159 +1950,159 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E62" t="s">
         <v>13</v>
       </c>
       <c r="F62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
@@ -2107,19 +2110,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -2127,19 +2130,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
         <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>139</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -2147,79 +2150,79 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E67" t="s">
         <v>47</v>
       </c>
       <c r="F67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
+        <v>144</v>
+      </c>
+      <c r="E68" t="s">
+        <v>145</v>
+      </c>
+      <c r="F68" t="s">
         <v>143</v>
-      </c>
-      <c r="E68" t="s">
-        <v>144</v>
-      </c>
-      <c r="F68" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -2227,136 +2230,136 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F73" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E74" t="s">
         <v>13</v>
       </c>
       <c r="F74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F75" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E76" t="s">
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E77" t="s">
         <v>13</v>
@@ -2367,7 +2370,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -2387,7 +2390,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2407,7 +2410,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2416,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E80" t="s">
         <v>13</v>
@@ -2427,7 +2430,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2436,7 +2439,7 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -2447,7 +2450,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -2456,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -2467,7 +2470,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -2476,7 +2479,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E83" t="s">
         <v>13</v>
@@ -2487,7 +2490,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2496,7 +2499,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
@@ -2507,7 +2510,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2516,7 +2519,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -2527,7 +2530,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -2536,7 +2539,7 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -2547,7 +2550,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2556,7 +2559,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E87" t="s">
         <v>13</v>
@@ -2567,7 +2570,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -2576,7 +2579,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E88" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="178">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -296,9 +296,6 @@
   </si>
   <si>
     <t>presented by | Director, Planning &amp; Engineering Department: Public Works | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-10-p4</t>
   </si>
   <si>
     <t>Party: Craig Sandt</t>
@@ -1745,7 +1742,7 @@
         <v>94</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,10 +1756,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s">
         <v>96</v>
-      </c>
-      <c r="E47" t="s">
-        <v>97</v>
       </c>
       <c r="F47" t="s">
         <v>36</v>
@@ -1779,13 +1776,13 @@
         <v>17</v>
       </c>
       <c r="D48" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
         <v>98</v>
-      </c>
-      <c r="E48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,10 +1796,10 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
         <v>100</v>
-      </c>
-      <c r="E49" t="s">
-        <v>101</v>
       </c>
       <c r="F49" t="s">
         <v>36</v>
@@ -1819,10 +1816,10 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" t="s">
         <v>102</v>
-      </c>
-      <c r="E50" t="s">
-        <v>103</v>
       </c>
       <c r="F50" t="s">
         <v>92</v>
@@ -1830,16 +1827,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
         <v>104</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
         <v>105</v>
-      </c>
-      <c r="C51" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" t="s">
-        <v>106</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
@@ -1850,16 +1847,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" t="s">
         <v>104</v>
       </c>
-      <c r="B52" t="s">
-        <v>105</v>
-      </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
         <v>44</v>
@@ -1870,19 +1867,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" t="s">
         <v>104</v>
       </c>
-      <c r="B53" t="s">
-        <v>105</v>
-      </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" t="s">
         <v>108</v>
-      </c>
-      <c r="E53" t="s">
-        <v>109</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -1890,59 +1887,59 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
         <v>104</v>
       </c>
-      <c r="B54" t="s">
-        <v>105</v>
-      </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E54" t="s">
         <v>54</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
         <v>104</v>
       </c>
-      <c r="B55" t="s">
-        <v>105</v>
-      </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" t="s">
         <v>112</v>
       </c>
-      <c r="E55" t="s">
-        <v>113</v>
-      </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
         <v>104</v>
       </c>
-      <c r="B56" t="s">
-        <v>105</v>
-      </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
         <v>114</v>
-      </c>
-      <c r="E56" t="s">
-        <v>115</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -1950,159 +1947,159 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" t="s">
         <v>104</v>
       </c>
-      <c r="B57" t="s">
-        <v>105</v>
-      </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
         <v>116</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>117</v>
-      </c>
-      <c r="F57" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" t="s">
         <v>104</v>
       </c>
-      <c r="B58" t="s">
-        <v>105</v>
-      </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" t="s">
         <v>119</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>120</v>
-      </c>
-      <c r="F58" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" t="s">
         <v>104</v>
       </c>
-      <c r="B59" t="s">
-        <v>105</v>
-      </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" t="s">
         <v>122</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>123</v>
-      </c>
-      <c r="F59" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" t="s">
         <v>104</v>
       </c>
-      <c r="B60" t="s">
-        <v>105</v>
-      </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
+        <v>124</v>
+      </c>
+      <c r="E60" t="s">
         <v>125</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>126</v>
-      </c>
-      <c r="F60" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
         <v>104</v>
       </c>
-      <c r="B61" t="s">
-        <v>105</v>
-      </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
+        <v>127</v>
+      </c>
+      <c r="E61" t="s">
         <v>128</v>
       </c>
-      <c r="E61" t="s">
-        <v>129</v>
-      </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>103</v>
+      </c>
+      <c r="B62" t="s">
         <v>104</v>
       </c>
-      <c r="B62" t="s">
-        <v>105</v>
-      </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
         <v>130</v>
-      </c>
-      <c r="E62" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" t="s">
         <v>104</v>
       </c>
-      <c r="B63" t="s">
-        <v>105</v>
-      </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" t="s">
         <v>132</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>133</v>
-      </c>
-      <c r="F63" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
         <v>104</v>
       </c>
-      <c r="B64" t="s">
-        <v>105</v>
-      </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E64" t="s">
         <v>135</v>
-      </c>
-      <c r="E64" t="s">
-        <v>136</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
@@ -2110,19 +2107,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
         <v>137</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
         <v>138</v>
       </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>139</v>
-      </c>
-      <c r="E65" t="s">
-        <v>140</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -2130,19 +2127,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" t="s">
         <v>137</v>
       </c>
-      <c r="B66" t="s">
-        <v>138</v>
-      </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -2150,79 +2147,79 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" t="s">
         <v>137</v>
       </c>
-      <c r="B67" t="s">
-        <v>138</v>
-      </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
         <v>47</v>
       </c>
       <c r="F67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" t="s">
         <v>137</v>
       </c>
-      <c r="B68" t="s">
-        <v>138</v>
-      </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" t="s">
         <v>144</v>
       </c>
-      <c r="E68" t="s">
-        <v>145</v>
-      </c>
       <c r="F68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s">
         <v>137</v>
-      </c>
-      <c r="B69" t="s">
-        <v>138</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
       </c>
       <c r="D69" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" t="s">
         <v>146</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>147</v>
-      </c>
-      <c r="F69" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
         <v>137</v>
       </c>
-      <c r="B70" t="s">
-        <v>138</v>
-      </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" t="s">
         <v>149</v>
-      </c>
-      <c r="E70" t="s">
-        <v>150</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -2230,136 +2227,136 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" t="s">
         <v>137</v>
       </c>
-      <c r="B71" t="s">
-        <v>138</v>
-      </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
         <v>151</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>152</v>
-      </c>
-      <c r="F71" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" t="s">
         <v>137</v>
       </c>
-      <c r="B72" t="s">
-        <v>138</v>
-      </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" t="s">
         <v>154</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>155</v>
-      </c>
-      <c r="F72" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" t="s">
         <v>137</v>
       </c>
-      <c r="B73" t="s">
-        <v>138</v>
-      </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
         <v>157</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>158</v>
-      </c>
-      <c r="F73" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" t="s">
         <v>137</v>
-      </c>
-      <c r="B74" t="s">
-        <v>138</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
       </c>
       <c r="D74" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
         <v>160</v>
-      </c>
-      <c r="E74" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" t="s">
         <v>137</v>
       </c>
-      <c r="B75" t="s">
-        <v>138</v>
-      </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
+        <v>161</v>
+      </c>
+      <c r="E75" t="s">
         <v>162</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>163</v>
-      </c>
-      <c r="F75" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" t="s">
         <v>137</v>
-      </c>
-      <c r="B76" t="s">
-        <v>138</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
       </c>
       <c r="D76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
         <v>165</v>
-      </c>
-      <c r="E76" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" t="s">
         <v>137</v>
-      </c>
-      <c r="B77" t="s">
-        <v>138</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E77" t="s">
         <v>13</v>
@@ -2370,7 +2367,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -2390,7 +2387,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2410,7 +2407,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2419,7 +2416,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E80" t="s">
         <v>13</v>
@@ -2430,7 +2427,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2439,7 +2436,7 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -2450,7 +2447,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -2459,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -2470,7 +2467,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -2479,7 +2476,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E83" t="s">
         <v>13</v>
@@ -2490,7 +2487,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2499,7 +2496,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
@@ -2510,7 +2507,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2519,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -2530,7 +2527,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -2539,7 +2536,7 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -2550,7 +2547,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2559,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E87" t="s">
         <v>13</v>
@@ -2570,7 +2567,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -2579,7 +2576,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E88" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="172">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -166,36 +166,30 @@
     <t>Party: Lisandro Orozco</t>
   </si>
   <si>
-    <t>presented by; contact named in the filing | lorozco@anaheim.net</t>
+    <t>contact named in the filing | lorozco@anaheim.net</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
   </si>
   <si>
-    <t>Party: City of Anaheim</t>
-  </si>
-  <si>
-    <t>presented by | No phone or email in the record.</t>
+    <t>Party: Stacy Tran</t>
+  </si>
+  <si>
+    <t>contact named in the filing | STran@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
+  </si>
+  <si>
+    <t>6 further records name the body that brought this matter forward (City of Anaheim; Lisandro Orozco; Stacy Tran). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
   </si>
   <si>
     <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
   </si>
   <si>
-    <t>Party: Stacy Tran</t>
-  </si>
-  <si>
-    <t>presented by; contact named in the filing | STran@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>Players: City of Anaheim (presented by)</t>
-  </si>
-  <si>
     <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
   </si>
   <si>
@@ -256,10 +250,13 @@
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
   </si>
   <si>
+    <t>One further record names the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
     <t>2024-05-08. DisneylandForward Project</t>
   </si>
   <si>
-    <t>Players: Disneyland (applicant); City of Anaheim (presented by)</t>
+    <t>Players: Disneyland (applicant)</t>
   </si>
   <si>
     <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
@@ -292,16 +289,7 @@
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
   </si>
   <si>
-    <t>Party: Katherine Luetzow</t>
-  </si>
-  <si>
-    <t>presented by | Director, Planning &amp; Engineering Department: Public Works | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Craig Sandt</t>
-  </si>
-  <si>
-    <t>presented by | Director of Construction Management | No phone or email in the record.</t>
+    <t>4 further records name the body that brought this matter forward (Craig Sandt, Director of Construction Management; Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
   </si>
   <si>
     <t>2026-01-01. CFTOD 2045 Comprehensive Plan - recreation / tourist provisions (p.37)</t>
@@ -313,15 +301,9 @@
     <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
   </si>
   <si>
-    <t>Players: Craig Sandt, Director of Construction Management (presented by)</t>
-  </si>
-  <si>
     <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
   </si>
   <si>
-    <t>Players: Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works (presented by)</t>
-  </si>
-  <si>
     <t>Mixed-Use/Real Estate</t>
   </si>
   <si>
@@ -340,24 +322,24 @@
     <t>applicant | LLC and Joey Caucas | No phone or email in the record.</t>
   </si>
   <si>
-    <t>Party: City of Anaheim Planning Staff</t>
+    <t>Party: Christine Nguyen</t>
+  </si>
+  <si>
+    <t>contact named in the filing | CNguyen2@anaheim.net | Also presenter on 2 other projects in our register: 2 in Anaheim.</t>
   </si>
   <si>
     <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_2bfcbb0f5f83e7b944ef537de2b1fd4a.pdf&amp;view=1#item-ha13a91a5c59d</t>
   </si>
   <si>
-    <t>Party: Christine Nguyen</t>
-  </si>
-  <si>
-    <t>contact named in the filing | CNguyen2@anaheim.net | Also presenter on 2 other projects in our register: 2 in Anaheim.</t>
-  </si>
-  <si>
     <t>Party: Joey Caucas</t>
   </si>
   <si>
     <t>contact named in the filing | No phone or email in the record.</t>
   </si>
   <si>
+    <t>One further record names the body that brought this matter forward (City of Anaheim Planning Staff). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
     <t>2025-01-13. Adoption of Ordinance No. 6601 amending multiple chapters of Title 18 (Zoning) of the Anaheim Municipal Code and adjustments to multiple specific plans</t>
   </si>
   <si>
@@ -397,7 +379,7 @@
     <t>2025-08-10. General Plan Amendment and Zoning Code amendments related to implementation of the Sixth Cycle Housing Element, including updates to General Plan Land Use Element Table LU-2 and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
   </si>
   <si>
-    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Players: City of Anaheim Planning Staff (presented by) | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
+    <t>DEVELOPMENT APPLICATION No. 2021-00223 | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
   </si>
   <si>
     <t>2025-08-11. Levying Special Taxes within City of Anaheim Community Facilities District No. 06-2 (Stadium Lofts) and Community Facilities District No. 08-1 (Platinum Triangle)</t>
@@ -925,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1313,16 +1295,16 @@
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1336,13 +1318,13 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1356,13 +1338,13 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
         <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,13 +1358,13 @@
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
         <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1396,7 +1378,7 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
         <v>13</v>
@@ -1416,13 +1398,13 @@
         <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1436,13 +1418,13 @@
         <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1476,7 +1458,7 @@
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
         <v>13</v>
@@ -1490,13 +1472,13 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
@@ -1510,13 +1492,13 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
         <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
-        <v>75</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1530,13 +1512,13 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
         <v>47</v>
@@ -1550,19 +1532,19 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1570,19 +1552,19 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,19 +1572,19 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1610,19 +1592,19 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" t="s">
         <v>81</v>
       </c>
-      <c r="E40" t="s">
-        <v>82</v>
-      </c>
       <c r="F40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1630,19 +1612,19 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
         <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1650,16 +1632,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" t="s">
         <v>85</v>
-      </c>
-      <c r="E42" t="s">
-        <v>86</v>
       </c>
       <c r="F42" t="s">
         <v>33</v>
@@ -1670,13 +1652,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
@@ -1690,16 +1672,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
         <v>88</v>
       </c>
-      <c r="C44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>89</v>
-      </c>
-      <c r="E44" t="s">
-        <v>90</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -1710,19 +1692,19 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1730,19 +1712,19 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1750,19 +1732,19 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1770,19 +1752,19 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1790,624 +1772,624 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
         <v>103</v>
       </c>
-      <c r="B53" t="s">
+      <c r="E53" t="s">
         <v>104</v>
       </c>
-      <c r="C53" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" t="s">
-        <v>108</v>
-      </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E55" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E57" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F57" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F60" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="F62" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B63" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F65" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>135</v>
+      </c>
+      <c r="E66" t="s">
+        <v>47</v>
+      </c>
+      <c r="F66" t="s">
         <v>136</v>
-      </c>
-      <c r="B66" t="s">
-        <v>137</v>
-      </c>
-      <c r="C66" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>139</v>
-      </c>
-      <c r="F66" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>137</v>
+      </c>
+      <c r="E67" t="s">
+        <v>138</v>
+      </c>
+      <c r="F67" t="s">
         <v>136</v>
-      </c>
-      <c r="B67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" t="s">
-        <v>47</v>
-      </c>
-      <c r="F67" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F68" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E73" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="F74" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="F75" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E76" t="s">
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2416,7 +2398,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
         <v>13</v>
@@ -2427,7 +2409,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2436,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -2447,7 +2429,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -2456,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -2467,7 +2449,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -2476,7 +2458,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E83" t="s">
         <v>13</v>
@@ -2487,7 +2469,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2496,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
@@ -2507,7 +2489,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2516,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -2527,7 +2509,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -2536,7 +2518,7 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -2547,7 +2529,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2556,32 +2538,12 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E87" t="s">
         <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B88" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" t="s">
-        <v>177</v>
-      </c>
-      <c r="E88" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="172">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -181,7 +181,7 @@
     <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
   </si>
   <si>
-    <t>6 further records name the body that brought this matter forward (City of Anaheim; Lisandro Orozco; Stacy Tran). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+    <t>6 further records name the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
   </si>
   <si>
     <t>2026-02-06. OCVibe Residential Phase I</t>
@@ -289,7 +289,7 @@
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
   </si>
   <si>
-    <t>4 further records name the body that brought this matter forward (Craig Sandt, Director of Construction Management; Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+    <t>4 further records name the body that brought this matter forward (Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works; Craig Sandt, Director of Construction Management). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
   </si>
   <si>
     <t>2026-01-01. CFTOD 2045 Comprehensive Plan - recreation / tourist provisions (p.37)</t>
@@ -907,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2335,36 +2335,36 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2378,7 +2378,7 @@
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E79" t="s">
         <v>13</v>
@@ -2398,7 +2398,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E80" t="s">
         <v>13</v>
@@ -2418,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -2458,7 +2458,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E83" t="s">
         <v>13</v>
@@ -2478,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
@@ -2498,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -2518,32 +2518,12 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>162</v>
-      </c>
-      <c r="B87" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>171</v>
-      </c>
-      <c r="E87" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="195">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Filters: dormant excluded | context records included | stage: filed | stage: hearing scheduled | stage: approved | stage: permitted | stage: under construction | venue: Theme Park | venue: Amusement Park | venue: Family Entertainment Center | venue: Museum | venue: Aquarium | venue: Science Center | venue: Heritage/Cultural Site | venue: Integrated Resort | venue: Casino/Gaming | venue: Entertainment District | venue: Entertainment Destination | venue: Mixed-Use Development</t>
   </si>
   <si>
-    <t>Basis: 5 projects, 53 records</t>
+    <t>Basis: 5 projects, 54 records</t>
   </si>
   <si>
     <t>Section</t>
@@ -58,15 +58,33 @@
     <t>ASSESSMENT</t>
   </si>
   <si>
-    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 53 captured records. Of those projects, 5 are described in full, selected by significance. 40 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
+    <t>This report covers United States &gt; Altamonte Springs, Anaheim, Bonita Springs, Central Florida Tourism Oversight District, Clark County, Kissimmee, Lake Buena Vista, Las Vegas, Miami-Dade County, Nashville, Oakland, Phoenix, San Antonio, South Florida, Walt Disney World for July 2026. It is drawn from 5 projects and 54 captured records. Of those projects, 5 are described in full, selected by significance. 76 projects whose every record has been dismissed are excluded entirely, because they have no filing to cite. 66 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Anything outside that geography or period is not covered here.</t>
   </si>
   <si>
     <t>Headline finds</t>
   </si>
   <si>
+    <t>PRESS</t>
+  </si>
+  <si>
+    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
+  </si>
+  <si>
+    <t>2026-07-24 | Clark County</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
+  </si>
+  <si>
     <t>RECORD</t>
   </si>
   <si>
+    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
+  </si>
+  <si>
     <t>OCVibe: Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
   </si>
   <si>
@@ -82,228 +100,216 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3618#item-h84e398be28a0</t>
   </si>
   <si>
-    <t>PRESS</t>
-  </si>
-  <si>
-    <t>Heart Hotel / Kulik River: Las Vegas Topic Kulik River Capital</t>
-  </si>
-  <si>
-    <t>2026-07-24 | Clark County</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/topic/Kulik%20River%20Capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Kulik river capital, LLC: Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
-  </si>
-  <si>
-    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-tm-26-500056</t>
-  </si>
-  <si>
-    <t>Disneyland Resort: Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
+    <t>Disneyland Resort: Determination of good faith compliance with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
   </si>
   <si>
     <t>2026-06-22 | Anaheim</t>
   </si>
   <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World: Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
+  </si>
+  <si>
+    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
+  </si>
+  <si>
+    <t>2026-01-26 | Anaheim</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
+  </si>
+  <si>
+    <t>Entertainment/Attractions</t>
+  </si>
+  <si>
+    <t>OCVibe</t>
+  </si>
+  <si>
+    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
+  </si>
+  <si>
+    <t>Anaheim | approved</t>
+  </si>
+  <si>
+    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC</t>
+  </si>
+  <si>
+    <t>applicant | No phone or email in the record, and no other name alongside it.</t>
+  </si>
+  <si>
+    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
+  </si>
+  <si>
+    <t>Party: Lisandro Orozco</t>
+  </si>
+  <si>
+    <t>contact named in the filing | lorozco@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
+  </si>
+  <si>
+    <t>Party: Stacy Tran</t>
+  </si>
+  <si>
+    <t>contact named in the filing | STran@anaheim.net</t>
+  </si>
+  <si>
+    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
+  </si>
+  <si>
+    <t>8 further records name the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
+    <t>2026-02-06. OCVibe Residential Phase I</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
+  </si>
+  <si>
+    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
+  </si>
+  <si>
+    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
+  </si>
+  <si>
+    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
+  </si>
+  <si>
+    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
+  </si>
+  <si>
+    <t>2026-05-17. Southern California gets $4B mega music venue in giant...</t>
+  </si>
+  <si>
+    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
+  </si>
+  <si>
+    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
+  </si>
+  <si>
+    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
+  </si>
+  <si>
+    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave...</t>
+  </si>
+  <si>
+    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
+  </si>
+  <si>
+    <t>2026-07-13. Determination that property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No. 2020-00004 for the 2025-2026 review period for the OCVibe Site Master Plan project</t>
+  </si>
+  <si>
+    <t>Players: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE) (applicant)</t>
+  </si>
+  <si>
+    <t>Disneyland Resort</t>
+  </si>
+  <si>
+    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
+  </si>
+  <si>
+    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
+  </si>
+  <si>
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3636#item-h5cf18daa4ec3</t>
   </si>
   <si>
-    <t xml:space="preserve">   Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3511#item-h2d4a3a6c3f2a</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World: Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23 | Central Florida Tourism Oversight District</t>
+    <t>Party: Disneyland</t>
+  </si>
+  <si>
+    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
+  </si>
+  <si>
+    <t>One further record names the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
+    <t>2024-05-08. DisneylandForward Project</t>
+  </si>
+  <si>
+    <t>Players: Disneyland (applicant)</t>
+  </si>
+  <si>
+    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
+  </si>
+  <si>
+    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
+  </si>
+  <si>
+    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
+  </si>
+  <si>
+    <t>$10,030,000</t>
+  </si>
+  <si>
+    <t>2026-06-22. Determination of good faith compliance with the terms and conditions of the First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period for the Disneyland Resort Project</t>
+  </si>
+  <si>
+    <t>Players: Walt Disney Parks and Resorts US, Inc. (applicant)</t>
+  </si>
+  <si>
+    <t>CFTOD / Walt Disney World</t>
+  </si>
+  <si>
+    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
+  </si>
+  <si>
+    <t>Central Florida Tourism Oversight District | under construction</t>
+  </si>
+  <si>
+    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
+  </si>
+  <si>
+    <t>4 further records name the body that brought this matter forward (Craig Sandt, Director of Construction Management; Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works; Katherine Luetzow, Director, Planning &amp; Engineering). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+  </si>
+  <si>
+    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - theme park provisions (p.38)</t>
+  </si>
+  <si>
+    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p38</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
+  </si>
+  <si>
+    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
   </si>
   <si>
     <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.2-p12</t>
   </si>
   <si>
-    <t>Platinum Triangle / PT Metro: Establish new development timeframes and performance time schedule for Development Agreement No. 2005-00008</t>
-  </si>
-  <si>
-    <t>2026-01-26 | Anaheim</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3560#item-h9f77764dd1e5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Development agreement no. 2005-00008 Addendum no. 4 To platinum triangle expansion project mitigation monitoring plan no. 321 Applicant : PT Metro, LLC and Joey Caucas; 20 Enterprise, Suite #125...</t>
-  </si>
-  <si>
-    <t>Entertainment/Attractions</t>
-  </si>
-  <si>
-    <t>OCVibe</t>
-  </si>
-  <si>
-    <t>Approve Cooperative Agreement No. 12-0876, in substantial form, with Caltrans for design (plans, specifications, and estimates) services for the Northbound SR-57 Off-Ramp to Katella Avenue...</t>
-  </si>
-  <si>
-    <t>Anaheim | approved</t>
-  </si>
-  <si>
-    <t>Records show 4 filings and 4 press reports between 2026-02-06 and 2026-07-13.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC</t>
-  </si>
-  <si>
-    <t>applicant | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>Party: Anaheim Real Estate Partners, LLC, TS Anaheim, LLC and FCD, LLC (OCVIBE)</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_7f2f654f7555addc70231de198fa22d9.pdf&amp;view=1#item-h9f002fc7dbca</t>
-  </si>
-  <si>
-    <t>Party: Lisandro Orozco</t>
-  </si>
-  <si>
-    <t>contact named in the filing | lorozco@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_45b322ae69423ed7f4d96ffe8e8de725.pdf&amp;view=1#item-h9fe8d90cfc0b</t>
-  </si>
-  <si>
-    <t>Party: Stacy Tran</t>
-  </si>
-  <si>
-    <t>contact named in the filing | STran@anaheim.net</t>
-  </si>
-  <si>
-    <t>https://www.anaheim.net/DocumentCenter/View/66931/Planning-Commission-Action-Agenda---10202025#item-h6dc7e70418cc</t>
-  </si>
-  <si>
-    <t>6 further records name the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
-  </si>
-  <si>
-    <t>2026-02-06. OCVibe Residential Phase I</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2004121045</t>
-  </si>
-  <si>
-    <t>2026-04-20. Approve Amendment No. 2 to Bond Purchase Agreement between the City of Anaheim, the Public Financing Authority, and JP Morgan amending the scheduled completion date to no later than June 25, 2027 for the parking decks associated with the OCVibe Project; and authorize the Finance Director to execute the amendment</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3606#item-h11f1fc13fc80</t>
-  </si>
-  <si>
-    <t>2026-05-05. OCVibe | The new heart of Orange County</t>
-  </si>
-  <si>
-    <t>https://www.ocvibe.com/news/ocvibe-and-award-winning-art-and-design-studio-futureforms-unveil-plans-for-historic-arts-program-in-southern-california</t>
-  </si>
-  <si>
-    <t>2026-05-11. Approve Cooperative Agreement No. 12-0876 with Caltrans for design services and Cooperative Agreement No. 12-0877 with Caltrans for right-of-way services for SR-57 off-ramps</t>
-  </si>
-  <si>
-    <t>2026-05-17. Southern California gets $4B mega music venue in giant ...</t>
-  </si>
-  <si>
-    <t>https://nypost.com/2026/05/18/lifestyle/southern-california-lands-mega-venue-in-new-entertainment-district/</t>
-  </si>
-  <si>
-    <t>2026-05-31. First Phase of $4B OCVibe Takes Shape</t>
-  </si>
-  <si>
-    <t>https://www.ocbj.com/oc-homepage/first-phase-of-4b-ocvibe-takes-shape/</t>
-  </si>
-  <si>
-    <t>2026-06-22. 2525 E Katella Ave, Anaheim, CA 92806 - The Weave ...</t>
-  </si>
-  <si>
-    <t>https://www.loopnet.com/Listing/2525-E-Katella-Ave-Anaheim-CA/29241061/</t>
-  </si>
-  <si>
-    <t>2026-07-13. Determine on the basis of the evidence submitted by Anaheim Real Estate Partners, LLC, TS Anaheim, LLC, and FCD, LLC (OCVibe), that the property owner has complied in good faith with the terms and conditions of Amended and Restated Development Agreement No...</t>
-  </si>
-  <si>
-    <t>Disneyland Resort</t>
-  </si>
-  <si>
-    <t>Approve the Cooperative Agreement with Walt Disney Parks and Resorts U.S., INC., in the amount estimated at $10,030,000, for funding, design...</t>
-  </si>
-  <si>
-    <t>Records show 4 filings on the first amended and restated development agreement between 2024-05-08 and 2026-06-22.</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts U.S., Inc.</t>
-  </si>
-  <si>
-    <t>Party: Disneyland</t>
-  </si>
-  <si>
-    <t>https://ceqanet.lci.ca.gov/Project/2021100402</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks and Resorts US, Inc.</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/DocumentViewer.php?file=anaheim_5713ee926e19136cdccede9cc8a3ce47.pdf&amp;view=1#item-h72954c9ae56e</t>
-  </si>
-  <si>
-    <t>One further record names the body that brought this matter forward (City of Anaheim). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
-  </si>
-  <si>
-    <t>2024-05-08. DisneylandForward Project</t>
-  </si>
-  <si>
-    <t>Players: Disneyland (applicant)</t>
-  </si>
-  <si>
-    <t>2025-06-16. Determine compliance in good faith with terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2024-2025 review period</t>
-  </si>
-  <si>
-    <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3425#item-h86fdaecda3ed</t>
-  </si>
-  <si>
-    <t>2025-10-27. Approve Cooperative Agreement for funding, design, and construction of Katella Avenue Widening</t>
-  </si>
-  <si>
-    <t>$10,030,000</t>
-  </si>
-  <si>
-    <t>2026-06-22. Determine compliance in good faith with the terms and conditions of First Amended and Restated Development Agreement No. 96-01 for the 2025-2026 review period</t>
-  </si>
-  <si>
-    <t>CFTOD / Walt Disney World</t>
-  </si>
-  <si>
-    <t>Records show 3 filings between 2026-01-01 and 2026-01-23.</t>
-  </si>
-  <si>
-    <t>Central Florida Tourism Oversight District | under construction</t>
-  </si>
-  <si>
-    <t>Party: Walt Disney Parks &amp; Resorts U.S. Inc.</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/1-23-2026-BOS-Agenda-Packet-FINALcs.pdf#item-6.4-p146</t>
-  </si>
-  <si>
-    <t>4 further records name the body that brought this matter forward (Katherine Luetzow, Director, Planning &amp; Engineering Department: Public Works; Craig Sandt, Director of Construction Management). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
-  </si>
-  <si>
-    <t>2026-01-01. CFTOD 2045 Comprehensive Plan - recreation / tourist provisions (p.37)</t>
-  </si>
-  <si>
-    <t>https://www.oversightdistrict.org/wp-content/uploads/2026/01/2045-CFTOD-Comprehensive-Plan.pdf#plan-p37</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the First Amendment to Roadway Expansion Land Dedication and Reimbursement Agreement and authorize the District Administrator or her designee to execute same</t>
-  </si>
-  <si>
-    <t>2026-01-23. Approve the District Administrator to execute a Non-exclusive temporary easement with permanent easement for underground communication lines</t>
-  </si>
-  <si>
     <t>Mixed-Use/Real Estate</t>
   </si>
   <si>
@@ -334,10 +340,7 @@
     <t>Party: Joey Caucas</t>
   </si>
   <si>
-    <t>contact named in the filing | No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>One further record names the body that brought this matter forward (City of Anaheim Planning Staff). That is who moved it in government rather than who is behind it, so it is not listed above as a party to approach.</t>
+    <t>contact named in the filing | No phone or email in the record, and no other name alongside it.</t>
   </si>
   <si>
     <t>2025-01-13. Adoption of Ordinance No. 6601 amending multiple chapters of Title 18 (Zoning) of the Anaheim Municipal Code and adjustments to multiple specific plans</t>
@@ -349,7 +352,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3305#item-h9b4b4aa880b3</t>
   </si>
   <si>
-    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, adopt a new Environmental Justice Element, amend Title 18 (Zoning) of the Anaheim Municipal Code, reclassify zoning, and amend the Platinum Triangle Master Land Use Plan and specific plans...</t>
+    <t>2025-03-23. City-initiated General Plan Amendments to update the General Plan Land Use and Circulation Elements, and adopt a new Environmental Justice Element; amendments to Title 18 (Zoning) of the Anaheim Municipal Code; Zoning Reclassification amending the Zoning Map...</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2021-00223</t>
@@ -376,7 +379,7 @@
     <t>https://anaheim.granicus.com/AgendaViewer.php?view_id=2&amp;clip_id=3398#item-h4c01cf1c0349</t>
   </si>
   <si>
-    <t>2025-08-10. General Plan Amendment and Zoning Code amendments related to implementation of the Sixth Cycle Housing Element, including updates to General Plan Land Use Element Table LU-2 and amendments to Title 18 (Zoning) of the Anaheim Municipal Code</t>
+    <t>2025-08-10. General Plan Amendment to update the General Plan Land Use Element Table LU-2 (Residential Land Use Designations); amendments to Title 18 (Zoning) of the Anaheim Municipal Code modifying Chapters 18.06 (Multiple-Family Residential Zones), 18.12 (Mixed-Use Zone), and 18.52 (Housing Incentives)</t>
   </si>
   <si>
     <t>DEVELOPMENT APPLICATION No. 2021-00223 | Contact: Christine Nguyen. CNguyen2@anaheim.net.</t>
@@ -412,7 +415,7 @@
     <t>Tentative map consisting of 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay.</t>
   </si>
   <si>
-    <t>Clark County | filed</t>
+    <t>Clark County | permitted</t>
   </si>
   <si>
     <t>Records show 5 filings and 3 press reports between 2026-05-26 and 2026-07-24.</t>
@@ -421,7 +424,64 @@
     <t>Party: Kulik River Capital, LLC</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110427</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110425</t>
+  </si>
+  <si>
+    <t>Party: Lorenzo Doumani</t>
+  </si>
+  <si>
+    <t>applicant; contact named in the filing | No phone or email in the record, and no other name alongside it.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=109036</t>
+  </si>
+  <si>
+    <t>Party: 305 Ccd, LLC</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=109037</t>
+  </si>
+  <si>
+    <t>Party: Formula 1 Las Vegas Grand Prix</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=109817</t>
+  </si>
+  <si>
+    <t>Party: Greengale Properties, LLC</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=107991</t>
+  </si>
+  <si>
+    <t>Party: Hatchwell Studios</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=108501</t>
+  </si>
+  <si>
+    <t>Party: Kelly Lawson</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=109486</t>
+  </si>
+  <si>
+    <t>Party: LV Diamond Property I, LLC</t>
+  </si>
+  <si>
+    <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:f1a4b305-a7fb-49f7-a5fe-06ab39312955/original/as/Paradise-Minutes-042826.pdf#item-ar-26-400027+uc-22-0556</t>
+  </si>
+  <si>
+    <t>Party: MSG Las Vegas, LLC</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=107709</t>
+  </si>
+  <si>
+    <t>Party: Uncommons Living BLDG 1, LLC</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=108370</t>
   </si>
   <si>
     <t>Party: Nancy Amundsen</t>
@@ -430,22 +490,22 @@
     <t>representative; contact named in the filing | Brown, Brown, &amp; Premsrirut | 520 S. 4th Street, Las Vegas, NV 89101 | No phone or email in the record.</t>
   </si>
   <si>
+    <t>Party: Lebene Aidam-ohene</t>
+  </si>
+  <si>
+    <t>representative | Brown Brown &amp; Premsrirut | 520 S. Fourth Street #200, Las Vegas, NV 89101 | No phone or email in the record.</t>
+  </si>
+  <si>
     <t>Party: Eli Applebaum</t>
   </si>
   <si>
-    <t>named in press coverage | No phone or email in the record.</t>
+    <t>named in press coverage | No phone or email in the record, and no other name alongside it.</t>
   </si>
   <si>
     <t>https://traveltomorrow.com/new-heart-shaped-hotel-approved-for-las-vegas-strip-sparks-debate-over-tacky-design/</t>
   </si>
   <si>
-    <t>2026-05-26. Tentative map approval for 1 commercial lot on 11.95 acres in a CR (Commercial Resort) Zone within the Airport Environs (AE-60) Overlay</t>
-  </si>
-  <si>
-    <t>TM-26-500056</t>
-  </si>
-  <si>
-    <t>2026-05-26. Use Permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; Waiver of Development Standards for non-standard improvements in right-of-way; Design Review for proposed resort hotel and recreational facility</t>
+    <t>2026-05-26. Use permits to expand gaming enterprise district, construct resort hotel, and construct recreational facility; waiver of development standards for non-standard improvements in right-of-way; design review for proposed resort hotel and recreational facility</t>
   </si>
   <si>
     <t>UC-26-0219</t>
@@ -454,6 +514,36 @@
     <t>https://www.clarkcountynv.gov/adobe/assets/urn:aaid:aem:bcdf1925-6c37-4308-b6f6-c718c78c9183/original/as/Paradise-Minutes-052626.pdf#item-uc-26-0219</t>
   </si>
   <si>
+    <t>2026-05-26. Tentative map</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres</t>
+  </si>
+  <si>
+    <t>2026-07-21. Holdover tentative map approval</t>
+  </si>
+  <si>
+    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
+  </si>
+  <si>
+    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
+  </si>
+  <si>
+    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
+  </si>
+  <si>
+    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
+  </si>
+  <si>
+    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation wheel gets green light</t>
+  </si>
+  <si>
+    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
+  </si>
+  <si>
     <t>2026-07-21. Holdover use permits to expand the gaming enterprise district, resort hotel, and recreational facility; Waiver of development standards to allow non-standard improvements in the right-of-way; Design review for a proposed resort hotel and recreational facility</t>
   </si>
   <si>
@@ -463,30 +553,6 @@
     <t>https://clark.legistar.com/Legislation.aspx#matter-110426</t>
   </si>
   <si>
-    <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
-  </si>
-  <si>
-    <t>VS-26-0218 | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/Legislation.aspx#matter-110425</t>
-  </si>
-  <si>
-    <t>2026-07-21. Resort project replacing failed Las Vegas Strip observation ...</t>
-  </si>
-  <si>
-    <t>https://news3lv.com/news/local/resort-project-skyvue-failed-las-vegas-strip-observation-wheel-clark-county-commission-zoning-approval</t>
-  </si>
-  <si>
-    <t>2026-07-21. Holdover tentative map</t>
-  </si>
-  <si>
-    <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen, Brown, Brown, &amp; Premsrirut. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
-  </si>
-  <si>
     <t>2026-07-23. Las Vegas Approves Heart-Shaped Casino on SkyVue Site</t>
   </si>
   <si>
@@ -511,7 +577,7 @@
     <t>Dormant projects are excluded from this report. None in this geography is dormant.</t>
   </si>
   <si>
-    <t>40 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Confirming them on the register and regenerating is what puts them in this document.</t>
+    <t>66 projects this scope proposes are held out of this document because they have not been confirmed as part of Simtec Attractions' coverage. A scope is a proposal: it finds projects that look like a match, and each one is confirmed by hand on the register before it may be printed. Those projects are on the register, unconfirmed, and are not a statement that they do not belong here. Confirming them on the register and regenerating is what puts them in this document.</t>
   </si>
   <si>
     <t>This document describes the 15 most significant projects in scope. Every project in scope is described.</t>
@@ -520,10 +586,13 @@
     <t>1 project described above has a one-line description on our register that is not printed here. Those lines were written by a model reading the filings rather than quoted from one, so there is no document to cite for them and they are not offered as Philip's assessment either. The filings under each entry are unaffected.</t>
   </si>
   <si>
-    <t>10 further filings on the projects described are in scope but not printed, because each project shows its most recent filings only.</t>
+    <t>11 further filings on the projects described are in scope but not printed, because each project shows its most recent filings only.</t>
   </si>
   <si>
     <t>12 records counted on the cover are the same filing captured more than once - a bilingual minute, or a document captured page by page - and are shown once above.</t>
+  </si>
+  <si>
+    <t>76 projects in this geography hold no live record and are excluded: every record attached to them has been dismissed on review, so there is nothing to cite.</t>
   </si>
   <si>
     <t>Records are captured from published sources. A matter that has not been published, or that is published somewhere we do not yet capture, will not appear.</t>
@@ -907,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1015,16 +1084,16 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1035,7 +1104,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -1055,7 +1124,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -1075,7 +1144,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
@@ -1095,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -1115,7 +1184,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
@@ -1135,7 +1204,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -1155,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
@@ -1175,7 +1244,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
@@ -1184,7 +1253,7 @@
         <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1215,7 +1284,7 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
@@ -1224,7 +1293,7 @@
         <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1235,7 +1304,7 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -1255,7 +1324,7 @@
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
@@ -1275,7 +1344,7 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>53</v>
@@ -1315,7 +1384,7 @@
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
         <v>57</v>
@@ -1335,7 +1404,7 @@
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
         <v>59</v>
@@ -1355,7 +1424,7 @@
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
         <v>61</v>
@@ -1375,7 +1444,7 @@
         <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
         <v>63</v>
@@ -1384,7 +1453,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1395,7 +1464,7 @@
         <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
@@ -1415,7 +1484,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
         <v>66</v>
@@ -1435,7 +1504,7 @@
         <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
@@ -1455,16 +1524,16 @@
         <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1472,13 +1541,13 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
@@ -1492,13 +1561,13 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1512,19 +1581,19 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E36" t="s">
         <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1532,19 +1601,19 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1552,19 +1621,19 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1572,13 +1641,13 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
         <v>44</v>
@@ -1592,19 +1661,19 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1612,19 +1681,19 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1632,16 +1701,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
         <v>33</v>
@@ -1652,16 +1721,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
@@ -1672,16 +1741,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -1692,19 +1761,19 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1712,16 +1781,16 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
@@ -1732,19 +1801,19 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E47" t="s">
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1752,13 +1821,13 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
         <v>13</v>
@@ -1772,33 +1841,33 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E49" t="s">
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>44</v>
@@ -1809,16 +1878,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
         <v>44</v>
@@ -1829,19 +1898,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
@@ -1849,39 +1918,39 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
@@ -1889,359 +1958,359 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F58" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F59" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="F61" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E62" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F62" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F64" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="F66" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="F67" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E70" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="F70" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E71" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="F71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="F72" t="s">
         <v>152</v>
@@ -2249,19 +2318,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
         <v>153</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F73" t="s">
         <v>154</v>
@@ -2269,261 +2338,481 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
         <v>155</v>
       </c>
       <c r="E74" t="s">
+        <v>47</v>
+      </c>
+      <c r="F74" t="s">
         <v>156</v>
-      </c>
-      <c r="F74" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
+        <v>157</v>
+      </c>
+      <c r="E75" t="s">
         <v>158</v>
       </c>
-      <c r="E75" t="s">
-        <v>13</v>
-      </c>
       <c r="F75" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" t="s">
         <v>160</v>
       </c>
-      <c r="E76" t="s">
-        <v>13</v>
-      </c>
       <c r="F76" t="s">
-        <v>26</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" t="s">
+        <v>132</v>
+      </c>
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" t="s">
         <v>161</v>
       </c>
-      <c r="B77" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" t="s">
-        <v>24</v>
-      </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="F77" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
       <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>184</v>
+      </c>
+      <c r="B88" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" t="s">
         <v>14</v>
       </c>
-      <c r="D86" t="s">
-        <v>171</v>
-      </c>
-      <c r="E86" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="D88" t="s">
+        <v>185</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>184</v>
+      </c>
+      <c r="B89" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>184</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" t="s">
+        <v>187</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>184</v>
+      </c>
+      <c r="B91" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" t="s">
+        <v>188</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" t="s">
+        <v>189</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>191</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>184</v>
+      </c>
+      <c r="B95" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
+        <v>192</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" t="s">
+        <v>193</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>184</v>
+      </c>
+      <c r="B97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" t="s">
+        <v>194</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" t="s">
         <v>13</v>
       </c>
     </row>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="194">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -424,7 +424,7 @@
     <t>Party: Kulik River Capital, LLC</t>
   </si>
   <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110425</t>
+    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
   </si>
   <si>
     <t>Party: Lorenzo Doumani</t>
@@ -524,9 +524,6 @@
   </si>
   <si>
     <t>TM-26-500056 | 11.95 acres | Contact: Nancy Amundsen. No phone or email in the record.</t>
-  </si>
-  <si>
-    <t>https://clark.legistar.com/gateway.aspx?M=l&amp;ID=110427</t>
   </si>
   <si>
     <t>2026-07-21. Vacate and abandon easements of interest to Clark County located between Mandalay Bay Road and Four Seasons Drive, and Las Vegas Boulevard South and Haven Street; and a portion of a right-of-way being Mandalay Bay Road located between Las Vegas Boulevard South and Haven Street within Paradise</t>
@@ -2473,7 +2470,7 @@
         <v>170</v>
       </c>
       <c r="F80" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2487,13 +2484,13 @@
         <v>21</v>
       </c>
       <c r="D81" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" t="s">
         <v>172</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>173</v>
-      </c>
-      <c r="F81" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2507,13 +2504,13 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
+        <v>174</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
         <v>175</v>
-      </c>
-      <c r="E82" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2527,13 +2524,13 @@
         <v>21</v>
       </c>
       <c r="D83" t="s">
+        <v>176</v>
+      </c>
+      <c r="E83" t="s">
         <v>177</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>178</v>
-      </c>
-      <c r="F83" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2547,13 +2544,13 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
+        <v>179</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
         <v>180</v>
-      </c>
-      <c r="E84" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2567,7 +2564,7 @@
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -2578,7 +2575,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -2598,7 +2595,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2618,7 +2615,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -2627,7 +2624,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E88" t="s">
         <v>13</v>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -2647,7 +2644,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E89" t="s">
         <v>13</v>
@@ -2658,7 +2655,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -2667,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
@@ -2678,7 +2675,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -2687,7 +2684,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
@@ -2698,7 +2695,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -2707,7 +2704,7 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E92" t="s">
         <v>13</v>
@@ -2718,7 +2715,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -2727,7 +2724,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -2738,7 +2735,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -2747,7 +2744,7 @@
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E94" t="s">
         <v>13</v>
@@ -2758,7 +2755,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -2767,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
@@ -2778,7 +2775,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -2787,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E96" t="s">
         <v>13</v>
@@ -2798,7 +2795,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2807,7 +2804,7 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E97" t="s">
         <v>13</v>

--- a/dashboard/e2e/shots/documents/full-report.xlsx
+++ b/dashboard/e2e/shots/documents/full-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="197">
   <si>
     <t>Market intelligence report</t>
   </si>
@@ -569,6 +569,15 @@
   </si>
   <si>
     <t>The period is July 2026. Activity outside it is not included even where it concerns the same project.</t>
+  </si>
+  <si>
+    <t>Coverage of Anaheim does not reach the decision, its body and its date. This is a limit of what we read in Anaheim, not a finding that the record is silent on it.</t>
+  </si>
+  <si>
+    <t>Coverage of Central Florida Tourism Oversight District does not reach the stated facts of the scheme and the decision, its body and its date. This is a limit of what we read in Central Florida Tourism Oversight District, not a finding that the record is silent on it.</t>
+  </si>
+  <si>
+    <t>Conditions of approval are published per project in Clark County, and nowhere else this document covers: Anaheim and Central Florida Tourism Oversight District do not publish them per project. Nothing here should be read as saying an approval in those markets carries no conditions. Where such requirements exist they are standing requirements of the jurisdiction rather than terms attached to this approval, and we do not reproduce them.</t>
   </si>
   <si>
     <t>Dormant projects are excluded from this report. None in this geography is dormant.</t>
@@ -973,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2813,6 +2822,66 @@
         <v>13</v>
       </c>
     </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>183</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
+        <v>194</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>195</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
+        <v>196</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
